--- a/3_TAI_LIEU/MAU_NHAP_HANG_LOAT/Mau_nhap_chi_phi.xlsx
+++ b/3_TAI_LIEU/MAU_NHAP_HANG_LOAT/Mau_nhap_chi_phi.xlsx
@@ -164,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -198,9 +198,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
@@ -257,7 +254,7 @@
     <tabColor rgb="FFB4531A"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L504"/>
+  <dimension ref="A1:M504"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -267,11 +264,12 @@
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -291,6 +289,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -309,6 +308,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -335,6 +335,7 @@
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -369,30 +370,35 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SL container</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
+          <t xml:space="preserve">SL (số lượng)</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Số tiền trước thuế *</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Thuế</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chi hộ (1/0)</t>
-        </is>
-      </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thu hộ (1/0)</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tiền tệ</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mã dịch vụ</t>
         </is>
@@ -405,12 +411,13 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="12"/>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
@@ -419,12 +426,13 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
@@ -433,12 +441,13 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
@@ -447,12 +456,13 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
@@ -461,12 +471,13 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -475,12 +486,13 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -489,12 +501,13 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -503,12 +516,13 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -517,12 +531,13 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -531,12 +546,13 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -545,12 +561,13 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -559,12 +576,13 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="12"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -573,12 +591,13 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -587,12 +606,13 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -601,12 +621,13 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -615,12 +636,13 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="12"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
@@ -629,12 +651,13 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
@@ -643,12 +666,13 @@
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="12"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
     </row>
     <row r="23">
       <c r="A23" s="11"/>
@@ -657,12 +681,13 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="12"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
     </row>
     <row r="24">
       <c r="A24" s="11"/>
@@ -671,12 +696,13 @@
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="12"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
     </row>
     <row r="25">
       <c r="A25" s="11"/>
@@ -685,12 +711,13 @@
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="12"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
@@ -699,12 +726,13 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="12"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
     </row>
     <row r="27">
       <c r="A27" s="11"/>
@@ -713,12 +741,13 @@
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="12"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
     </row>
     <row r="28">
       <c r="A28" s="11"/>
@@ -727,12 +756,13 @@
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="12"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
     </row>
     <row r="29">
       <c r="A29" s="11"/>
@@ -741,12 +771,13 @@
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="12"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
     </row>
     <row r="30">
       <c r="A30" s="11"/>
@@ -755,12 +786,13 @@
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="12"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
     </row>
     <row r="31">
       <c r="A31" s="11"/>
@@ -769,12 +801,13 @@
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="12"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
     </row>
     <row r="32">
       <c r="A32" s="11"/>
@@ -783,12 +816,13 @@
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="12"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
     </row>
     <row r="33">
       <c r="A33" s="11"/>
@@ -797,12 +831,13 @@
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="12"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
     </row>
     <row r="34">
       <c r="A34" s="11"/>
@@ -811,12 +846,13 @@
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="12"/>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
     </row>
     <row r="35">
       <c r="A35" s="11"/>
@@ -825,12 +861,13 @@
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="12"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
     </row>
     <row r="36">
       <c r="A36" s="11"/>
@@ -839,12 +876,13 @@
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="12"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
     </row>
     <row r="37">
       <c r="A37" s="11"/>
@@ -853,12 +891,13 @@
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="12"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
     </row>
     <row r="38">
       <c r="A38" s="11"/>
@@ -867,12 +906,13 @@
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="12"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
     </row>
     <row r="39">
       <c r="A39" s="11"/>
@@ -881,12 +921,13 @@
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="12"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
     </row>
     <row r="40">
       <c r="A40" s="11"/>
@@ -895,12 +936,13 @@
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="12"/>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
     </row>
     <row r="41">
       <c r="A41" s="11"/>
@@ -909,12 +951,13 @@
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="12"/>
       <c r="J41" s="11"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
     </row>
     <row r="42">
       <c r="A42" s="11"/>
@@ -923,12 +966,13 @@
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="12"/>
       <c r="J42" s="11"/>
       <c r="K42" s="11"/>
       <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
     </row>
     <row r="43">
       <c r="A43" s="11"/>
@@ -937,12 +981,13 @@
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="12"/>
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
     </row>
     <row r="44">
       <c r="A44" s="11"/>
@@ -951,12 +996,13 @@
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="12"/>
       <c r="J44" s="11"/>
       <c r="K44" s="11"/>
       <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
     </row>
     <row r="45">
       <c r="A45" s="11"/>
@@ -965,12 +1011,13 @@
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="12"/>
       <c r="J45" s="11"/>
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
     </row>
     <row r="46">
       <c r="A46" s="11"/>
@@ -979,12 +1026,13 @@
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="12"/>
       <c r="J46" s="11"/>
       <c r="K46" s="11"/>
       <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
     </row>
     <row r="47">
       <c r="A47" s="11"/>
@@ -993,12 +1041,13 @@
       <c r="D47" s="11"/>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="12"/>
       <c r="J47" s="11"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
     </row>
     <row r="48">
       <c r="A48" s="11"/>
@@ -1007,12 +1056,13 @@
       <c r="D48" s="11"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="12"/>
       <c r="J48" s="11"/>
       <c r="K48" s="11"/>
       <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
     </row>
     <row r="49">
       <c r="A49" s="11"/>
@@ -1021,12 +1071,13 @@
       <c r="D49" s="11"/>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="12"/>
       <c r="J49" s="11"/>
       <c r="K49" s="11"/>
       <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
     </row>
     <row r="50">
       <c r="A50" s="11"/>
@@ -1035,12 +1086,13 @@
       <c r="D50" s="11"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="12"/>
       <c r="J50" s="11"/>
       <c r="K50" s="11"/>
       <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
     </row>
     <row r="51">
       <c r="A51" s="11"/>
@@ -1049,12 +1101,13 @@
       <c r="D51" s="11"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="12"/>
       <c r="J51" s="11"/>
       <c r="K51" s="11"/>
       <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
     </row>
     <row r="52">
       <c r="A52" s="11"/>
@@ -1063,12 +1116,13 @@
       <c r="D52" s="11"/>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="12"/>
       <c r="J52" s="11"/>
       <c r="K52" s="11"/>
       <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
     </row>
     <row r="53">
       <c r="A53" s="11"/>
@@ -1077,12 +1131,13 @@
       <c r="D53" s="11"/>
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="12"/>
       <c r="J53" s="11"/>
       <c r="K53" s="11"/>
       <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
     </row>
     <row r="54">
       <c r="A54" s="11"/>
@@ -1091,12 +1146,13 @@
       <c r="D54" s="11"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="12"/>
       <c r="J54" s="11"/>
       <c r="K54" s="11"/>
       <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
     </row>
     <row r="55">
       <c r="A55" s="11"/>
@@ -1105,12 +1161,13 @@
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="12"/>
       <c r="J55" s="11"/>
       <c r="K55" s="11"/>
       <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
     </row>
     <row r="56">
       <c r="A56" s="11"/>
@@ -1119,12 +1176,13 @@
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="12"/>
       <c r="J56" s="11"/>
       <c r="K56" s="11"/>
       <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
     </row>
     <row r="57">
       <c r="A57" s="11"/>
@@ -1133,12 +1191,13 @@
       <c r="D57" s="11"/>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="12"/>
       <c r="J57" s="11"/>
       <c r="K57" s="11"/>
       <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
     </row>
     <row r="58">
       <c r="A58" s="11"/>
@@ -1147,12 +1206,13 @@
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="12"/>
       <c r="J58" s="11"/>
       <c r="K58" s="11"/>
       <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
     </row>
     <row r="59">
       <c r="A59" s="11"/>
@@ -1161,12 +1221,13 @@
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
       <c r="F59" s="11"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="12"/>
       <c r="J59" s="11"/>
       <c r="K59" s="11"/>
       <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
     </row>
     <row r="60">
       <c r="A60" s="11"/>
@@ -1175,12 +1236,13 @@
       <c r="D60" s="11"/>
       <c r="E60" s="11"/>
       <c r="F60" s="11"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="12"/>
       <c r="J60" s="11"/>
       <c r="K60" s="11"/>
       <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
     </row>
     <row r="61">
       <c r="A61" s="11"/>
@@ -1189,12 +1251,13 @@
       <c r="D61" s="11"/>
       <c r="E61" s="11"/>
       <c r="F61" s="11"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="12"/>
       <c r="J61" s="11"/>
       <c r="K61" s="11"/>
       <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
     </row>
     <row r="62">
       <c r="A62" s="11"/>
@@ -1203,12 +1266,13 @@
       <c r="D62" s="11"/>
       <c r="E62" s="11"/>
       <c r="F62" s="11"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="12"/>
       <c r="J62" s="11"/>
       <c r="K62" s="11"/>
       <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
     </row>
     <row r="63">
       <c r="A63" s="11"/>
@@ -1217,12 +1281,13 @@
       <c r="D63" s="11"/>
       <c r="E63" s="11"/>
       <c r="F63" s="11"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="12"/>
       <c r="J63" s="11"/>
       <c r="K63" s="11"/>
       <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
     </row>
     <row r="64">
       <c r="A64" s="11"/>
@@ -1231,12 +1296,13 @@
       <c r="D64" s="11"/>
       <c r="E64" s="11"/>
       <c r="F64" s="11"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="12"/>
       <c r="J64" s="11"/>
       <c r="K64" s="11"/>
       <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
     </row>
     <row r="65">
       <c r="A65" s="11"/>
@@ -1245,12 +1311,13 @@
       <c r="D65" s="11"/>
       <c r="E65" s="11"/>
       <c r="F65" s="11"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="12"/>
       <c r="J65" s="11"/>
       <c r="K65" s="11"/>
       <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
     </row>
     <row r="66">
       <c r="A66" s="11"/>
@@ -1259,12 +1326,13 @@
       <c r="D66" s="11"/>
       <c r="E66" s="11"/>
       <c r="F66" s="11"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="12"/>
       <c r="J66" s="11"/>
       <c r="K66" s="11"/>
       <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
     </row>
     <row r="67">
       <c r="A67" s="11"/>
@@ -1273,12 +1341,13 @@
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
       <c r="F67" s="11"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="12"/>
       <c r="J67" s="11"/>
       <c r="K67" s="11"/>
       <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
     </row>
     <row r="68">
       <c r="A68" s="11"/>
@@ -1287,12 +1356,13 @@
       <c r="D68" s="11"/>
       <c r="E68" s="11"/>
       <c r="F68" s="11"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="12"/>
       <c r="J68" s="11"/>
       <c r="K68" s="11"/>
       <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
     </row>
     <row r="69">
       <c r="A69" s="11"/>
@@ -1301,12 +1371,13 @@
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
       <c r="F69" s="11"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="12"/>
       <c r="J69" s="11"/>
       <c r="K69" s="11"/>
       <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
     </row>
     <row r="70">
       <c r="A70" s="11"/>
@@ -1315,12 +1386,13 @@
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
       <c r="F70" s="11"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="12"/>
       <c r="J70" s="11"/>
       <c r="K70" s="11"/>
       <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
     </row>
     <row r="71">
       <c r="A71" s="11"/>
@@ -1329,12 +1401,13 @@
       <c r="D71" s="11"/>
       <c r="E71" s="11"/>
       <c r="F71" s="11"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="12"/>
       <c r="J71" s="11"/>
       <c r="K71" s="11"/>
       <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
     </row>
     <row r="72">
       <c r="A72" s="11"/>
@@ -1343,12 +1416,13 @@
       <c r="D72" s="11"/>
       <c r="E72" s="11"/>
       <c r="F72" s="11"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="12"/>
       <c r="J72" s="11"/>
       <c r="K72" s="11"/>
       <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
     </row>
     <row r="73">
       <c r="A73" s="11"/>
@@ -1357,12 +1431,13 @@
       <c r="D73" s="11"/>
       <c r="E73" s="11"/>
       <c r="F73" s="11"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="12"/>
       <c r="J73" s="11"/>
       <c r="K73" s="11"/>
       <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
     </row>
     <row r="74">
       <c r="A74" s="11"/>
@@ -1371,12 +1446,13 @@
       <c r="D74" s="11"/>
       <c r="E74" s="11"/>
       <c r="F74" s="11"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="12"/>
       <c r="J74" s="11"/>
       <c r="K74" s="11"/>
       <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
     </row>
     <row r="75">
       <c r="A75" s="11"/>
@@ -1385,12 +1461,13 @@
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
       <c r="F75" s="11"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="12"/>
       <c r="J75" s="11"/>
       <c r="K75" s="11"/>
       <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
     </row>
     <row r="76">
       <c r="A76" s="11"/>
@@ -1399,12 +1476,13 @@
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
       <c r="F76" s="11"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="12"/>
       <c r="J76" s="11"/>
       <c r="K76" s="11"/>
       <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
     </row>
     <row r="77">
       <c r="A77" s="11"/>
@@ -1413,12 +1491,13 @@
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
       <c r="F77" s="11"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="12"/>
       <c r="J77" s="11"/>
       <c r="K77" s="11"/>
       <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
     </row>
     <row r="78">
       <c r="A78" s="11"/>
@@ -1427,12 +1506,13 @@
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
       <c r="F78" s="11"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="12"/>
       <c r="J78" s="11"/>
       <c r="K78" s="11"/>
       <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
     </row>
     <row r="79">
       <c r="A79" s="11"/>
@@ -1441,12 +1521,13 @@
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
       <c r="F79" s="11"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="12"/>
       <c r="J79" s="11"/>
       <c r="K79" s="11"/>
       <c r="L79" s="11"/>
+      <c r="M79" s="11"/>
     </row>
     <row r="80">
       <c r="A80" s="11"/>
@@ -1455,12 +1536,13 @@
       <c r="D80" s="11"/>
       <c r="E80" s="11"/>
       <c r="F80" s="11"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="12"/>
       <c r="J80" s="11"/>
       <c r="K80" s="11"/>
       <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
     </row>
     <row r="81">
       <c r="A81" s="11"/>
@@ -1469,12 +1551,13 @@
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
       <c r="F81" s="11"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="12"/>
       <c r="J81" s="11"/>
       <c r="K81" s="11"/>
       <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
     </row>
     <row r="82">
       <c r="A82" s="11"/>
@@ -1483,12 +1566,13 @@
       <c r="D82" s="11"/>
       <c r="E82" s="11"/>
       <c r="F82" s="11"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="12"/>
       <c r="J82" s="11"/>
       <c r="K82" s="11"/>
       <c r="L82" s="11"/>
+      <c r="M82" s="11"/>
     </row>
     <row r="83">
       <c r="A83" s="11"/>
@@ -1497,12 +1581,13 @@
       <c r="D83" s="11"/>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="12"/>
       <c r="J83" s="11"/>
       <c r="K83" s="11"/>
       <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
     </row>
     <row r="84">
       <c r="A84" s="11"/>
@@ -1511,12 +1596,13 @@
       <c r="D84" s="11"/>
       <c r="E84" s="11"/>
       <c r="F84" s="11"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="12"/>
       <c r="J84" s="11"/>
       <c r="K84" s="11"/>
       <c r="L84" s="11"/>
+      <c r="M84" s="11"/>
     </row>
     <row r="85">
       <c r="A85" s="11"/>
@@ -1525,12 +1611,13 @@
       <c r="D85" s="11"/>
       <c r="E85" s="11"/>
       <c r="F85" s="11"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="12"/>
       <c r="J85" s="11"/>
       <c r="K85" s="11"/>
       <c r="L85" s="11"/>
+      <c r="M85" s="11"/>
     </row>
     <row r="86">
       <c r="A86" s="11"/>
@@ -1539,12 +1626,13 @@
       <c r="D86" s="11"/>
       <c r="E86" s="11"/>
       <c r="F86" s="11"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="12"/>
       <c r="J86" s="11"/>
       <c r="K86" s="11"/>
       <c r="L86" s="11"/>
+      <c r="M86" s="11"/>
     </row>
     <row r="87">
       <c r="A87" s="11"/>
@@ -1553,12 +1641,13 @@
       <c r="D87" s="11"/>
       <c r="E87" s="11"/>
       <c r="F87" s="11"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="13"/>
-      <c r="I87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="12"/>
       <c r="J87" s="11"/>
       <c r="K87" s="11"/>
       <c r="L87" s="11"/>
+      <c r="M87" s="11"/>
     </row>
     <row r="88">
       <c r="A88" s="11"/>
@@ -1567,12 +1656,13 @@
       <c r="D88" s="11"/>
       <c r="E88" s="11"/>
       <c r="F88" s="11"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="12"/>
       <c r="J88" s="11"/>
       <c r="K88" s="11"/>
       <c r="L88" s="11"/>
+      <c r="M88" s="11"/>
     </row>
     <row r="89">
       <c r="A89" s="11"/>
@@ -1581,12 +1671,13 @@
       <c r="D89" s="11"/>
       <c r="E89" s="11"/>
       <c r="F89" s="11"/>
-      <c r="G89" s="12"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="12"/>
       <c r="J89" s="11"/>
       <c r="K89" s="11"/>
       <c r="L89" s="11"/>
+      <c r="M89" s="11"/>
     </row>
     <row r="90">
       <c r="A90" s="11"/>
@@ -1595,12 +1686,13 @@
       <c r="D90" s="11"/>
       <c r="E90" s="11"/>
       <c r="F90" s="11"/>
-      <c r="G90" s="12"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="12"/>
       <c r="J90" s="11"/>
       <c r="K90" s="11"/>
       <c r="L90" s="11"/>
+      <c r="M90" s="11"/>
     </row>
     <row r="91">
       <c r="A91" s="11"/>
@@ -1609,12 +1701,13 @@
       <c r="D91" s="11"/>
       <c r="E91" s="11"/>
       <c r="F91" s="11"/>
-      <c r="G91" s="12"/>
-      <c r="H91" s="13"/>
-      <c r="I91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="12"/>
       <c r="J91" s="11"/>
       <c r="K91" s="11"/>
       <c r="L91" s="11"/>
+      <c r="M91" s="11"/>
     </row>
     <row r="92">
       <c r="A92" s="11"/>
@@ -1623,12 +1716,13 @@
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
       <c r="F92" s="11"/>
-      <c r="G92" s="12"/>
-      <c r="H92" s="13"/>
-      <c r="I92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="12"/>
       <c r="J92" s="11"/>
       <c r="K92" s="11"/>
       <c r="L92" s="11"/>
+      <c r="M92" s="11"/>
     </row>
     <row r="93">
       <c r="A93" s="11"/>
@@ -1637,12 +1731,13 @@
       <c r="D93" s="11"/>
       <c r="E93" s="11"/>
       <c r="F93" s="11"/>
-      <c r="G93" s="12"/>
-      <c r="H93" s="13"/>
-      <c r="I93" s="11"/>
+      <c r="G93" s="11"/>
+      <c r="H93" s="11"/>
+      <c r="I93" s="12"/>
       <c r="J93" s="11"/>
       <c r="K93" s="11"/>
       <c r="L93" s="11"/>
+      <c r="M93" s="11"/>
     </row>
     <row r="94">
       <c r="A94" s="11"/>
@@ -1651,12 +1746,13 @@
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
       <c r="F94" s="11"/>
-      <c r="G94" s="12"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="11"/>
+      <c r="G94" s="11"/>
+      <c r="H94" s="11"/>
+      <c r="I94" s="12"/>
       <c r="J94" s="11"/>
       <c r="K94" s="11"/>
       <c r="L94" s="11"/>
+      <c r="M94" s="11"/>
     </row>
     <row r="95">
       <c r="A95" s="11"/>
@@ -1665,12 +1761,13 @@
       <c r="D95" s="11"/>
       <c r="E95" s="11"/>
       <c r="F95" s="11"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="13"/>
-      <c r="I95" s="11"/>
+      <c r="G95" s="11"/>
+      <c r="H95" s="11"/>
+      <c r="I95" s="12"/>
       <c r="J95" s="11"/>
       <c r="K95" s="11"/>
       <c r="L95" s="11"/>
+      <c r="M95" s="11"/>
     </row>
     <row r="96">
       <c r="A96" s="11"/>
@@ -1679,12 +1776,13 @@
       <c r="D96" s="11"/>
       <c r="E96" s="11"/>
       <c r="F96" s="11"/>
-      <c r="G96" s="12"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="11"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="12"/>
       <c r="J96" s="11"/>
       <c r="K96" s="11"/>
       <c r="L96" s="11"/>
+      <c r="M96" s="11"/>
     </row>
     <row r="97">
       <c r="A97" s="11"/>
@@ -1693,12 +1791,13 @@
       <c r="D97" s="11"/>
       <c r="E97" s="11"/>
       <c r="F97" s="11"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="13"/>
-      <c r="I97" s="11"/>
+      <c r="G97" s="11"/>
+      <c r="H97" s="11"/>
+      <c r="I97" s="12"/>
       <c r="J97" s="11"/>
       <c r="K97" s="11"/>
       <c r="L97" s="11"/>
+      <c r="M97" s="11"/>
     </row>
     <row r="98">
       <c r="A98" s="11"/>
@@ -1707,12 +1806,13 @@
       <c r="D98" s="11"/>
       <c r="E98" s="11"/>
       <c r="F98" s="11"/>
-      <c r="G98" s="12"/>
-      <c r="H98" s="13"/>
-      <c r="I98" s="11"/>
+      <c r="G98" s="11"/>
+      <c r="H98" s="11"/>
+      <c r="I98" s="12"/>
       <c r="J98" s="11"/>
       <c r="K98" s="11"/>
       <c r="L98" s="11"/>
+      <c r="M98" s="11"/>
     </row>
     <row r="99">
       <c r="A99" s="11"/>
@@ -1721,12 +1821,13 @@
       <c r="D99" s="11"/>
       <c r="E99" s="11"/>
       <c r="F99" s="11"/>
-      <c r="G99" s="12"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="11"/>
+      <c r="G99" s="11"/>
+      <c r="H99" s="11"/>
+      <c r="I99" s="12"/>
       <c r="J99" s="11"/>
       <c r="K99" s="11"/>
       <c r="L99" s="11"/>
+      <c r="M99" s="11"/>
     </row>
     <row r="100">
       <c r="A100" s="11"/>
@@ -1735,12 +1836,13 @@
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
       <c r="F100" s="11"/>
-      <c r="G100" s="12"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="11"/>
+      <c r="G100" s="11"/>
+      <c r="H100" s="11"/>
+      <c r="I100" s="12"/>
       <c r="J100" s="11"/>
       <c r="K100" s="11"/>
       <c r="L100" s="11"/>
+      <c r="M100" s="11"/>
     </row>
     <row r="101">
       <c r="A101" s="11"/>
@@ -1749,12 +1851,13 @@
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
       <c r="F101" s="11"/>
-      <c r="G101" s="12"/>
-      <c r="H101" s="13"/>
-      <c r="I101" s="11"/>
+      <c r="G101" s="11"/>
+      <c r="H101" s="11"/>
+      <c r="I101" s="12"/>
       <c r="J101" s="11"/>
       <c r="K101" s="11"/>
       <c r="L101" s="11"/>
+      <c r="M101" s="11"/>
     </row>
     <row r="102">
       <c r="A102" s="11"/>
@@ -1763,12 +1866,13 @@
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
       <c r="F102" s="11"/>
-      <c r="G102" s="12"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="11"/>
+      <c r="G102" s="11"/>
+      <c r="H102" s="11"/>
+      <c r="I102" s="12"/>
       <c r="J102" s="11"/>
       <c r="K102" s="11"/>
       <c r="L102" s="11"/>
+      <c r="M102" s="11"/>
     </row>
     <row r="103">
       <c r="A103" s="11"/>
@@ -1777,12 +1881,13 @@
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
       <c r="F103" s="11"/>
-      <c r="G103" s="12"/>
-      <c r="H103" s="13"/>
-      <c r="I103" s="11"/>
+      <c r="G103" s="11"/>
+      <c r="H103" s="11"/>
+      <c r="I103" s="12"/>
       <c r="J103" s="11"/>
       <c r="K103" s="11"/>
       <c r="L103" s="11"/>
+      <c r="M103" s="11"/>
     </row>
     <row r="104">
       <c r="A104" s="11"/>
@@ -1791,12 +1896,13 @@
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
       <c r="F104" s="11"/>
-      <c r="G104" s="12"/>
-      <c r="H104" s="13"/>
-      <c r="I104" s="11"/>
+      <c r="G104" s="11"/>
+      <c r="H104" s="11"/>
+      <c r="I104" s="12"/>
       <c r="J104" s="11"/>
       <c r="K104" s="11"/>
       <c r="L104" s="11"/>
+      <c r="M104" s="11"/>
     </row>
     <row r="105">
       <c r="A105" s="11"/>
@@ -1805,12 +1911,13 @@
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
       <c r="F105" s="11"/>
-      <c r="G105" s="12"/>
-      <c r="H105" s="13"/>
-      <c r="I105" s="11"/>
+      <c r="G105" s="11"/>
+      <c r="H105" s="11"/>
+      <c r="I105" s="12"/>
       <c r="J105" s="11"/>
       <c r="K105" s="11"/>
       <c r="L105" s="11"/>
+      <c r="M105" s="11"/>
     </row>
     <row r="106">
       <c r="A106" s="11"/>
@@ -1819,12 +1926,13 @@
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
       <c r="F106" s="11"/>
-      <c r="G106" s="12"/>
-      <c r="H106" s="13"/>
-      <c r="I106" s="11"/>
+      <c r="G106" s="11"/>
+      <c r="H106" s="11"/>
+      <c r="I106" s="12"/>
       <c r="J106" s="11"/>
       <c r="K106" s="11"/>
       <c r="L106" s="11"/>
+      <c r="M106" s="11"/>
     </row>
     <row r="107">
       <c r="A107" s="11"/>
@@ -1833,12 +1941,13 @@
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
       <c r="F107" s="11"/>
-      <c r="G107" s="12"/>
-      <c r="H107" s="13"/>
-      <c r="I107" s="11"/>
+      <c r="G107" s="11"/>
+      <c r="H107" s="11"/>
+      <c r="I107" s="12"/>
       <c r="J107" s="11"/>
       <c r="K107" s="11"/>
       <c r="L107" s="11"/>
+      <c r="M107" s="11"/>
     </row>
     <row r="108">
       <c r="A108" s="11"/>
@@ -1847,12 +1956,13 @@
       <c r="D108" s="11"/>
       <c r="E108" s="11"/>
       <c r="F108" s="11"/>
-      <c r="G108" s="12"/>
-      <c r="H108" s="13"/>
-      <c r="I108" s="11"/>
+      <c r="G108" s="11"/>
+      <c r="H108" s="11"/>
+      <c r="I108" s="12"/>
       <c r="J108" s="11"/>
       <c r="K108" s="11"/>
       <c r="L108" s="11"/>
+      <c r="M108" s="11"/>
     </row>
     <row r="109">
       <c r="A109" s="11"/>
@@ -1861,12 +1971,13 @@
       <c r="D109" s="11"/>
       <c r="E109" s="11"/>
       <c r="F109" s="11"/>
-      <c r="G109" s="12"/>
-      <c r="H109" s="13"/>
-      <c r="I109" s="11"/>
+      <c r="G109" s="11"/>
+      <c r="H109" s="11"/>
+      <c r="I109" s="12"/>
       <c r="J109" s="11"/>
       <c r="K109" s="11"/>
       <c r="L109" s="11"/>
+      <c r="M109" s="11"/>
     </row>
     <row r="110">
       <c r="A110" s="11"/>
@@ -1875,12 +1986,13 @@
       <c r="D110" s="11"/>
       <c r="E110" s="11"/>
       <c r="F110" s="11"/>
-      <c r="G110" s="12"/>
-      <c r="H110" s="13"/>
-      <c r="I110" s="11"/>
+      <c r="G110" s="11"/>
+      <c r="H110" s="11"/>
+      <c r="I110" s="12"/>
       <c r="J110" s="11"/>
       <c r="K110" s="11"/>
       <c r="L110" s="11"/>
+      <c r="M110" s="11"/>
     </row>
     <row r="111">
       <c r="A111" s="11"/>
@@ -1889,12 +2001,13 @@
       <c r="D111" s="11"/>
       <c r="E111" s="11"/>
       <c r="F111" s="11"/>
-      <c r="G111" s="12"/>
-      <c r="H111" s="13"/>
-      <c r="I111" s="11"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="11"/>
+      <c r="I111" s="12"/>
       <c r="J111" s="11"/>
       <c r="K111" s="11"/>
       <c r="L111" s="11"/>
+      <c r="M111" s="11"/>
     </row>
     <row r="112">
       <c r="A112" s="11"/>
@@ -1903,12 +2016,13 @@
       <c r="D112" s="11"/>
       <c r="E112" s="11"/>
       <c r="F112" s="11"/>
-      <c r="G112" s="12"/>
-      <c r="H112" s="13"/>
-      <c r="I112" s="11"/>
+      <c r="G112" s="11"/>
+      <c r="H112" s="11"/>
+      <c r="I112" s="12"/>
       <c r="J112" s="11"/>
       <c r="K112" s="11"/>
       <c r="L112" s="11"/>
+      <c r="M112" s="11"/>
     </row>
     <row r="113">
       <c r="A113" s="11"/>
@@ -1917,12 +2031,13 @@
       <c r="D113" s="11"/>
       <c r="E113" s="11"/>
       <c r="F113" s="11"/>
-      <c r="G113" s="12"/>
-      <c r="H113" s="13"/>
-      <c r="I113" s="11"/>
+      <c r="G113" s="11"/>
+      <c r="H113" s="11"/>
+      <c r="I113" s="12"/>
       <c r="J113" s="11"/>
       <c r="K113" s="11"/>
       <c r="L113" s="11"/>
+      <c r="M113" s="11"/>
     </row>
     <row r="114">
       <c r="A114" s="11"/>
@@ -1931,12 +2046,13 @@
       <c r="D114" s="11"/>
       <c r="E114" s="11"/>
       <c r="F114" s="11"/>
-      <c r="G114" s="12"/>
-      <c r="H114" s="13"/>
-      <c r="I114" s="11"/>
+      <c r="G114" s="11"/>
+      <c r="H114" s="11"/>
+      <c r="I114" s="12"/>
       <c r="J114" s="11"/>
       <c r="K114" s="11"/>
       <c r="L114" s="11"/>
+      <c r="M114" s="11"/>
     </row>
     <row r="115">
       <c r="A115" s="11"/>
@@ -1945,12 +2061,13 @@
       <c r="D115" s="11"/>
       <c r="E115" s="11"/>
       <c r="F115" s="11"/>
-      <c r="G115" s="12"/>
-      <c r="H115" s="13"/>
-      <c r="I115" s="11"/>
+      <c r="G115" s="11"/>
+      <c r="H115" s="11"/>
+      <c r="I115" s="12"/>
       <c r="J115" s="11"/>
       <c r="K115" s="11"/>
       <c r="L115" s="11"/>
+      <c r="M115" s="11"/>
     </row>
     <row r="116">
       <c r="A116" s="11"/>
@@ -1959,12 +2076,13 @@
       <c r="D116" s="11"/>
       <c r="E116" s="11"/>
       <c r="F116" s="11"/>
-      <c r="G116" s="12"/>
-      <c r="H116" s="13"/>
-      <c r="I116" s="11"/>
+      <c r="G116" s="11"/>
+      <c r="H116" s="11"/>
+      <c r="I116" s="12"/>
       <c r="J116" s="11"/>
       <c r="K116" s="11"/>
       <c r="L116" s="11"/>
+      <c r="M116" s="11"/>
     </row>
     <row r="117">
       <c r="A117" s="11"/>
@@ -1973,12 +2091,13 @@
       <c r="D117" s="11"/>
       <c r="E117" s="11"/>
       <c r="F117" s="11"/>
-      <c r="G117" s="12"/>
-      <c r="H117" s="13"/>
-      <c r="I117" s="11"/>
+      <c r="G117" s="11"/>
+      <c r="H117" s="11"/>
+      <c r="I117" s="12"/>
       <c r="J117" s="11"/>
       <c r="K117" s="11"/>
       <c r="L117" s="11"/>
+      <c r="M117" s="11"/>
     </row>
     <row r="118">
       <c r="A118" s="11"/>
@@ -1987,12 +2106,13 @@
       <c r="D118" s="11"/>
       <c r="E118" s="11"/>
       <c r="F118" s="11"/>
-      <c r="G118" s="12"/>
-      <c r="H118" s="13"/>
-      <c r="I118" s="11"/>
+      <c r="G118" s="11"/>
+      <c r="H118" s="11"/>
+      <c r="I118" s="12"/>
       <c r="J118" s="11"/>
       <c r="K118" s="11"/>
       <c r="L118" s="11"/>
+      <c r="M118" s="11"/>
     </row>
     <row r="119">
       <c r="A119" s="11"/>
@@ -2001,12 +2121,13 @@
       <c r="D119" s="11"/>
       <c r="E119" s="11"/>
       <c r="F119" s="11"/>
-      <c r="G119" s="12"/>
-      <c r="H119" s="13"/>
-      <c r="I119" s="11"/>
+      <c r="G119" s="11"/>
+      <c r="H119" s="11"/>
+      <c r="I119" s="12"/>
       <c r="J119" s="11"/>
       <c r="K119" s="11"/>
       <c r="L119" s="11"/>
+      <c r="M119" s="11"/>
     </row>
     <row r="120">
       <c r="A120" s="11"/>
@@ -2015,12 +2136,13 @@
       <c r="D120" s="11"/>
       <c r="E120" s="11"/>
       <c r="F120" s="11"/>
-      <c r="G120" s="12"/>
-      <c r="H120" s="13"/>
-      <c r="I120" s="11"/>
+      <c r="G120" s="11"/>
+      <c r="H120" s="11"/>
+      <c r="I120" s="12"/>
       <c r="J120" s="11"/>
       <c r="K120" s="11"/>
       <c r="L120" s="11"/>
+      <c r="M120" s="11"/>
     </row>
     <row r="121">
       <c r="A121" s="11"/>
@@ -2029,12 +2151,13 @@
       <c r="D121" s="11"/>
       <c r="E121" s="11"/>
       <c r="F121" s="11"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="13"/>
-      <c r="I121" s="11"/>
+      <c r="G121" s="11"/>
+      <c r="H121" s="11"/>
+      <c r="I121" s="12"/>
       <c r="J121" s="11"/>
       <c r="K121" s="11"/>
       <c r="L121" s="11"/>
+      <c r="M121" s="11"/>
     </row>
     <row r="122">
       <c r="A122" s="11"/>
@@ -2043,12 +2166,13 @@
       <c r="D122" s="11"/>
       <c r="E122" s="11"/>
       <c r="F122" s="11"/>
-      <c r="G122" s="12"/>
-      <c r="H122" s="13"/>
-      <c r="I122" s="11"/>
+      <c r="G122" s="11"/>
+      <c r="H122" s="11"/>
+      <c r="I122" s="12"/>
       <c r="J122" s="11"/>
       <c r="K122" s="11"/>
       <c r="L122" s="11"/>
+      <c r="M122" s="11"/>
     </row>
     <row r="123">
       <c r="A123" s="11"/>
@@ -2057,12 +2181,13 @@
       <c r="D123" s="11"/>
       <c r="E123" s="11"/>
       <c r="F123" s="11"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="13"/>
-      <c r="I123" s="11"/>
+      <c r="G123" s="11"/>
+      <c r="H123" s="11"/>
+      <c r="I123" s="12"/>
       <c r="J123" s="11"/>
       <c r="K123" s="11"/>
       <c r="L123" s="11"/>
+      <c r="M123" s="11"/>
     </row>
     <row r="124">
       <c r="A124" s="11"/>
@@ -2071,12 +2196,13 @@
       <c r="D124" s="11"/>
       <c r="E124" s="11"/>
       <c r="F124" s="11"/>
-      <c r="G124" s="12"/>
-      <c r="H124" s="13"/>
-      <c r="I124" s="11"/>
+      <c r="G124" s="11"/>
+      <c r="H124" s="11"/>
+      <c r="I124" s="12"/>
       <c r="J124" s="11"/>
       <c r="K124" s="11"/>
       <c r="L124" s="11"/>
+      <c r="M124" s="11"/>
     </row>
     <row r="125">
       <c r="A125" s="11"/>
@@ -2085,12 +2211,13 @@
       <c r="D125" s="11"/>
       <c r="E125" s="11"/>
       <c r="F125" s="11"/>
-      <c r="G125" s="12"/>
-      <c r="H125" s="13"/>
-      <c r="I125" s="11"/>
+      <c r="G125" s="11"/>
+      <c r="H125" s="11"/>
+      <c r="I125" s="12"/>
       <c r="J125" s="11"/>
       <c r="K125" s="11"/>
       <c r="L125" s="11"/>
+      <c r="M125" s="11"/>
     </row>
     <row r="126">
       <c r="A126" s="11"/>
@@ -2099,12 +2226,13 @@
       <c r="D126" s="11"/>
       <c r="E126" s="11"/>
       <c r="F126" s="11"/>
-      <c r="G126" s="12"/>
-      <c r="H126" s="13"/>
-      <c r="I126" s="11"/>
+      <c r="G126" s="11"/>
+      <c r="H126" s="11"/>
+      <c r="I126" s="12"/>
       <c r="J126" s="11"/>
       <c r="K126" s="11"/>
       <c r="L126" s="11"/>
+      <c r="M126" s="11"/>
     </row>
     <row r="127">
       <c r="A127" s="11"/>
@@ -2113,12 +2241,13 @@
       <c r="D127" s="11"/>
       <c r="E127" s="11"/>
       <c r="F127" s="11"/>
-      <c r="G127" s="12"/>
-      <c r="H127" s="13"/>
-      <c r="I127" s="11"/>
+      <c r="G127" s="11"/>
+      <c r="H127" s="11"/>
+      <c r="I127" s="12"/>
       <c r="J127" s="11"/>
       <c r="K127" s="11"/>
       <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
     </row>
     <row r="128">
       <c r="A128" s="11"/>
@@ -2127,12 +2256,13 @@
       <c r="D128" s="11"/>
       <c r="E128" s="11"/>
       <c r="F128" s="11"/>
-      <c r="G128" s="12"/>
-      <c r="H128" s="13"/>
-      <c r="I128" s="11"/>
+      <c r="G128" s="11"/>
+      <c r="H128" s="11"/>
+      <c r="I128" s="12"/>
       <c r="J128" s="11"/>
       <c r="K128" s="11"/>
       <c r="L128" s="11"/>
+      <c r="M128" s="11"/>
     </row>
     <row r="129">
       <c r="A129" s="11"/>
@@ -2141,12 +2271,13 @@
       <c r="D129" s="11"/>
       <c r="E129" s="11"/>
       <c r="F129" s="11"/>
-      <c r="G129" s="12"/>
-      <c r="H129" s="13"/>
-      <c r="I129" s="11"/>
+      <c r="G129" s="11"/>
+      <c r="H129" s="11"/>
+      <c r="I129" s="12"/>
       <c r="J129" s="11"/>
       <c r="K129" s="11"/>
       <c r="L129" s="11"/>
+      <c r="M129" s="11"/>
     </row>
     <row r="130">
       <c r="A130" s="11"/>
@@ -2155,12 +2286,13 @@
       <c r="D130" s="11"/>
       <c r="E130" s="11"/>
       <c r="F130" s="11"/>
-      <c r="G130" s="12"/>
-      <c r="H130" s="13"/>
-      <c r="I130" s="11"/>
+      <c r="G130" s="11"/>
+      <c r="H130" s="11"/>
+      <c r="I130" s="12"/>
       <c r="J130" s="11"/>
       <c r="K130" s="11"/>
       <c r="L130" s="11"/>
+      <c r="M130" s="11"/>
     </row>
     <row r="131">
       <c r="A131" s="11"/>
@@ -2169,12 +2301,13 @@
       <c r="D131" s="11"/>
       <c r="E131" s="11"/>
       <c r="F131" s="11"/>
-      <c r="G131" s="12"/>
-      <c r="H131" s="13"/>
-      <c r="I131" s="11"/>
+      <c r="G131" s="11"/>
+      <c r="H131" s="11"/>
+      <c r="I131" s="12"/>
       <c r="J131" s="11"/>
       <c r="K131" s="11"/>
       <c r="L131" s="11"/>
+      <c r="M131" s="11"/>
     </row>
     <row r="132">
       <c r="A132" s="11"/>
@@ -2183,12 +2316,13 @@
       <c r="D132" s="11"/>
       <c r="E132" s="11"/>
       <c r="F132" s="11"/>
-      <c r="G132" s="12"/>
-      <c r="H132" s="13"/>
-      <c r="I132" s="11"/>
+      <c r="G132" s="11"/>
+      <c r="H132" s="11"/>
+      <c r="I132" s="12"/>
       <c r="J132" s="11"/>
       <c r="K132" s="11"/>
       <c r="L132" s="11"/>
+      <c r="M132" s="11"/>
     </row>
     <row r="133">
       <c r="A133" s="11"/>
@@ -2197,12 +2331,13 @@
       <c r="D133" s="11"/>
       <c r="E133" s="11"/>
       <c r="F133" s="11"/>
-      <c r="G133" s="12"/>
-      <c r="H133" s="13"/>
-      <c r="I133" s="11"/>
+      <c r="G133" s="11"/>
+      <c r="H133" s="11"/>
+      <c r="I133" s="12"/>
       <c r="J133" s="11"/>
       <c r="K133" s="11"/>
       <c r="L133" s="11"/>
+      <c r="M133" s="11"/>
     </row>
     <row r="134">
       <c r="A134" s="11"/>
@@ -2211,12 +2346,13 @@
       <c r="D134" s="11"/>
       <c r="E134" s="11"/>
       <c r="F134" s="11"/>
-      <c r="G134" s="12"/>
-      <c r="H134" s="13"/>
-      <c r="I134" s="11"/>
+      <c r="G134" s="11"/>
+      <c r="H134" s="11"/>
+      <c r="I134" s="12"/>
       <c r="J134" s="11"/>
       <c r="K134" s="11"/>
       <c r="L134" s="11"/>
+      <c r="M134" s="11"/>
     </row>
     <row r="135">
       <c r="A135" s="11"/>
@@ -2225,12 +2361,13 @@
       <c r="D135" s="11"/>
       <c r="E135" s="11"/>
       <c r="F135" s="11"/>
-      <c r="G135" s="12"/>
-      <c r="H135" s="13"/>
-      <c r="I135" s="11"/>
+      <c r="G135" s="11"/>
+      <c r="H135" s="11"/>
+      <c r="I135" s="12"/>
       <c r="J135" s="11"/>
       <c r="K135" s="11"/>
       <c r="L135" s="11"/>
+      <c r="M135" s="11"/>
     </row>
     <row r="136">
       <c r="A136" s="11"/>
@@ -2239,12 +2376,13 @@
       <c r="D136" s="11"/>
       <c r="E136" s="11"/>
       <c r="F136" s="11"/>
-      <c r="G136" s="12"/>
-      <c r="H136" s="13"/>
-      <c r="I136" s="11"/>
+      <c r="G136" s="11"/>
+      <c r="H136" s="11"/>
+      <c r="I136" s="12"/>
       <c r="J136" s="11"/>
       <c r="K136" s="11"/>
       <c r="L136" s="11"/>
+      <c r="M136" s="11"/>
     </row>
     <row r="137">
       <c r="A137" s="11"/>
@@ -2253,12 +2391,13 @@
       <c r="D137" s="11"/>
       <c r="E137" s="11"/>
       <c r="F137" s="11"/>
-      <c r="G137" s="12"/>
-      <c r="H137" s="13"/>
-      <c r="I137" s="11"/>
+      <c r="G137" s="11"/>
+      <c r="H137" s="11"/>
+      <c r="I137" s="12"/>
       <c r="J137" s="11"/>
       <c r="K137" s="11"/>
       <c r="L137" s="11"/>
+      <c r="M137" s="11"/>
     </row>
     <row r="138">
       <c r="A138" s="11"/>
@@ -2267,12 +2406,13 @@
       <c r="D138" s="11"/>
       <c r="E138" s="11"/>
       <c r="F138" s="11"/>
-      <c r="G138" s="12"/>
-      <c r="H138" s="13"/>
-      <c r="I138" s="11"/>
+      <c r="G138" s="11"/>
+      <c r="H138" s="11"/>
+      <c r="I138" s="12"/>
       <c r="J138" s="11"/>
       <c r="K138" s="11"/>
       <c r="L138" s="11"/>
+      <c r="M138" s="11"/>
     </row>
     <row r="139">
       <c r="A139" s="11"/>
@@ -2281,12 +2421,13 @@
       <c r="D139" s="11"/>
       <c r="E139" s="11"/>
       <c r="F139" s="11"/>
-      <c r="G139" s="12"/>
-      <c r="H139" s="13"/>
-      <c r="I139" s="11"/>
+      <c r="G139" s="11"/>
+      <c r="H139" s="11"/>
+      <c r="I139" s="12"/>
       <c r="J139" s="11"/>
       <c r="K139" s="11"/>
       <c r="L139" s="11"/>
+      <c r="M139" s="11"/>
     </row>
     <row r="140">
       <c r="A140" s="11"/>
@@ -2295,12 +2436,13 @@
       <c r="D140" s="11"/>
       <c r="E140" s="11"/>
       <c r="F140" s="11"/>
-      <c r="G140" s="12"/>
-      <c r="H140" s="13"/>
-      <c r="I140" s="11"/>
+      <c r="G140" s="11"/>
+      <c r="H140" s="11"/>
+      <c r="I140" s="12"/>
       <c r="J140" s="11"/>
       <c r="K140" s="11"/>
       <c r="L140" s="11"/>
+      <c r="M140" s="11"/>
     </row>
     <row r="141">
       <c r="A141" s="11"/>
@@ -2309,12 +2451,13 @@
       <c r="D141" s="11"/>
       <c r="E141" s="11"/>
       <c r="F141" s="11"/>
-      <c r="G141" s="12"/>
-      <c r="H141" s="13"/>
-      <c r="I141" s="11"/>
+      <c r="G141" s="11"/>
+      <c r="H141" s="11"/>
+      <c r="I141" s="12"/>
       <c r="J141" s="11"/>
       <c r="K141" s="11"/>
       <c r="L141" s="11"/>
+      <c r="M141" s="11"/>
     </row>
     <row r="142">
       <c r="A142" s="11"/>
@@ -2323,12 +2466,13 @@
       <c r="D142" s="11"/>
       <c r="E142" s="11"/>
       <c r="F142" s="11"/>
-      <c r="G142" s="12"/>
-      <c r="H142" s="13"/>
-      <c r="I142" s="11"/>
+      <c r="G142" s="11"/>
+      <c r="H142" s="11"/>
+      <c r="I142" s="12"/>
       <c r="J142" s="11"/>
       <c r="K142" s="11"/>
       <c r="L142" s="11"/>
+      <c r="M142" s="11"/>
     </row>
     <row r="143">
       <c r="A143" s="11"/>
@@ -2337,12 +2481,13 @@
       <c r="D143" s="11"/>
       <c r="E143" s="11"/>
       <c r="F143" s="11"/>
-      <c r="G143" s="12"/>
-      <c r="H143" s="13"/>
-      <c r="I143" s="11"/>
+      <c r="G143" s="11"/>
+      <c r="H143" s="11"/>
+      <c r="I143" s="12"/>
       <c r="J143" s="11"/>
       <c r="K143" s="11"/>
       <c r="L143" s="11"/>
+      <c r="M143" s="11"/>
     </row>
     <row r="144">
       <c r="A144" s="11"/>
@@ -2351,12 +2496,13 @@
       <c r="D144" s="11"/>
       <c r="E144" s="11"/>
       <c r="F144" s="11"/>
-      <c r="G144" s="12"/>
-      <c r="H144" s="13"/>
-      <c r="I144" s="11"/>
+      <c r="G144" s="11"/>
+      <c r="H144" s="11"/>
+      <c r="I144" s="12"/>
       <c r="J144" s="11"/>
       <c r="K144" s="11"/>
       <c r="L144" s="11"/>
+      <c r="M144" s="11"/>
     </row>
     <row r="145">
       <c r="A145" s="11"/>
@@ -2365,12 +2511,13 @@
       <c r="D145" s="11"/>
       <c r="E145" s="11"/>
       <c r="F145" s="11"/>
-      <c r="G145" s="12"/>
-      <c r="H145" s="13"/>
-      <c r="I145" s="11"/>
+      <c r="G145" s="11"/>
+      <c r="H145" s="11"/>
+      <c r="I145" s="12"/>
       <c r="J145" s="11"/>
       <c r="K145" s="11"/>
       <c r="L145" s="11"/>
+      <c r="M145" s="11"/>
     </row>
     <row r="146">
       <c r="A146" s="11"/>
@@ -2379,12 +2526,13 @@
       <c r="D146" s="11"/>
       <c r="E146" s="11"/>
       <c r="F146" s="11"/>
-      <c r="G146" s="12"/>
-      <c r="H146" s="13"/>
-      <c r="I146" s="11"/>
+      <c r="G146" s="11"/>
+      <c r="H146" s="11"/>
+      <c r="I146" s="12"/>
       <c r="J146" s="11"/>
       <c r="K146" s="11"/>
       <c r="L146" s="11"/>
+      <c r="M146" s="11"/>
     </row>
     <row r="147">
       <c r="A147" s="11"/>
@@ -2393,12 +2541,13 @@
       <c r="D147" s="11"/>
       <c r="E147" s="11"/>
       <c r="F147" s="11"/>
-      <c r="G147" s="12"/>
-      <c r="H147" s="13"/>
-      <c r="I147" s="11"/>
+      <c r="G147" s="11"/>
+      <c r="H147" s="11"/>
+      <c r="I147" s="12"/>
       <c r="J147" s="11"/>
       <c r="K147" s="11"/>
       <c r="L147" s="11"/>
+      <c r="M147" s="11"/>
     </row>
     <row r="148">
       <c r="A148" s="11"/>
@@ -2407,12 +2556,13 @@
       <c r="D148" s="11"/>
       <c r="E148" s="11"/>
       <c r="F148" s="11"/>
-      <c r="G148" s="12"/>
-      <c r="H148" s="13"/>
-      <c r="I148" s="11"/>
+      <c r="G148" s="11"/>
+      <c r="H148" s="11"/>
+      <c r="I148" s="12"/>
       <c r="J148" s="11"/>
       <c r="K148" s="11"/>
       <c r="L148" s="11"/>
+      <c r="M148" s="11"/>
     </row>
     <row r="149">
       <c r="A149" s="11"/>
@@ -2421,12 +2571,13 @@
       <c r="D149" s="11"/>
       <c r="E149" s="11"/>
       <c r="F149" s="11"/>
-      <c r="G149" s="12"/>
-      <c r="H149" s="13"/>
-      <c r="I149" s="11"/>
+      <c r="G149" s="11"/>
+      <c r="H149" s="11"/>
+      <c r="I149" s="12"/>
       <c r="J149" s="11"/>
       <c r="K149" s="11"/>
       <c r="L149" s="11"/>
+      <c r="M149" s="11"/>
     </row>
     <row r="150">
       <c r="A150" s="11"/>
@@ -2435,12 +2586,13 @@
       <c r="D150" s="11"/>
       <c r="E150" s="11"/>
       <c r="F150" s="11"/>
-      <c r="G150" s="12"/>
-      <c r="H150" s="13"/>
-      <c r="I150" s="11"/>
+      <c r="G150" s="11"/>
+      <c r="H150" s="11"/>
+      <c r="I150" s="12"/>
       <c r="J150" s="11"/>
       <c r="K150" s="11"/>
       <c r="L150" s="11"/>
+      <c r="M150" s="11"/>
     </row>
     <row r="151">
       <c r="A151" s="11"/>
@@ -2449,12 +2601,13 @@
       <c r="D151" s="11"/>
       <c r="E151" s="11"/>
       <c r="F151" s="11"/>
-      <c r="G151" s="12"/>
-      <c r="H151" s="13"/>
-      <c r="I151" s="11"/>
+      <c r="G151" s="11"/>
+      <c r="H151" s="11"/>
+      <c r="I151" s="12"/>
       <c r="J151" s="11"/>
       <c r="K151" s="11"/>
       <c r="L151" s="11"/>
+      <c r="M151" s="11"/>
     </row>
     <row r="152">
       <c r="A152" s="11"/>
@@ -2463,12 +2616,13 @@
       <c r="D152" s="11"/>
       <c r="E152" s="11"/>
       <c r="F152" s="11"/>
-      <c r="G152" s="12"/>
-      <c r="H152" s="13"/>
-      <c r="I152" s="11"/>
+      <c r="G152" s="11"/>
+      <c r="H152" s="11"/>
+      <c r="I152" s="12"/>
       <c r="J152" s="11"/>
       <c r="K152" s="11"/>
       <c r="L152" s="11"/>
+      <c r="M152" s="11"/>
     </row>
     <row r="153">
       <c r="A153" s="11"/>
@@ -2477,12 +2631,13 @@
       <c r="D153" s="11"/>
       <c r="E153" s="11"/>
       <c r="F153" s="11"/>
-      <c r="G153" s="12"/>
-      <c r="H153" s="13"/>
-      <c r="I153" s="11"/>
+      <c r="G153" s="11"/>
+      <c r="H153" s="11"/>
+      <c r="I153" s="12"/>
       <c r="J153" s="11"/>
       <c r="K153" s="11"/>
       <c r="L153" s="11"/>
+      <c r="M153" s="11"/>
     </row>
     <row r="154">
       <c r="A154" s="11"/>
@@ -2491,12 +2646,13 @@
       <c r="D154" s="11"/>
       <c r="E154" s="11"/>
       <c r="F154" s="11"/>
-      <c r="G154" s="12"/>
-      <c r="H154" s="13"/>
-      <c r="I154" s="11"/>
+      <c r="G154" s="11"/>
+      <c r="H154" s="11"/>
+      <c r="I154" s="12"/>
       <c r="J154" s="11"/>
       <c r="K154" s="11"/>
       <c r="L154" s="11"/>
+      <c r="M154" s="11"/>
     </row>
     <row r="155">
       <c r="A155" s="11"/>
@@ -2505,12 +2661,13 @@
       <c r="D155" s="11"/>
       <c r="E155" s="11"/>
       <c r="F155" s="11"/>
-      <c r="G155" s="12"/>
-      <c r="H155" s="13"/>
-      <c r="I155" s="11"/>
+      <c r="G155" s="11"/>
+      <c r="H155" s="11"/>
+      <c r="I155" s="12"/>
       <c r="J155" s="11"/>
       <c r="K155" s="11"/>
       <c r="L155" s="11"/>
+      <c r="M155" s="11"/>
     </row>
     <row r="156">
       <c r="A156" s="11"/>
@@ -2519,12 +2676,13 @@
       <c r="D156" s="11"/>
       <c r="E156" s="11"/>
       <c r="F156" s="11"/>
-      <c r="G156" s="12"/>
-      <c r="H156" s="13"/>
-      <c r="I156" s="11"/>
+      <c r="G156" s="11"/>
+      <c r="H156" s="11"/>
+      <c r="I156" s="12"/>
       <c r="J156" s="11"/>
       <c r="K156" s="11"/>
       <c r="L156" s="11"/>
+      <c r="M156" s="11"/>
     </row>
     <row r="157">
       <c r="A157" s="11"/>
@@ -2533,12 +2691,13 @@
       <c r="D157" s="11"/>
       <c r="E157" s="11"/>
       <c r="F157" s="11"/>
-      <c r="G157" s="12"/>
-      <c r="H157" s="13"/>
-      <c r="I157" s="11"/>
+      <c r="G157" s="11"/>
+      <c r="H157" s="11"/>
+      <c r="I157" s="12"/>
       <c r="J157" s="11"/>
       <c r="K157" s="11"/>
       <c r="L157" s="11"/>
+      <c r="M157" s="11"/>
     </row>
     <row r="158">
       <c r="A158" s="11"/>
@@ -2547,12 +2706,13 @@
       <c r="D158" s="11"/>
       <c r="E158" s="11"/>
       <c r="F158" s="11"/>
-      <c r="G158" s="12"/>
-      <c r="H158" s="13"/>
-      <c r="I158" s="11"/>
+      <c r="G158" s="11"/>
+      <c r="H158" s="11"/>
+      <c r="I158" s="12"/>
       <c r="J158" s="11"/>
       <c r="K158" s="11"/>
       <c r="L158" s="11"/>
+      <c r="M158" s="11"/>
     </row>
     <row r="159">
       <c r="A159" s="11"/>
@@ -2561,12 +2721,13 @@
       <c r="D159" s="11"/>
       <c r="E159" s="11"/>
       <c r="F159" s="11"/>
-      <c r="G159" s="12"/>
-      <c r="H159" s="13"/>
-      <c r="I159" s="11"/>
+      <c r="G159" s="11"/>
+      <c r="H159" s="11"/>
+      <c r="I159" s="12"/>
       <c r="J159" s="11"/>
       <c r="K159" s="11"/>
       <c r="L159" s="11"/>
+      <c r="M159" s="11"/>
     </row>
     <row r="160">
       <c r="A160" s="11"/>
@@ -2575,12 +2736,13 @@
       <c r="D160" s="11"/>
       <c r="E160" s="11"/>
       <c r="F160" s="11"/>
-      <c r="G160" s="12"/>
-      <c r="H160" s="13"/>
-      <c r="I160" s="11"/>
+      <c r="G160" s="11"/>
+      <c r="H160" s="11"/>
+      <c r="I160" s="12"/>
       <c r="J160" s="11"/>
       <c r="K160" s="11"/>
       <c r="L160" s="11"/>
+      <c r="M160" s="11"/>
     </row>
     <row r="161">
       <c r="A161" s="11"/>
@@ -2589,12 +2751,13 @@
       <c r="D161" s="11"/>
       <c r="E161" s="11"/>
       <c r="F161" s="11"/>
-      <c r="G161" s="12"/>
-      <c r="H161" s="13"/>
-      <c r="I161" s="11"/>
+      <c r="G161" s="11"/>
+      <c r="H161" s="11"/>
+      <c r="I161" s="12"/>
       <c r="J161" s="11"/>
       <c r="K161" s="11"/>
       <c r="L161" s="11"/>
+      <c r="M161" s="11"/>
     </row>
     <row r="162">
       <c r="A162" s="11"/>
@@ -2603,12 +2766,13 @@
       <c r="D162" s="11"/>
       <c r="E162" s="11"/>
       <c r="F162" s="11"/>
-      <c r="G162" s="12"/>
-      <c r="H162" s="13"/>
-      <c r="I162" s="11"/>
+      <c r="G162" s="11"/>
+      <c r="H162" s="11"/>
+      <c r="I162" s="12"/>
       <c r="J162" s="11"/>
       <c r="K162" s="11"/>
       <c r="L162" s="11"/>
+      <c r="M162" s="11"/>
     </row>
     <row r="163">
       <c r="A163" s="11"/>
@@ -2617,12 +2781,13 @@
       <c r="D163" s="11"/>
       <c r="E163" s="11"/>
       <c r="F163" s="11"/>
-      <c r="G163" s="12"/>
-      <c r="H163" s="13"/>
-      <c r="I163" s="11"/>
+      <c r="G163" s="11"/>
+      <c r="H163" s="11"/>
+      <c r="I163" s="12"/>
       <c r="J163" s="11"/>
       <c r="K163" s="11"/>
       <c r="L163" s="11"/>
+      <c r="M163" s="11"/>
     </row>
     <row r="164">
       <c r="A164" s="11"/>
@@ -2631,12 +2796,13 @@
       <c r="D164" s="11"/>
       <c r="E164" s="11"/>
       <c r="F164" s="11"/>
-      <c r="G164" s="12"/>
-      <c r="H164" s="13"/>
-      <c r="I164" s="11"/>
+      <c r="G164" s="11"/>
+      <c r="H164" s="11"/>
+      <c r="I164" s="12"/>
       <c r="J164" s="11"/>
       <c r="K164" s="11"/>
       <c r="L164" s="11"/>
+      <c r="M164" s="11"/>
     </row>
     <row r="165">
       <c r="A165" s="11"/>
@@ -2645,12 +2811,13 @@
       <c r="D165" s="11"/>
       <c r="E165" s="11"/>
       <c r="F165" s="11"/>
-      <c r="G165" s="12"/>
-      <c r="H165" s="13"/>
-      <c r="I165" s="11"/>
+      <c r="G165" s="11"/>
+      <c r="H165" s="11"/>
+      <c r="I165" s="12"/>
       <c r="J165" s="11"/>
       <c r="K165" s="11"/>
       <c r="L165" s="11"/>
+      <c r="M165" s="11"/>
     </row>
     <row r="166">
       <c r="A166" s="11"/>
@@ -2659,12 +2826,13 @@
       <c r="D166" s="11"/>
       <c r="E166" s="11"/>
       <c r="F166" s="11"/>
-      <c r="G166" s="12"/>
-      <c r="H166" s="13"/>
-      <c r="I166" s="11"/>
+      <c r="G166" s="11"/>
+      <c r="H166" s="11"/>
+      <c r="I166" s="12"/>
       <c r="J166" s="11"/>
       <c r="K166" s="11"/>
       <c r="L166" s="11"/>
+      <c r="M166" s="11"/>
     </row>
     <row r="167">
       <c r="A167" s="11"/>
@@ -2673,12 +2841,13 @@
       <c r="D167" s="11"/>
       <c r="E167" s="11"/>
       <c r="F167" s="11"/>
-      <c r="G167" s="12"/>
-      <c r="H167" s="13"/>
-      <c r="I167" s="11"/>
+      <c r="G167" s="11"/>
+      <c r="H167" s="11"/>
+      <c r="I167" s="12"/>
       <c r="J167" s="11"/>
       <c r="K167" s="11"/>
       <c r="L167" s="11"/>
+      <c r="M167" s="11"/>
     </row>
     <row r="168">
       <c r="A168" s="11"/>
@@ -2687,12 +2856,13 @@
       <c r="D168" s="11"/>
       <c r="E168" s="11"/>
       <c r="F168" s="11"/>
-      <c r="G168" s="12"/>
-      <c r="H168" s="13"/>
-      <c r="I168" s="11"/>
+      <c r="G168" s="11"/>
+      <c r="H168" s="11"/>
+      <c r="I168" s="12"/>
       <c r="J168" s="11"/>
       <c r="K168" s="11"/>
       <c r="L168" s="11"/>
+      <c r="M168" s="11"/>
     </row>
     <row r="169">
       <c r="A169" s="11"/>
@@ -2701,12 +2871,13 @@
       <c r="D169" s="11"/>
       <c r="E169" s="11"/>
       <c r="F169" s="11"/>
-      <c r="G169" s="12"/>
-      <c r="H169" s="13"/>
-      <c r="I169" s="11"/>
+      <c r="G169" s="11"/>
+      <c r="H169" s="11"/>
+      <c r="I169" s="12"/>
       <c r="J169" s="11"/>
       <c r="K169" s="11"/>
       <c r="L169" s="11"/>
+      <c r="M169" s="11"/>
     </row>
     <row r="170">
       <c r="A170" s="11"/>
@@ -2715,12 +2886,13 @@
       <c r="D170" s="11"/>
       <c r="E170" s="11"/>
       <c r="F170" s="11"/>
-      <c r="G170" s="12"/>
-      <c r="H170" s="13"/>
-      <c r="I170" s="11"/>
+      <c r="G170" s="11"/>
+      <c r="H170" s="11"/>
+      <c r="I170" s="12"/>
       <c r="J170" s="11"/>
       <c r="K170" s="11"/>
       <c r="L170" s="11"/>
+      <c r="M170" s="11"/>
     </row>
     <row r="171">
       <c r="A171" s="11"/>
@@ -2729,12 +2901,13 @@
       <c r="D171" s="11"/>
       <c r="E171" s="11"/>
       <c r="F171" s="11"/>
-      <c r="G171" s="12"/>
-      <c r="H171" s="13"/>
-      <c r="I171" s="11"/>
+      <c r="G171" s="11"/>
+      <c r="H171" s="11"/>
+      <c r="I171" s="12"/>
       <c r="J171" s="11"/>
       <c r="K171" s="11"/>
       <c r="L171" s="11"/>
+      <c r="M171" s="11"/>
     </row>
     <row r="172">
       <c r="A172" s="11"/>
@@ -2743,12 +2916,13 @@
       <c r="D172" s="11"/>
       <c r="E172" s="11"/>
       <c r="F172" s="11"/>
-      <c r="G172" s="12"/>
-      <c r="H172" s="13"/>
-      <c r="I172" s="11"/>
+      <c r="G172" s="11"/>
+      <c r="H172" s="11"/>
+      <c r="I172" s="12"/>
       <c r="J172" s="11"/>
       <c r="K172" s="11"/>
       <c r="L172" s="11"/>
+      <c r="M172" s="11"/>
     </row>
     <row r="173">
       <c r="A173" s="11"/>
@@ -2757,12 +2931,13 @@
       <c r="D173" s="11"/>
       <c r="E173" s="11"/>
       <c r="F173" s="11"/>
-      <c r="G173" s="12"/>
-      <c r="H173" s="13"/>
-      <c r="I173" s="11"/>
+      <c r="G173" s="11"/>
+      <c r="H173" s="11"/>
+      <c r="I173" s="12"/>
       <c r="J173" s="11"/>
       <c r="K173" s="11"/>
       <c r="L173" s="11"/>
+      <c r="M173" s="11"/>
     </row>
     <row r="174">
       <c r="A174" s="11"/>
@@ -2771,12 +2946,13 @@
       <c r="D174" s="11"/>
       <c r="E174" s="11"/>
       <c r="F174" s="11"/>
-      <c r="G174" s="12"/>
-      <c r="H174" s="13"/>
-      <c r="I174" s="11"/>
+      <c r="G174" s="11"/>
+      <c r="H174" s="11"/>
+      <c r="I174" s="12"/>
       <c r="J174" s="11"/>
       <c r="K174" s="11"/>
       <c r="L174" s="11"/>
+      <c r="M174" s="11"/>
     </row>
     <row r="175">
       <c r="A175" s="11"/>
@@ -2785,12 +2961,13 @@
       <c r="D175" s="11"/>
       <c r="E175" s="11"/>
       <c r="F175" s="11"/>
-      <c r="G175" s="12"/>
-      <c r="H175" s="13"/>
-      <c r="I175" s="11"/>
+      <c r="G175" s="11"/>
+      <c r="H175" s="11"/>
+      <c r="I175" s="12"/>
       <c r="J175" s="11"/>
       <c r="K175" s="11"/>
       <c r="L175" s="11"/>
+      <c r="M175" s="11"/>
     </row>
     <row r="176">
       <c r="A176" s="11"/>
@@ -2799,12 +2976,13 @@
       <c r="D176" s="11"/>
       <c r="E176" s="11"/>
       <c r="F176" s="11"/>
-      <c r="G176" s="12"/>
-      <c r="H176" s="13"/>
-      <c r="I176" s="11"/>
+      <c r="G176" s="11"/>
+      <c r="H176" s="11"/>
+      <c r="I176" s="12"/>
       <c r="J176" s="11"/>
       <c r="K176" s="11"/>
       <c r="L176" s="11"/>
+      <c r="M176" s="11"/>
     </row>
     <row r="177">
       <c r="A177" s="11"/>
@@ -2813,12 +2991,13 @@
       <c r="D177" s="11"/>
       <c r="E177" s="11"/>
       <c r="F177" s="11"/>
-      <c r="G177" s="12"/>
-      <c r="H177" s="13"/>
-      <c r="I177" s="11"/>
+      <c r="G177" s="11"/>
+      <c r="H177" s="11"/>
+      <c r="I177" s="12"/>
       <c r="J177" s="11"/>
       <c r="K177" s="11"/>
       <c r="L177" s="11"/>
+      <c r="M177" s="11"/>
     </row>
     <row r="178">
       <c r="A178" s="11"/>
@@ -2827,12 +3006,13 @@
       <c r="D178" s="11"/>
       <c r="E178" s="11"/>
       <c r="F178" s="11"/>
-      <c r="G178" s="12"/>
-      <c r="H178" s="13"/>
-      <c r="I178" s="11"/>
+      <c r="G178" s="11"/>
+      <c r="H178" s="11"/>
+      <c r="I178" s="12"/>
       <c r="J178" s="11"/>
       <c r="K178" s="11"/>
       <c r="L178" s="11"/>
+      <c r="M178" s="11"/>
     </row>
     <row r="179">
       <c r="A179" s="11"/>
@@ -2841,12 +3021,13 @@
       <c r="D179" s="11"/>
       <c r="E179" s="11"/>
       <c r="F179" s="11"/>
-      <c r="G179" s="12"/>
-      <c r="H179" s="13"/>
-      <c r="I179" s="11"/>
+      <c r="G179" s="11"/>
+      <c r="H179" s="11"/>
+      <c r="I179" s="12"/>
       <c r="J179" s="11"/>
       <c r="K179" s="11"/>
       <c r="L179" s="11"/>
+      <c r="M179" s="11"/>
     </row>
     <row r="180">
       <c r="A180" s="11"/>
@@ -2855,12 +3036,13 @@
       <c r="D180" s="11"/>
       <c r="E180" s="11"/>
       <c r="F180" s="11"/>
-      <c r="G180" s="12"/>
-      <c r="H180" s="13"/>
-      <c r="I180" s="11"/>
+      <c r="G180" s="11"/>
+      <c r="H180" s="11"/>
+      <c r="I180" s="12"/>
       <c r="J180" s="11"/>
       <c r="K180" s="11"/>
       <c r="L180" s="11"/>
+      <c r="M180" s="11"/>
     </row>
     <row r="181">
       <c r="A181" s="11"/>
@@ -2869,12 +3051,13 @@
       <c r="D181" s="11"/>
       <c r="E181" s="11"/>
       <c r="F181" s="11"/>
-      <c r="G181" s="12"/>
-      <c r="H181" s="13"/>
-      <c r="I181" s="11"/>
+      <c r="G181" s="11"/>
+      <c r="H181" s="11"/>
+      <c r="I181" s="12"/>
       <c r="J181" s="11"/>
       <c r="K181" s="11"/>
       <c r="L181" s="11"/>
+      <c r="M181" s="11"/>
     </row>
     <row r="182">
       <c r="A182" s="11"/>
@@ -2883,12 +3066,13 @@
       <c r="D182" s="11"/>
       <c r="E182" s="11"/>
       <c r="F182" s="11"/>
-      <c r="G182" s="12"/>
-      <c r="H182" s="13"/>
-      <c r="I182" s="11"/>
+      <c r="G182" s="11"/>
+      <c r="H182" s="11"/>
+      <c r="I182" s="12"/>
       <c r="J182" s="11"/>
       <c r="K182" s="11"/>
       <c r="L182" s="11"/>
+      <c r="M182" s="11"/>
     </row>
     <row r="183">
       <c r="A183" s="11"/>
@@ -2897,12 +3081,13 @@
       <c r="D183" s="11"/>
       <c r="E183" s="11"/>
       <c r="F183" s="11"/>
-      <c r="G183" s="12"/>
-      <c r="H183" s="13"/>
-      <c r="I183" s="11"/>
+      <c r="G183" s="11"/>
+      <c r="H183" s="11"/>
+      <c r="I183" s="12"/>
       <c r="J183" s="11"/>
       <c r="K183" s="11"/>
       <c r="L183" s="11"/>
+      <c r="M183" s="11"/>
     </row>
     <row r="184">
       <c r="A184" s="11"/>
@@ -2911,12 +3096,13 @@
       <c r="D184" s="11"/>
       <c r="E184" s="11"/>
       <c r="F184" s="11"/>
-      <c r="G184" s="12"/>
-      <c r="H184" s="13"/>
-      <c r="I184" s="11"/>
+      <c r="G184" s="11"/>
+      <c r="H184" s="11"/>
+      <c r="I184" s="12"/>
       <c r="J184" s="11"/>
       <c r="K184" s="11"/>
       <c r="L184" s="11"/>
+      <c r="M184" s="11"/>
     </row>
     <row r="185">
       <c r="A185" s="11"/>
@@ -2925,12 +3111,13 @@
       <c r="D185" s="11"/>
       <c r="E185" s="11"/>
       <c r="F185" s="11"/>
-      <c r="G185" s="12"/>
-      <c r="H185" s="13"/>
-      <c r="I185" s="11"/>
+      <c r="G185" s="11"/>
+      <c r="H185" s="11"/>
+      <c r="I185" s="12"/>
       <c r="J185" s="11"/>
       <c r="K185" s="11"/>
       <c r="L185" s="11"/>
+      <c r="M185" s="11"/>
     </row>
     <row r="186">
       <c r="A186" s="11"/>
@@ -2939,12 +3126,13 @@
       <c r="D186" s="11"/>
       <c r="E186" s="11"/>
       <c r="F186" s="11"/>
-      <c r="G186" s="12"/>
-      <c r="H186" s="13"/>
-      <c r="I186" s="11"/>
+      <c r="G186" s="11"/>
+      <c r="H186" s="11"/>
+      <c r="I186" s="12"/>
       <c r="J186" s="11"/>
       <c r="K186" s="11"/>
       <c r="L186" s="11"/>
+      <c r="M186" s="11"/>
     </row>
     <row r="187">
       <c r="A187" s="11"/>
@@ -2953,12 +3141,13 @@
       <c r="D187" s="11"/>
       <c r="E187" s="11"/>
       <c r="F187" s="11"/>
-      <c r="G187" s="12"/>
-      <c r="H187" s="13"/>
-      <c r="I187" s="11"/>
+      <c r="G187" s="11"/>
+      <c r="H187" s="11"/>
+      <c r="I187" s="12"/>
       <c r="J187" s="11"/>
       <c r="K187" s="11"/>
       <c r="L187" s="11"/>
+      <c r="M187" s="11"/>
     </row>
     <row r="188">
       <c r="A188" s="11"/>
@@ -2967,12 +3156,13 @@
       <c r="D188" s="11"/>
       <c r="E188" s="11"/>
       <c r="F188" s="11"/>
-      <c r="G188" s="12"/>
-      <c r="H188" s="13"/>
-      <c r="I188" s="11"/>
+      <c r="G188" s="11"/>
+      <c r="H188" s="11"/>
+      <c r="I188" s="12"/>
       <c r="J188" s="11"/>
       <c r="K188" s="11"/>
       <c r="L188" s="11"/>
+      <c r="M188" s="11"/>
     </row>
     <row r="189">
       <c r="A189" s="11"/>
@@ -2981,12 +3171,13 @@
       <c r="D189" s="11"/>
       <c r="E189" s="11"/>
       <c r="F189" s="11"/>
-      <c r="G189" s="12"/>
-      <c r="H189" s="13"/>
-      <c r="I189" s="11"/>
+      <c r="G189" s="11"/>
+      <c r="H189" s="11"/>
+      <c r="I189" s="12"/>
       <c r="J189" s="11"/>
       <c r="K189" s="11"/>
       <c r="L189" s="11"/>
+      <c r="M189" s="11"/>
     </row>
     <row r="190">
       <c r="A190" s="11"/>
@@ -2995,12 +3186,13 @@
       <c r="D190" s="11"/>
       <c r="E190" s="11"/>
       <c r="F190" s="11"/>
-      <c r="G190" s="12"/>
-      <c r="H190" s="13"/>
-      <c r="I190" s="11"/>
+      <c r="G190" s="11"/>
+      <c r="H190" s="11"/>
+      <c r="I190" s="12"/>
       <c r="J190" s="11"/>
       <c r="K190" s="11"/>
       <c r="L190" s="11"/>
+      <c r="M190" s="11"/>
     </row>
     <row r="191">
       <c r="A191" s="11"/>
@@ -3009,12 +3201,13 @@
       <c r="D191" s="11"/>
       <c r="E191" s="11"/>
       <c r="F191" s="11"/>
-      <c r="G191" s="12"/>
-      <c r="H191" s="13"/>
-      <c r="I191" s="11"/>
+      <c r="G191" s="11"/>
+      <c r="H191" s="11"/>
+      <c r="I191" s="12"/>
       <c r="J191" s="11"/>
       <c r="K191" s="11"/>
       <c r="L191" s="11"/>
+      <c r="M191" s="11"/>
     </row>
     <row r="192">
       <c r="A192" s="11"/>
@@ -3023,12 +3216,13 @@
       <c r="D192" s="11"/>
       <c r="E192" s="11"/>
       <c r="F192" s="11"/>
-      <c r="G192" s="12"/>
-      <c r="H192" s="13"/>
-      <c r="I192" s="11"/>
+      <c r="G192" s="11"/>
+      <c r="H192" s="11"/>
+      <c r="I192" s="12"/>
       <c r="J192" s="11"/>
       <c r="K192" s="11"/>
       <c r="L192" s="11"/>
+      <c r="M192" s="11"/>
     </row>
     <row r="193">
       <c r="A193" s="11"/>
@@ -3037,12 +3231,13 @@
       <c r="D193" s="11"/>
       <c r="E193" s="11"/>
       <c r="F193" s="11"/>
-      <c r="G193" s="12"/>
-      <c r="H193" s="13"/>
-      <c r="I193" s="11"/>
+      <c r="G193" s="11"/>
+      <c r="H193" s="11"/>
+      <c r="I193" s="12"/>
       <c r="J193" s="11"/>
       <c r="K193" s="11"/>
       <c r="L193" s="11"/>
+      <c r="M193" s="11"/>
     </row>
     <row r="194">
       <c r="A194" s="11"/>
@@ -3051,12 +3246,13 @@
       <c r="D194" s="11"/>
       <c r="E194" s="11"/>
       <c r="F194" s="11"/>
-      <c r="G194" s="12"/>
-      <c r="H194" s="13"/>
-      <c r="I194" s="11"/>
+      <c r="G194" s="11"/>
+      <c r="H194" s="11"/>
+      <c r="I194" s="12"/>
       <c r="J194" s="11"/>
       <c r="K194" s="11"/>
       <c r="L194" s="11"/>
+      <c r="M194" s="11"/>
     </row>
     <row r="195">
       <c r="A195" s="11"/>
@@ -3065,12 +3261,13 @@
       <c r="D195" s="11"/>
       <c r="E195" s="11"/>
       <c r="F195" s="11"/>
-      <c r="G195" s="12"/>
-      <c r="H195" s="13"/>
-      <c r="I195" s="11"/>
+      <c r="G195" s="11"/>
+      <c r="H195" s="11"/>
+      <c r="I195" s="12"/>
       <c r="J195" s="11"/>
       <c r="K195" s="11"/>
       <c r="L195" s="11"/>
+      <c r="M195" s="11"/>
     </row>
     <row r="196">
       <c r="A196" s="11"/>
@@ -3079,12 +3276,13 @@
       <c r="D196" s="11"/>
       <c r="E196" s="11"/>
       <c r="F196" s="11"/>
-      <c r="G196" s="12"/>
-      <c r="H196" s="13"/>
-      <c r="I196" s="11"/>
+      <c r="G196" s="11"/>
+      <c r="H196" s="11"/>
+      <c r="I196" s="12"/>
       <c r="J196" s="11"/>
       <c r="K196" s="11"/>
       <c r="L196" s="11"/>
+      <c r="M196" s="11"/>
     </row>
     <row r="197">
       <c r="A197" s="11"/>
@@ -3093,12 +3291,13 @@
       <c r="D197" s="11"/>
       <c r="E197" s="11"/>
       <c r="F197" s="11"/>
-      <c r="G197" s="12"/>
-      <c r="H197" s="13"/>
-      <c r="I197" s="11"/>
+      <c r="G197" s="11"/>
+      <c r="H197" s="11"/>
+      <c r="I197" s="12"/>
       <c r="J197" s="11"/>
       <c r="K197" s="11"/>
       <c r="L197" s="11"/>
+      <c r="M197" s="11"/>
     </row>
     <row r="198">
       <c r="A198" s="11"/>
@@ -3107,12 +3306,13 @@
       <c r="D198" s="11"/>
       <c r="E198" s="11"/>
       <c r="F198" s="11"/>
-      <c r="G198" s="12"/>
-      <c r="H198" s="13"/>
-      <c r="I198" s="11"/>
+      <c r="G198" s="11"/>
+      <c r="H198" s="11"/>
+      <c r="I198" s="12"/>
       <c r="J198" s="11"/>
       <c r="K198" s="11"/>
       <c r="L198" s="11"/>
+      <c r="M198" s="11"/>
     </row>
     <row r="199">
       <c r="A199" s="11"/>
@@ -3121,12 +3321,13 @@
       <c r="D199" s="11"/>
       <c r="E199" s="11"/>
       <c r="F199" s="11"/>
-      <c r="G199" s="12"/>
-      <c r="H199" s="13"/>
-      <c r="I199" s="11"/>
+      <c r="G199" s="11"/>
+      <c r="H199" s="11"/>
+      <c r="I199" s="12"/>
       <c r="J199" s="11"/>
       <c r="K199" s="11"/>
       <c r="L199" s="11"/>
+      <c r="M199" s="11"/>
     </row>
     <row r="200">
       <c r="A200" s="11"/>
@@ -3135,12 +3336,13 @@
       <c r="D200" s="11"/>
       <c r="E200" s="11"/>
       <c r="F200" s="11"/>
-      <c r="G200" s="12"/>
-      <c r="H200" s="13"/>
-      <c r="I200" s="11"/>
+      <c r="G200" s="11"/>
+      <c r="H200" s="11"/>
+      <c r="I200" s="12"/>
       <c r="J200" s="11"/>
       <c r="K200" s="11"/>
       <c r="L200" s="11"/>
+      <c r="M200" s="11"/>
     </row>
     <row r="201">
       <c r="A201" s="11"/>
@@ -3149,12 +3351,13 @@
       <c r="D201" s="11"/>
       <c r="E201" s="11"/>
       <c r="F201" s="11"/>
-      <c r="G201" s="12"/>
-      <c r="H201" s="13"/>
-      <c r="I201" s="11"/>
+      <c r="G201" s="11"/>
+      <c r="H201" s="11"/>
+      <c r="I201" s="12"/>
       <c r="J201" s="11"/>
       <c r="K201" s="11"/>
       <c r="L201" s="11"/>
+      <c r="M201" s="11"/>
     </row>
     <row r="202">
       <c r="A202" s="11"/>
@@ -3163,12 +3366,13 @@
       <c r="D202" s="11"/>
       <c r="E202" s="11"/>
       <c r="F202" s="11"/>
-      <c r="G202" s="12"/>
-      <c r="H202" s="13"/>
-      <c r="I202" s="11"/>
+      <c r="G202" s="11"/>
+      <c r="H202" s="11"/>
+      <c r="I202" s="12"/>
       <c r="J202" s="11"/>
       <c r="K202" s="11"/>
       <c r="L202" s="11"/>
+      <c r="M202" s="11"/>
     </row>
     <row r="203">
       <c r="A203" s="11"/>
@@ -3177,12 +3381,13 @@
       <c r="D203" s="11"/>
       <c r="E203" s="11"/>
       <c r="F203" s="11"/>
-      <c r="G203" s="12"/>
-      <c r="H203" s="13"/>
-      <c r="I203" s="11"/>
+      <c r="G203" s="11"/>
+      <c r="H203" s="11"/>
+      <c r="I203" s="12"/>
       <c r="J203" s="11"/>
       <c r="K203" s="11"/>
       <c r="L203" s="11"/>
+      <c r="M203" s="11"/>
     </row>
     <row r="204">
       <c r="A204" s="11"/>
@@ -3191,12 +3396,13 @@
       <c r="D204" s="11"/>
       <c r="E204" s="11"/>
       <c r="F204" s="11"/>
-      <c r="G204" s="12"/>
-      <c r="H204" s="13"/>
-      <c r="I204" s="11"/>
+      <c r="G204" s="11"/>
+      <c r="H204" s="11"/>
+      <c r="I204" s="12"/>
       <c r="J204" s="11"/>
       <c r="K204" s="11"/>
       <c r="L204" s="11"/>
+      <c r="M204" s="11"/>
     </row>
     <row r="205">
       <c r="A205" s="11"/>
@@ -3205,12 +3411,13 @@
       <c r="D205" s="11"/>
       <c r="E205" s="11"/>
       <c r="F205" s="11"/>
-      <c r="G205" s="12"/>
-      <c r="H205" s="13"/>
-      <c r="I205" s="11"/>
+      <c r="G205" s="11"/>
+      <c r="H205" s="11"/>
+      <c r="I205" s="12"/>
       <c r="J205" s="11"/>
       <c r="K205" s="11"/>
       <c r="L205" s="11"/>
+      <c r="M205" s="11"/>
     </row>
     <row r="206">
       <c r="A206" s="11"/>
@@ -3219,12 +3426,13 @@
       <c r="D206" s="11"/>
       <c r="E206" s="11"/>
       <c r="F206" s="11"/>
-      <c r="G206" s="12"/>
-      <c r="H206" s="13"/>
-      <c r="I206" s="11"/>
+      <c r="G206" s="11"/>
+      <c r="H206" s="11"/>
+      <c r="I206" s="12"/>
       <c r="J206" s="11"/>
       <c r="K206" s="11"/>
       <c r="L206" s="11"/>
+      <c r="M206" s="11"/>
     </row>
     <row r="207">
       <c r="A207" s="11"/>
@@ -3233,12 +3441,13 @@
       <c r="D207" s="11"/>
       <c r="E207" s="11"/>
       <c r="F207" s="11"/>
-      <c r="G207" s="12"/>
-      <c r="H207" s="13"/>
-      <c r="I207" s="11"/>
+      <c r="G207" s="11"/>
+      <c r="H207" s="11"/>
+      <c r="I207" s="12"/>
       <c r="J207" s="11"/>
       <c r="K207" s="11"/>
       <c r="L207" s="11"/>
+      <c r="M207" s="11"/>
     </row>
     <row r="208">
       <c r="A208" s="11"/>
@@ -3247,12 +3456,13 @@
       <c r="D208" s="11"/>
       <c r="E208" s="11"/>
       <c r="F208" s="11"/>
-      <c r="G208" s="12"/>
-      <c r="H208" s="13"/>
-      <c r="I208" s="11"/>
+      <c r="G208" s="11"/>
+      <c r="H208" s="11"/>
+      <c r="I208" s="12"/>
       <c r="J208" s="11"/>
       <c r="K208" s="11"/>
       <c r="L208" s="11"/>
+      <c r="M208" s="11"/>
     </row>
     <row r="209">
       <c r="A209" s="11"/>
@@ -3261,12 +3471,13 @@
       <c r="D209" s="11"/>
       <c r="E209" s="11"/>
       <c r="F209" s="11"/>
-      <c r="G209" s="12"/>
-      <c r="H209" s="13"/>
-      <c r="I209" s="11"/>
+      <c r="G209" s="11"/>
+      <c r="H209" s="11"/>
+      <c r="I209" s="12"/>
       <c r="J209" s="11"/>
       <c r="K209" s="11"/>
       <c r="L209" s="11"/>
+      <c r="M209" s="11"/>
     </row>
     <row r="210">
       <c r="A210" s="11"/>
@@ -3275,12 +3486,13 @@
       <c r="D210" s="11"/>
       <c r="E210" s="11"/>
       <c r="F210" s="11"/>
-      <c r="G210" s="12"/>
-      <c r="H210" s="13"/>
-      <c r="I210" s="11"/>
+      <c r="G210" s="11"/>
+      <c r="H210" s="11"/>
+      <c r="I210" s="12"/>
       <c r="J210" s="11"/>
       <c r="K210" s="11"/>
       <c r="L210" s="11"/>
+      <c r="M210" s="11"/>
     </row>
     <row r="211">
       <c r="A211" s="11"/>
@@ -3289,12 +3501,13 @@
       <c r="D211" s="11"/>
       <c r="E211" s="11"/>
       <c r="F211" s="11"/>
-      <c r="G211" s="12"/>
-      <c r="H211" s="13"/>
-      <c r="I211" s="11"/>
+      <c r="G211" s="11"/>
+      <c r="H211" s="11"/>
+      <c r="I211" s="12"/>
       <c r="J211" s="11"/>
       <c r="K211" s="11"/>
       <c r="L211" s="11"/>
+      <c r="M211" s="11"/>
     </row>
     <row r="212">
       <c r="A212" s="11"/>
@@ -3303,12 +3516,13 @@
       <c r="D212" s="11"/>
       <c r="E212" s="11"/>
       <c r="F212" s="11"/>
-      <c r="G212" s="12"/>
-      <c r="H212" s="13"/>
-      <c r="I212" s="11"/>
+      <c r="G212" s="11"/>
+      <c r="H212" s="11"/>
+      <c r="I212" s="12"/>
       <c r="J212" s="11"/>
       <c r="K212" s="11"/>
       <c r="L212" s="11"/>
+      <c r="M212" s="11"/>
     </row>
     <row r="213">
       <c r="A213" s="11"/>
@@ -3317,12 +3531,13 @@
       <c r="D213" s="11"/>
       <c r="E213" s="11"/>
       <c r="F213" s="11"/>
-      <c r="G213" s="12"/>
-      <c r="H213" s="13"/>
-      <c r="I213" s="11"/>
+      <c r="G213" s="11"/>
+      <c r="H213" s="11"/>
+      <c r="I213" s="12"/>
       <c r="J213" s="11"/>
       <c r="K213" s="11"/>
       <c r="L213" s="11"/>
+      <c r="M213" s="11"/>
     </row>
     <row r="214">
       <c r="A214" s="11"/>
@@ -3331,12 +3546,13 @@
       <c r="D214" s="11"/>
       <c r="E214" s="11"/>
       <c r="F214" s="11"/>
-      <c r="G214" s="12"/>
-      <c r="H214" s="13"/>
-      <c r="I214" s="11"/>
+      <c r="G214" s="11"/>
+      <c r="H214" s="11"/>
+      <c r="I214" s="12"/>
       <c r="J214" s="11"/>
       <c r="K214" s="11"/>
       <c r="L214" s="11"/>
+      <c r="M214" s="11"/>
     </row>
     <row r="215">
       <c r="A215" s="11"/>
@@ -3345,12 +3561,13 @@
       <c r="D215" s="11"/>
       <c r="E215" s="11"/>
       <c r="F215" s="11"/>
-      <c r="G215" s="12"/>
-      <c r="H215" s="13"/>
-      <c r="I215" s="11"/>
+      <c r="G215" s="11"/>
+      <c r="H215" s="11"/>
+      <c r="I215" s="12"/>
       <c r="J215" s="11"/>
       <c r="K215" s="11"/>
       <c r="L215" s="11"/>
+      <c r="M215" s="11"/>
     </row>
     <row r="216">
       <c r="A216" s="11"/>
@@ -3359,12 +3576,13 @@
       <c r="D216" s="11"/>
       <c r="E216" s="11"/>
       <c r="F216" s="11"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="13"/>
-      <c r="I216" s="11"/>
+      <c r="G216" s="11"/>
+      <c r="H216" s="11"/>
+      <c r="I216" s="12"/>
       <c r="J216" s="11"/>
       <c r="K216" s="11"/>
       <c r="L216" s="11"/>
+      <c r="M216" s="11"/>
     </row>
     <row r="217">
       <c r="A217" s="11"/>
@@ -3373,12 +3591,13 @@
       <c r="D217" s="11"/>
       <c r="E217" s="11"/>
       <c r="F217" s="11"/>
-      <c r="G217" s="12"/>
-      <c r="H217" s="13"/>
-      <c r="I217" s="11"/>
+      <c r="G217" s="11"/>
+      <c r="H217" s="11"/>
+      <c r="I217" s="12"/>
       <c r="J217" s="11"/>
       <c r="K217" s="11"/>
       <c r="L217" s="11"/>
+      <c r="M217" s="11"/>
     </row>
     <row r="218">
       <c r="A218" s="11"/>
@@ -3387,12 +3606,13 @@
       <c r="D218" s="11"/>
       <c r="E218" s="11"/>
       <c r="F218" s="11"/>
-      <c r="G218" s="12"/>
-      <c r="H218" s="13"/>
-      <c r="I218" s="11"/>
+      <c r="G218" s="11"/>
+      <c r="H218" s="11"/>
+      <c r="I218" s="12"/>
       <c r="J218" s="11"/>
       <c r="K218" s="11"/>
       <c r="L218" s="11"/>
+      <c r="M218" s="11"/>
     </row>
     <row r="219">
       <c r="A219" s="11"/>
@@ -3401,12 +3621,13 @@
       <c r="D219" s="11"/>
       <c r="E219" s="11"/>
       <c r="F219" s="11"/>
-      <c r="G219" s="12"/>
-      <c r="H219" s="13"/>
-      <c r="I219" s="11"/>
+      <c r="G219" s="11"/>
+      <c r="H219" s="11"/>
+      <c r="I219" s="12"/>
       <c r="J219" s="11"/>
       <c r="K219" s="11"/>
       <c r="L219" s="11"/>
+      <c r="M219" s="11"/>
     </row>
     <row r="220">
       <c r="A220" s="11"/>
@@ -3415,12 +3636,13 @@
       <c r="D220" s="11"/>
       <c r="E220" s="11"/>
       <c r="F220" s="11"/>
-      <c r="G220" s="12"/>
-      <c r="H220" s="13"/>
-      <c r="I220" s="11"/>
+      <c r="G220" s="11"/>
+      <c r="H220" s="11"/>
+      <c r="I220" s="12"/>
       <c r="J220" s="11"/>
       <c r="K220" s="11"/>
       <c r="L220" s="11"/>
+      <c r="M220" s="11"/>
     </row>
     <row r="221">
       <c r="A221" s="11"/>
@@ -3429,12 +3651,13 @@
       <c r="D221" s="11"/>
       <c r="E221" s="11"/>
       <c r="F221" s="11"/>
-      <c r="G221" s="12"/>
-      <c r="H221" s="13"/>
-      <c r="I221" s="11"/>
+      <c r="G221" s="11"/>
+      <c r="H221" s="11"/>
+      <c r="I221" s="12"/>
       <c r="J221" s="11"/>
       <c r="K221" s="11"/>
       <c r="L221" s="11"/>
+      <c r="M221" s="11"/>
     </row>
     <row r="222">
       <c r="A222" s="11"/>
@@ -3443,12 +3666,13 @@
       <c r="D222" s="11"/>
       <c r="E222" s="11"/>
       <c r="F222" s="11"/>
-      <c r="G222" s="12"/>
-      <c r="H222" s="13"/>
-      <c r="I222" s="11"/>
+      <c r="G222" s="11"/>
+      <c r="H222" s="11"/>
+      <c r="I222" s="12"/>
       <c r="J222" s="11"/>
       <c r="K222" s="11"/>
       <c r="L222" s="11"/>
+      <c r="M222" s="11"/>
     </row>
     <row r="223">
       <c r="A223" s="11"/>
@@ -3457,12 +3681,13 @@
       <c r="D223" s="11"/>
       <c r="E223" s="11"/>
       <c r="F223" s="11"/>
-      <c r="G223" s="12"/>
-      <c r="H223" s="13"/>
-      <c r="I223" s="11"/>
+      <c r="G223" s="11"/>
+      <c r="H223" s="11"/>
+      <c r="I223" s="12"/>
       <c r="J223" s="11"/>
       <c r="K223" s="11"/>
       <c r="L223" s="11"/>
+      <c r="M223" s="11"/>
     </row>
     <row r="224">
       <c r="A224" s="11"/>
@@ -3471,12 +3696,13 @@
       <c r="D224" s="11"/>
       <c r="E224" s="11"/>
       <c r="F224" s="11"/>
-      <c r="G224" s="12"/>
-      <c r="H224" s="13"/>
-      <c r="I224" s="11"/>
+      <c r="G224" s="11"/>
+      <c r="H224" s="11"/>
+      <c r="I224" s="12"/>
       <c r="J224" s="11"/>
       <c r="K224" s="11"/>
       <c r="L224" s="11"/>
+      <c r="M224" s="11"/>
     </row>
     <row r="225">
       <c r="A225" s="11"/>
@@ -3485,12 +3711,13 @@
       <c r="D225" s="11"/>
       <c r="E225" s="11"/>
       <c r="F225" s="11"/>
-      <c r="G225" s="12"/>
-      <c r="H225" s="13"/>
-      <c r="I225" s="11"/>
+      <c r="G225" s="11"/>
+      <c r="H225" s="11"/>
+      <c r="I225" s="12"/>
       <c r="J225" s="11"/>
       <c r="K225" s="11"/>
       <c r="L225" s="11"/>
+      <c r="M225" s="11"/>
     </row>
     <row r="226">
       <c r="A226" s="11"/>
@@ -3499,12 +3726,13 @@
       <c r="D226" s="11"/>
       <c r="E226" s="11"/>
       <c r="F226" s="11"/>
-      <c r="G226" s="12"/>
-      <c r="H226" s="13"/>
-      <c r="I226" s="11"/>
+      <c r="G226" s="11"/>
+      <c r="H226" s="11"/>
+      <c r="I226" s="12"/>
       <c r="J226" s="11"/>
       <c r="K226" s="11"/>
       <c r="L226" s="11"/>
+      <c r="M226" s="11"/>
     </row>
     <row r="227">
       <c r="A227" s="11"/>
@@ -3513,12 +3741,13 @@
       <c r="D227" s="11"/>
       <c r="E227" s="11"/>
       <c r="F227" s="11"/>
-      <c r="G227" s="12"/>
-      <c r="H227" s="13"/>
-      <c r="I227" s="11"/>
+      <c r="G227" s="11"/>
+      <c r="H227" s="11"/>
+      <c r="I227" s="12"/>
       <c r="J227" s="11"/>
       <c r="K227" s="11"/>
       <c r="L227" s="11"/>
+      <c r="M227" s="11"/>
     </row>
     <row r="228">
       <c r="A228" s="11"/>
@@ -3527,12 +3756,13 @@
       <c r="D228" s="11"/>
       <c r="E228" s="11"/>
       <c r="F228" s="11"/>
-      <c r="G228" s="12"/>
-      <c r="H228" s="13"/>
-      <c r="I228" s="11"/>
+      <c r="G228" s="11"/>
+      <c r="H228" s="11"/>
+      <c r="I228" s="12"/>
       <c r="J228" s="11"/>
       <c r="K228" s="11"/>
       <c r="L228" s="11"/>
+      <c r="M228" s="11"/>
     </row>
     <row r="229">
       <c r="A229" s="11"/>
@@ -3541,12 +3771,13 @@
       <c r="D229" s="11"/>
       <c r="E229" s="11"/>
       <c r="F229" s="11"/>
-      <c r="G229" s="12"/>
-      <c r="H229" s="13"/>
-      <c r="I229" s="11"/>
+      <c r="G229" s="11"/>
+      <c r="H229" s="11"/>
+      <c r="I229" s="12"/>
       <c r="J229" s="11"/>
       <c r="K229" s="11"/>
       <c r="L229" s="11"/>
+      <c r="M229" s="11"/>
     </row>
     <row r="230">
       <c r="A230" s="11"/>
@@ -3555,12 +3786,13 @@
       <c r="D230" s="11"/>
       <c r="E230" s="11"/>
       <c r="F230" s="11"/>
-      <c r="G230" s="12"/>
-      <c r="H230" s="13"/>
-      <c r="I230" s="11"/>
+      <c r="G230" s="11"/>
+      <c r="H230" s="11"/>
+      <c r="I230" s="12"/>
       <c r="J230" s="11"/>
       <c r="K230" s="11"/>
       <c r="L230" s="11"/>
+      <c r="M230" s="11"/>
     </row>
     <row r="231">
       <c r="A231" s="11"/>
@@ -3569,12 +3801,13 @@
       <c r="D231" s="11"/>
       <c r="E231" s="11"/>
       <c r="F231" s="11"/>
-      <c r="G231" s="12"/>
-      <c r="H231" s="13"/>
-      <c r="I231" s="11"/>
+      <c r="G231" s="11"/>
+      <c r="H231" s="11"/>
+      <c r="I231" s="12"/>
       <c r="J231" s="11"/>
       <c r="K231" s="11"/>
       <c r="L231" s="11"/>
+      <c r="M231" s="11"/>
     </row>
     <row r="232">
       <c r="A232" s="11"/>
@@ -3583,12 +3816,13 @@
       <c r="D232" s="11"/>
       <c r="E232" s="11"/>
       <c r="F232" s="11"/>
-      <c r="G232" s="12"/>
-      <c r="H232" s="13"/>
-      <c r="I232" s="11"/>
+      <c r="G232" s="11"/>
+      <c r="H232" s="11"/>
+      <c r="I232" s="12"/>
       <c r="J232" s="11"/>
       <c r="K232" s="11"/>
       <c r="L232" s="11"/>
+      <c r="M232" s="11"/>
     </row>
     <row r="233">
       <c r="A233" s="11"/>
@@ -3597,12 +3831,13 @@
       <c r="D233" s="11"/>
       <c r="E233" s="11"/>
       <c r="F233" s="11"/>
-      <c r="G233" s="12"/>
-      <c r="H233" s="13"/>
-      <c r="I233" s="11"/>
+      <c r="G233" s="11"/>
+      <c r="H233" s="11"/>
+      <c r="I233" s="12"/>
       <c r="J233" s="11"/>
       <c r="K233" s="11"/>
       <c r="L233" s="11"/>
+      <c r="M233" s="11"/>
     </row>
     <row r="234">
       <c r="A234" s="11"/>
@@ -3611,12 +3846,13 @@
       <c r="D234" s="11"/>
       <c r="E234" s="11"/>
       <c r="F234" s="11"/>
-      <c r="G234" s="12"/>
-      <c r="H234" s="13"/>
-      <c r="I234" s="11"/>
+      <c r="G234" s="11"/>
+      <c r="H234" s="11"/>
+      <c r="I234" s="12"/>
       <c r="J234" s="11"/>
       <c r="K234" s="11"/>
       <c r="L234" s="11"/>
+      <c r="M234" s="11"/>
     </row>
     <row r="235">
       <c r="A235" s="11"/>
@@ -3625,12 +3861,13 @@
       <c r="D235" s="11"/>
       <c r="E235" s="11"/>
       <c r="F235" s="11"/>
-      <c r="G235" s="12"/>
-      <c r="H235" s="13"/>
-      <c r="I235" s="11"/>
+      <c r="G235" s="11"/>
+      <c r="H235" s="11"/>
+      <c r="I235" s="12"/>
       <c r="J235" s="11"/>
       <c r="K235" s="11"/>
       <c r="L235" s="11"/>
+      <c r="M235" s="11"/>
     </row>
     <row r="236">
       <c r="A236" s="11"/>
@@ -3639,12 +3876,13 @@
       <c r="D236" s="11"/>
       <c r="E236" s="11"/>
       <c r="F236" s="11"/>
-      <c r="G236" s="12"/>
-      <c r="H236" s="13"/>
-      <c r="I236" s="11"/>
+      <c r="G236" s="11"/>
+      <c r="H236" s="11"/>
+      <c r="I236" s="12"/>
       <c r="J236" s="11"/>
       <c r="K236" s="11"/>
       <c r="L236" s="11"/>
+      <c r="M236" s="11"/>
     </row>
     <row r="237">
       <c r="A237" s="11"/>
@@ -3653,12 +3891,13 @@
       <c r="D237" s="11"/>
       <c r="E237" s="11"/>
       <c r="F237" s="11"/>
-      <c r="G237" s="12"/>
-      <c r="H237" s="13"/>
-      <c r="I237" s="11"/>
+      <c r="G237" s="11"/>
+      <c r="H237" s="11"/>
+      <c r="I237" s="12"/>
       <c r="J237" s="11"/>
       <c r="K237" s="11"/>
       <c r="L237" s="11"/>
+      <c r="M237" s="11"/>
     </row>
     <row r="238">
       <c r="A238" s="11"/>
@@ -3667,12 +3906,13 @@
       <c r="D238" s="11"/>
       <c r="E238" s="11"/>
       <c r="F238" s="11"/>
-      <c r="G238" s="12"/>
-      <c r="H238" s="13"/>
-      <c r="I238" s="11"/>
+      <c r="G238" s="11"/>
+      <c r="H238" s="11"/>
+      <c r="I238" s="12"/>
       <c r="J238" s="11"/>
       <c r="K238" s="11"/>
       <c r="L238" s="11"/>
+      <c r="M238" s="11"/>
     </row>
     <row r="239">
       <c r="A239" s="11"/>
@@ -3681,12 +3921,13 @@
       <c r="D239" s="11"/>
       <c r="E239" s="11"/>
       <c r="F239" s="11"/>
-      <c r="G239" s="12"/>
-      <c r="H239" s="13"/>
-      <c r="I239" s="11"/>
+      <c r="G239" s="11"/>
+      <c r="H239" s="11"/>
+      <c r="I239" s="12"/>
       <c r="J239" s="11"/>
       <c r="K239" s="11"/>
       <c r="L239" s="11"/>
+      <c r="M239" s="11"/>
     </row>
     <row r="240">
       <c r="A240" s="11"/>
@@ -3695,12 +3936,13 @@
       <c r="D240" s="11"/>
       <c r="E240" s="11"/>
       <c r="F240" s="11"/>
-      <c r="G240" s="12"/>
-      <c r="H240" s="13"/>
-      <c r="I240" s="11"/>
+      <c r="G240" s="11"/>
+      <c r="H240" s="11"/>
+      <c r="I240" s="12"/>
       <c r="J240" s="11"/>
       <c r="K240" s="11"/>
       <c r="L240" s="11"/>
+      <c r="M240" s="11"/>
     </row>
     <row r="241">
       <c r="A241" s="11"/>
@@ -3709,12 +3951,13 @@
       <c r="D241" s="11"/>
       <c r="E241" s="11"/>
       <c r="F241" s="11"/>
-      <c r="G241" s="12"/>
-      <c r="H241" s="13"/>
-      <c r="I241" s="11"/>
+      <c r="G241" s="11"/>
+      <c r="H241" s="11"/>
+      <c r="I241" s="12"/>
       <c r="J241" s="11"/>
       <c r="K241" s="11"/>
       <c r="L241" s="11"/>
+      <c r="M241" s="11"/>
     </row>
     <row r="242">
       <c r="A242" s="11"/>
@@ -3723,12 +3966,13 @@
       <c r="D242" s="11"/>
       <c r="E242" s="11"/>
       <c r="F242" s="11"/>
-      <c r="G242" s="12"/>
-      <c r="H242" s="13"/>
-      <c r="I242" s="11"/>
+      <c r="G242" s="11"/>
+      <c r="H242" s="11"/>
+      <c r="I242" s="12"/>
       <c r="J242" s="11"/>
       <c r="K242" s="11"/>
       <c r="L242" s="11"/>
+      <c r="M242" s="11"/>
     </row>
     <row r="243">
       <c r="A243" s="11"/>
@@ -3737,12 +3981,13 @@
       <c r="D243" s="11"/>
       <c r="E243" s="11"/>
       <c r="F243" s="11"/>
-      <c r="G243" s="12"/>
-      <c r="H243" s="13"/>
-      <c r="I243" s="11"/>
+      <c r="G243" s="11"/>
+      <c r="H243" s="11"/>
+      <c r="I243" s="12"/>
       <c r="J243" s="11"/>
       <c r="K243" s="11"/>
       <c r="L243" s="11"/>
+      <c r="M243" s="11"/>
     </row>
     <row r="244">
       <c r="A244" s="11"/>
@@ -3751,12 +3996,13 @@
       <c r="D244" s="11"/>
       <c r="E244" s="11"/>
       <c r="F244" s="11"/>
-      <c r="G244" s="12"/>
-      <c r="H244" s="13"/>
-      <c r="I244" s="11"/>
+      <c r="G244" s="11"/>
+      <c r="H244" s="11"/>
+      <c r="I244" s="12"/>
       <c r="J244" s="11"/>
       <c r="K244" s="11"/>
       <c r="L244" s="11"/>
+      <c r="M244" s="11"/>
     </row>
     <row r="245">
       <c r="A245" s="11"/>
@@ -3765,12 +4011,13 @@
       <c r="D245" s="11"/>
       <c r="E245" s="11"/>
       <c r="F245" s="11"/>
-      <c r="G245" s="12"/>
-      <c r="H245" s="13"/>
-      <c r="I245" s="11"/>
+      <c r="G245" s="11"/>
+      <c r="H245" s="11"/>
+      <c r="I245" s="12"/>
       <c r="J245" s="11"/>
       <c r="K245" s="11"/>
       <c r="L245" s="11"/>
+      <c r="M245" s="11"/>
     </row>
     <row r="246">
       <c r="A246" s="11"/>
@@ -3779,12 +4026,13 @@
       <c r="D246" s="11"/>
       <c r="E246" s="11"/>
       <c r="F246" s="11"/>
-      <c r="G246" s="12"/>
-      <c r="H246" s="13"/>
-      <c r="I246" s="11"/>
+      <c r="G246" s="11"/>
+      <c r="H246" s="11"/>
+      <c r="I246" s="12"/>
       <c r="J246" s="11"/>
       <c r="K246" s="11"/>
       <c r="L246" s="11"/>
+      <c r="M246" s="11"/>
     </row>
     <row r="247">
       <c r="A247" s="11"/>
@@ -3793,12 +4041,13 @@
       <c r="D247" s="11"/>
       <c r="E247" s="11"/>
       <c r="F247" s="11"/>
-      <c r="G247" s="12"/>
-      <c r="H247" s="13"/>
-      <c r="I247" s="11"/>
+      <c r="G247" s="11"/>
+      <c r="H247" s="11"/>
+      <c r="I247" s="12"/>
       <c r="J247" s="11"/>
       <c r="K247" s="11"/>
       <c r="L247" s="11"/>
+      <c r="M247" s="11"/>
     </row>
     <row r="248">
       <c r="A248" s="11"/>
@@ -3807,12 +4056,13 @@
       <c r="D248" s="11"/>
       <c r="E248" s="11"/>
       <c r="F248" s="11"/>
-      <c r="G248" s="12"/>
-      <c r="H248" s="13"/>
-      <c r="I248" s="11"/>
+      <c r="G248" s="11"/>
+      <c r="H248" s="11"/>
+      <c r="I248" s="12"/>
       <c r="J248" s="11"/>
       <c r="K248" s="11"/>
       <c r="L248" s="11"/>
+      <c r="M248" s="11"/>
     </row>
     <row r="249">
       <c r="A249" s="11"/>
@@ -3821,12 +4071,13 @@
       <c r="D249" s="11"/>
       <c r="E249" s="11"/>
       <c r="F249" s="11"/>
-      <c r="G249" s="12"/>
-      <c r="H249" s="13"/>
-      <c r="I249" s="11"/>
+      <c r="G249" s="11"/>
+      <c r="H249" s="11"/>
+      <c r="I249" s="12"/>
       <c r="J249" s="11"/>
       <c r="K249" s="11"/>
       <c r="L249" s="11"/>
+      <c r="M249" s="11"/>
     </row>
     <row r="250">
       <c r="A250" s="11"/>
@@ -3835,12 +4086,13 @@
       <c r="D250" s="11"/>
       <c r="E250" s="11"/>
       <c r="F250" s="11"/>
-      <c r="G250" s="12"/>
-      <c r="H250" s="13"/>
-      <c r="I250" s="11"/>
+      <c r="G250" s="11"/>
+      <c r="H250" s="11"/>
+      <c r="I250" s="12"/>
       <c r="J250" s="11"/>
       <c r="K250" s="11"/>
       <c r="L250" s="11"/>
+      <c r="M250" s="11"/>
     </row>
     <row r="251">
       <c r="A251" s="11"/>
@@ -3849,12 +4101,13 @@
       <c r="D251" s="11"/>
       <c r="E251" s="11"/>
       <c r="F251" s="11"/>
-      <c r="G251" s="12"/>
-      <c r="H251" s="13"/>
-      <c r="I251" s="11"/>
+      <c r="G251" s="11"/>
+      <c r="H251" s="11"/>
+      <c r="I251" s="12"/>
       <c r="J251" s="11"/>
       <c r="K251" s="11"/>
       <c r="L251" s="11"/>
+      <c r="M251" s="11"/>
     </row>
     <row r="252">
       <c r="A252" s="11"/>
@@ -3863,12 +4116,13 @@
       <c r="D252" s="11"/>
       <c r="E252" s="11"/>
       <c r="F252" s="11"/>
-      <c r="G252" s="12"/>
-      <c r="H252" s="13"/>
-      <c r="I252" s="11"/>
+      <c r="G252" s="11"/>
+      <c r="H252" s="11"/>
+      <c r="I252" s="12"/>
       <c r="J252" s="11"/>
       <c r="K252" s="11"/>
       <c r="L252" s="11"/>
+      <c r="M252" s="11"/>
     </row>
     <row r="253">
       <c r="A253" s="11"/>
@@ -3877,12 +4131,13 @@
       <c r="D253" s="11"/>
       <c r="E253" s="11"/>
       <c r="F253" s="11"/>
-      <c r="G253" s="12"/>
-      <c r="H253" s="13"/>
-      <c r="I253" s="11"/>
+      <c r="G253" s="11"/>
+      <c r="H253" s="11"/>
+      <c r="I253" s="12"/>
       <c r="J253" s="11"/>
       <c r="K253" s="11"/>
       <c r="L253" s="11"/>
+      <c r="M253" s="11"/>
     </row>
     <row r="254">
       <c r="A254" s="11"/>
@@ -3891,12 +4146,13 @@
       <c r="D254" s="11"/>
       <c r="E254" s="11"/>
       <c r="F254" s="11"/>
-      <c r="G254" s="12"/>
-      <c r="H254" s="13"/>
-      <c r="I254" s="11"/>
+      <c r="G254" s="11"/>
+      <c r="H254" s="11"/>
+      <c r="I254" s="12"/>
       <c r="J254" s="11"/>
       <c r="K254" s="11"/>
       <c r="L254" s="11"/>
+      <c r="M254" s="11"/>
     </row>
     <row r="255">
       <c r="A255" s="11"/>
@@ -3905,12 +4161,13 @@
       <c r="D255" s="11"/>
       <c r="E255" s="11"/>
       <c r="F255" s="11"/>
-      <c r="G255" s="12"/>
-      <c r="H255" s="13"/>
-      <c r="I255" s="11"/>
+      <c r="G255" s="11"/>
+      <c r="H255" s="11"/>
+      <c r="I255" s="12"/>
       <c r="J255" s="11"/>
       <c r="K255" s="11"/>
       <c r="L255" s="11"/>
+      <c r="M255" s="11"/>
     </row>
     <row r="256">
       <c r="A256" s="11"/>
@@ -3919,12 +4176,13 @@
       <c r="D256" s="11"/>
       <c r="E256" s="11"/>
       <c r="F256" s="11"/>
-      <c r="G256" s="12"/>
-      <c r="H256" s="13"/>
-      <c r="I256" s="11"/>
+      <c r="G256" s="11"/>
+      <c r="H256" s="11"/>
+      <c r="I256" s="12"/>
       <c r="J256" s="11"/>
       <c r="K256" s="11"/>
       <c r="L256" s="11"/>
+      <c r="M256" s="11"/>
     </row>
     <row r="257">
       <c r="A257" s="11"/>
@@ -3933,12 +4191,13 @@
       <c r="D257" s="11"/>
       <c r="E257" s="11"/>
       <c r="F257" s="11"/>
-      <c r="G257" s="12"/>
-      <c r="H257" s="13"/>
-      <c r="I257" s="11"/>
+      <c r="G257" s="11"/>
+      <c r="H257" s="11"/>
+      <c r="I257" s="12"/>
       <c r="J257" s="11"/>
       <c r="K257" s="11"/>
       <c r="L257" s="11"/>
+      <c r="M257" s="11"/>
     </row>
     <row r="258">
       <c r="A258" s="11"/>
@@ -3947,12 +4206,13 @@
       <c r="D258" s="11"/>
       <c r="E258" s="11"/>
       <c r="F258" s="11"/>
-      <c r="G258" s="12"/>
-      <c r="H258" s="13"/>
-      <c r="I258" s="11"/>
+      <c r="G258" s="11"/>
+      <c r="H258" s="11"/>
+      <c r="I258" s="12"/>
       <c r="J258" s="11"/>
       <c r="K258" s="11"/>
       <c r="L258" s="11"/>
+      <c r="M258" s="11"/>
     </row>
     <row r="259">
       <c r="A259" s="11"/>
@@ -3961,12 +4221,13 @@
       <c r="D259" s="11"/>
       <c r="E259" s="11"/>
       <c r="F259" s="11"/>
-      <c r="G259" s="12"/>
-      <c r="H259" s="13"/>
-      <c r="I259" s="11"/>
+      <c r="G259" s="11"/>
+      <c r="H259" s="11"/>
+      <c r="I259" s="12"/>
       <c r="J259" s="11"/>
       <c r="K259" s="11"/>
       <c r="L259" s="11"/>
+      <c r="M259" s="11"/>
     </row>
     <row r="260">
       <c r="A260" s="11"/>
@@ -3975,12 +4236,13 @@
       <c r="D260" s="11"/>
       <c r="E260" s="11"/>
       <c r="F260" s="11"/>
-      <c r="G260" s="12"/>
-      <c r="H260" s="13"/>
-      <c r="I260" s="11"/>
+      <c r="G260" s="11"/>
+      <c r="H260" s="11"/>
+      <c r="I260" s="12"/>
       <c r="J260" s="11"/>
       <c r="K260" s="11"/>
       <c r="L260" s="11"/>
+      <c r="M260" s="11"/>
     </row>
     <row r="261">
       <c r="A261" s="11"/>
@@ -3989,12 +4251,13 @@
       <c r="D261" s="11"/>
       <c r="E261" s="11"/>
       <c r="F261" s="11"/>
-      <c r="G261" s="12"/>
-      <c r="H261" s="13"/>
-      <c r="I261" s="11"/>
+      <c r="G261" s="11"/>
+      <c r="H261" s="11"/>
+      <c r="I261" s="12"/>
       <c r="J261" s="11"/>
       <c r="K261" s="11"/>
       <c r="L261" s="11"/>
+      <c r="M261" s="11"/>
     </row>
     <row r="262">
       <c r="A262" s="11"/>
@@ -4003,12 +4266,13 @@
       <c r="D262" s="11"/>
       <c r="E262" s="11"/>
       <c r="F262" s="11"/>
-      <c r="G262" s="12"/>
-      <c r="H262" s="13"/>
-      <c r="I262" s="11"/>
+      <c r="G262" s="11"/>
+      <c r="H262" s="11"/>
+      <c r="I262" s="12"/>
       <c r="J262" s="11"/>
       <c r="K262" s="11"/>
       <c r="L262" s="11"/>
+      <c r="M262" s="11"/>
     </row>
     <row r="263">
       <c r="A263" s="11"/>
@@ -4017,12 +4281,13 @@
       <c r="D263" s="11"/>
       <c r="E263" s="11"/>
       <c r="F263" s="11"/>
-      <c r="G263" s="12"/>
-      <c r="H263" s="13"/>
-      <c r="I263" s="11"/>
+      <c r="G263" s="11"/>
+      <c r="H263" s="11"/>
+      <c r="I263" s="12"/>
       <c r="J263" s="11"/>
       <c r="K263" s="11"/>
       <c r="L263" s="11"/>
+      <c r="M263" s="11"/>
     </row>
     <row r="264">
       <c r="A264" s="11"/>
@@ -4031,12 +4296,13 @@
       <c r="D264" s="11"/>
       <c r="E264" s="11"/>
       <c r="F264" s="11"/>
-      <c r="G264" s="12"/>
-      <c r="H264" s="13"/>
-      <c r="I264" s="11"/>
+      <c r="G264" s="11"/>
+      <c r="H264" s="11"/>
+      <c r="I264" s="12"/>
       <c r="J264" s="11"/>
       <c r="K264" s="11"/>
       <c r="L264" s="11"/>
+      <c r="M264" s="11"/>
     </row>
     <row r="265">
       <c r="A265" s="11"/>
@@ -4045,12 +4311,13 @@
       <c r="D265" s="11"/>
       <c r="E265" s="11"/>
       <c r="F265" s="11"/>
-      <c r="G265" s="12"/>
-      <c r="H265" s="13"/>
-      <c r="I265" s="11"/>
+      <c r="G265" s="11"/>
+      <c r="H265" s="11"/>
+      <c r="I265" s="12"/>
       <c r="J265" s="11"/>
       <c r="K265" s="11"/>
       <c r="L265" s="11"/>
+      <c r="M265" s="11"/>
     </row>
     <row r="266">
       <c r="A266" s="11"/>
@@ -4059,12 +4326,13 @@
       <c r="D266" s="11"/>
       <c r="E266" s="11"/>
       <c r="F266" s="11"/>
-      <c r="G266" s="12"/>
-      <c r="H266" s="13"/>
-      <c r="I266" s="11"/>
+      <c r="G266" s="11"/>
+      <c r="H266" s="11"/>
+      <c r="I266" s="12"/>
       <c r="J266" s="11"/>
       <c r="K266" s="11"/>
       <c r="L266" s="11"/>
+      <c r="M266" s="11"/>
     </row>
     <row r="267">
       <c r="A267" s="11"/>
@@ -4073,12 +4341,13 @@
       <c r="D267" s="11"/>
       <c r="E267" s="11"/>
       <c r="F267" s="11"/>
-      <c r="G267" s="12"/>
-      <c r="H267" s="13"/>
-      <c r="I267" s="11"/>
+      <c r="G267" s="11"/>
+      <c r="H267" s="11"/>
+      <c r="I267" s="12"/>
       <c r="J267" s="11"/>
       <c r="K267" s="11"/>
       <c r="L267" s="11"/>
+      <c r="M267" s="11"/>
     </row>
     <row r="268">
       <c r="A268" s="11"/>
@@ -4087,12 +4356,13 @@
       <c r="D268" s="11"/>
       <c r="E268" s="11"/>
       <c r="F268" s="11"/>
-      <c r="G268" s="12"/>
-      <c r="H268" s="13"/>
-      <c r="I268" s="11"/>
+      <c r="G268" s="11"/>
+      <c r="H268" s="11"/>
+      <c r="I268" s="12"/>
       <c r="J268" s="11"/>
       <c r="K268" s="11"/>
       <c r="L268" s="11"/>
+      <c r="M268" s="11"/>
     </row>
     <row r="269">
       <c r="A269" s="11"/>
@@ -4101,12 +4371,13 @@
       <c r="D269" s="11"/>
       <c r="E269" s="11"/>
       <c r="F269" s="11"/>
-      <c r="G269" s="12"/>
-      <c r="H269" s="13"/>
-      <c r="I269" s="11"/>
+      <c r="G269" s="11"/>
+      <c r="H269" s="11"/>
+      <c r="I269" s="12"/>
       <c r="J269" s="11"/>
       <c r="K269" s="11"/>
       <c r="L269" s="11"/>
+      <c r="M269" s="11"/>
     </row>
     <row r="270">
       <c r="A270" s="11"/>
@@ -4115,12 +4386,13 @@
       <c r="D270" s="11"/>
       <c r="E270" s="11"/>
       <c r="F270" s="11"/>
-      <c r="G270" s="12"/>
-      <c r="H270" s="13"/>
-      <c r="I270" s="11"/>
+      <c r="G270" s="11"/>
+      <c r="H270" s="11"/>
+      <c r="I270" s="12"/>
       <c r="J270" s="11"/>
       <c r="K270" s="11"/>
       <c r="L270" s="11"/>
+      <c r="M270" s="11"/>
     </row>
     <row r="271">
       <c r="A271" s="11"/>
@@ -4129,12 +4401,13 @@
       <c r="D271" s="11"/>
       <c r="E271" s="11"/>
       <c r="F271" s="11"/>
-      <c r="G271" s="12"/>
-      <c r="H271" s="13"/>
-      <c r="I271" s="11"/>
+      <c r="G271" s="11"/>
+      <c r="H271" s="11"/>
+      <c r="I271" s="12"/>
       <c r="J271" s="11"/>
       <c r="K271" s="11"/>
       <c r="L271" s="11"/>
+      <c r="M271" s="11"/>
     </row>
     <row r="272">
       <c r="A272" s="11"/>
@@ -4143,12 +4416,13 @@
       <c r="D272" s="11"/>
       <c r="E272" s="11"/>
       <c r="F272" s="11"/>
-      <c r="G272" s="12"/>
-      <c r="H272" s="13"/>
-      <c r="I272" s="11"/>
+      <c r="G272" s="11"/>
+      <c r="H272" s="11"/>
+      <c r="I272" s="12"/>
       <c r="J272" s="11"/>
       <c r="K272" s="11"/>
       <c r="L272" s="11"/>
+      <c r="M272" s="11"/>
     </row>
     <row r="273">
       <c r="A273" s="11"/>
@@ -4157,12 +4431,13 @@
       <c r="D273" s="11"/>
       <c r="E273" s="11"/>
       <c r="F273" s="11"/>
-      <c r="G273" s="12"/>
-      <c r="H273" s="13"/>
-      <c r="I273" s="11"/>
+      <c r="G273" s="11"/>
+      <c r="H273" s="11"/>
+      <c r="I273" s="12"/>
       <c r="J273" s="11"/>
       <c r="K273" s="11"/>
       <c r="L273" s="11"/>
+      <c r="M273" s="11"/>
     </row>
     <row r="274">
       <c r="A274" s="11"/>
@@ -4171,12 +4446,13 @@
       <c r="D274" s="11"/>
       <c r="E274" s="11"/>
       <c r="F274" s="11"/>
-      <c r="G274" s="12"/>
-      <c r="H274" s="13"/>
-      <c r="I274" s="11"/>
+      <c r="G274" s="11"/>
+      <c r="H274" s="11"/>
+      <c r="I274" s="12"/>
       <c r="J274" s="11"/>
       <c r="K274" s="11"/>
       <c r="L274" s="11"/>
+      <c r="M274" s="11"/>
     </row>
     <row r="275">
       <c r="A275" s="11"/>
@@ -4185,12 +4461,13 @@
       <c r="D275" s="11"/>
       <c r="E275" s="11"/>
       <c r="F275" s="11"/>
-      <c r="G275" s="12"/>
-      <c r="H275" s="13"/>
-      <c r="I275" s="11"/>
+      <c r="G275" s="11"/>
+      <c r="H275" s="11"/>
+      <c r="I275" s="12"/>
       <c r="J275" s="11"/>
       <c r="K275" s="11"/>
       <c r="L275" s="11"/>
+      <c r="M275" s="11"/>
     </row>
     <row r="276">
       <c r="A276" s="11"/>
@@ -4199,12 +4476,13 @@
       <c r="D276" s="11"/>
       <c r="E276" s="11"/>
       <c r="F276" s="11"/>
-      <c r="G276" s="12"/>
-      <c r="H276" s="13"/>
-      <c r="I276" s="11"/>
+      <c r="G276" s="11"/>
+      <c r="H276" s="11"/>
+      <c r="I276" s="12"/>
       <c r="J276" s="11"/>
       <c r="K276" s="11"/>
       <c r="L276" s="11"/>
+      <c r="M276" s="11"/>
     </row>
     <row r="277">
       <c r="A277" s="11"/>
@@ -4213,12 +4491,13 @@
       <c r="D277" s="11"/>
       <c r="E277" s="11"/>
       <c r="F277" s="11"/>
-      <c r="G277" s="12"/>
-      <c r="H277" s="13"/>
-      <c r="I277" s="11"/>
+      <c r="G277" s="11"/>
+      <c r="H277" s="11"/>
+      <c r="I277" s="12"/>
       <c r="J277" s="11"/>
       <c r="K277" s="11"/>
       <c r="L277" s="11"/>
+      <c r="M277" s="11"/>
     </row>
     <row r="278">
       <c r="A278" s="11"/>
@@ -4227,12 +4506,13 @@
       <c r="D278" s="11"/>
       <c r="E278" s="11"/>
       <c r="F278" s="11"/>
-      <c r="G278" s="12"/>
-      <c r="H278" s="13"/>
-      <c r="I278" s="11"/>
+      <c r="G278" s="11"/>
+      <c r="H278" s="11"/>
+      <c r="I278" s="12"/>
       <c r="J278" s="11"/>
       <c r="K278" s="11"/>
       <c r="L278" s="11"/>
+      <c r="M278" s="11"/>
     </row>
     <row r="279">
       <c r="A279" s="11"/>
@@ -4241,12 +4521,13 @@
       <c r="D279" s="11"/>
       <c r="E279" s="11"/>
       <c r="F279" s="11"/>
-      <c r="G279" s="12"/>
-      <c r="H279" s="13"/>
-      <c r="I279" s="11"/>
+      <c r="G279" s="11"/>
+      <c r="H279" s="11"/>
+      <c r="I279" s="12"/>
       <c r="J279" s="11"/>
       <c r="K279" s="11"/>
       <c r="L279" s="11"/>
+      <c r="M279" s="11"/>
     </row>
     <row r="280">
       <c r="A280" s="11"/>
@@ -4255,12 +4536,13 @@
       <c r="D280" s="11"/>
       <c r="E280" s="11"/>
       <c r="F280" s="11"/>
-      <c r="G280" s="12"/>
-      <c r="H280" s="13"/>
-      <c r="I280" s="11"/>
+      <c r="G280" s="11"/>
+      <c r="H280" s="11"/>
+      <c r="I280" s="12"/>
       <c r="J280" s="11"/>
       <c r="K280" s="11"/>
       <c r="L280" s="11"/>
+      <c r="M280" s="11"/>
     </row>
     <row r="281">
       <c r="A281" s="11"/>
@@ -4269,12 +4551,13 @@
       <c r="D281" s="11"/>
       <c r="E281" s="11"/>
       <c r="F281" s="11"/>
-      <c r="G281" s="12"/>
-      <c r="H281" s="13"/>
-      <c r="I281" s="11"/>
+      <c r="G281" s="11"/>
+      <c r="H281" s="11"/>
+      <c r="I281" s="12"/>
       <c r="J281" s="11"/>
       <c r="K281" s="11"/>
       <c r="L281" s="11"/>
+      <c r="M281" s="11"/>
     </row>
     <row r="282">
       <c r="A282" s="11"/>
@@ -4283,12 +4566,13 @@
       <c r="D282" s="11"/>
       <c r="E282" s="11"/>
       <c r="F282" s="11"/>
-      <c r="G282" s="12"/>
-      <c r="H282" s="13"/>
-      <c r="I282" s="11"/>
+      <c r="G282" s="11"/>
+      <c r="H282" s="11"/>
+      <c r="I282" s="12"/>
       <c r="J282" s="11"/>
       <c r="K282" s="11"/>
       <c r="L282" s="11"/>
+      <c r="M282" s="11"/>
     </row>
     <row r="283">
       <c r="A283" s="11"/>
@@ -4297,12 +4581,13 @@
       <c r="D283" s="11"/>
       <c r="E283" s="11"/>
       <c r="F283" s="11"/>
-      <c r="G283" s="12"/>
-      <c r="H283" s="13"/>
-      <c r="I283" s="11"/>
+      <c r="G283" s="11"/>
+      <c r="H283" s="11"/>
+      <c r="I283" s="12"/>
       <c r="J283" s="11"/>
       <c r="K283" s="11"/>
       <c r="L283" s="11"/>
+      <c r="M283" s="11"/>
     </row>
     <row r="284">
       <c r="A284" s="11"/>
@@ -4311,12 +4596,13 @@
       <c r="D284" s="11"/>
       <c r="E284" s="11"/>
       <c r="F284" s="11"/>
-      <c r="G284" s="12"/>
-      <c r="H284" s="13"/>
-      <c r="I284" s="11"/>
+      <c r="G284" s="11"/>
+      <c r="H284" s="11"/>
+      <c r="I284" s="12"/>
       <c r="J284" s="11"/>
       <c r="K284" s="11"/>
       <c r="L284" s="11"/>
+      <c r="M284" s="11"/>
     </row>
     <row r="285">
       <c r="A285" s="11"/>
@@ -4325,12 +4611,13 @@
       <c r="D285" s="11"/>
       <c r="E285" s="11"/>
       <c r="F285" s="11"/>
-      <c r="G285" s="12"/>
-      <c r="H285" s="13"/>
-      <c r="I285" s="11"/>
+      <c r="G285" s="11"/>
+      <c r="H285" s="11"/>
+      <c r="I285" s="12"/>
       <c r="J285" s="11"/>
       <c r="K285" s="11"/>
       <c r="L285" s="11"/>
+      <c r="M285" s="11"/>
     </row>
     <row r="286">
       <c r="A286" s="11"/>
@@ -4339,12 +4626,13 @@
       <c r="D286" s="11"/>
       <c r="E286" s="11"/>
       <c r="F286" s="11"/>
-      <c r="G286" s="12"/>
-      <c r="H286" s="13"/>
-      <c r="I286" s="11"/>
+      <c r="G286" s="11"/>
+      <c r="H286" s="11"/>
+      <c r="I286" s="12"/>
       <c r="J286" s="11"/>
       <c r="K286" s="11"/>
       <c r="L286" s="11"/>
+      <c r="M286" s="11"/>
     </row>
     <row r="287">
       <c r="A287" s="11"/>
@@ -4353,12 +4641,13 @@
       <c r="D287" s="11"/>
       <c r="E287" s="11"/>
       <c r="F287" s="11"/>
-      <c r="G287" s="12"/>
-      <c r="H287" s="13"/>
-      <c r="I287" s="11"/>
+      <c r="G287" s="11"/>
+      <c r="H287" s="11"/>
+      <c r="I287" s="12"/>
       <c r="J287" s="11"/>
       <c r="K287" s="11"/>
       <c r="L287" s="11"/>
+      <c r="M287" s="11"/>
     </row>
     <row r="288">
       <c r="A288" s="11"/>
@@ -4367,12 +4656,13 @@
       <c r="D288" s="11"/>
       <c r="E288" s="11"/>
       <c r="F288" s="11"/>
-      <c r="G288" s="12"/>
-      <c r="H288" s="13"/>
-      <c r="I288" s="11"/>
+      <c r="G288" s="11"/>
+      <c r="H288" s="11"/>
+      <c r="I288" s="12"/>
       <c r="J288" s="11"/>
       <c r="K288" s="11"/>
       <c r="L288" s="11"/>
+      <c r="M288" s="11"/>
     </row>
     <row r="289">
       <c r="A289" s="11"/>
@@ -4381,12 +4671,13 @@
       <c r="D289" s="11"/>
       <c r="E289" s="11"/>
       <c r="F289" s="11"/>
-      <c r="G289" s="12"/>
-      <c r="H289" s="13"/>
-      <c r="I289" s="11"/>
+      <c r="G289" s="11"/>
+      <c r="H289" s="11"/>
+      <c r="I289" s="12"/>
       <c r="J289" s="11"/>
       <c r="K289" s="11"/>
       <c r="L289" s="11"/>
+      <c r="M289" s="11"/>
     </row>
     <row r="290">
       <c r="A290" s="11"/>
@@ -4395,12 +4686,13 @@
       <c r="D290" s="11"/>
       <c r="E290" s="11"/>
       <c r="F290" s="11"/>
-      <c r="G290" s="12"/>
-      <c r="H290" s="13"/>
-      <c r="I290" s="11"/>
+      <c r="G290" s="11"/>
+      <c r="H290" s="11"/>
+      <c r="I290" s="12"/>
       <c r="J290" s="11"/>
       <c r="K290" s="11"/>
       <c r="L290" s="11"/>
+      <c r="M290" s="11"/>
     </row>
     <row r="291">
       <c r="A291" s="11"/>
@@ -4409,12 +4701,13 @@
       <c r="D291" s="11"/>
       <c r="E291" s="11"/>
       <c r="F291" s="11"/>
-      <c r="G291" s="12"/>
-      <c r="H291" s="13"/>
-      <c r="I291" s="11"/>
+      <c r="G291" s="11"/>
+      <c r="H291" s="11"/>
+      <c r="I291" s="12"/>
       <c r="J291" s="11"/>
       <c r="K291" s="11"/>
       <c r="L291" s="11"/>
+      <c r="M291" s="11"/>
     </row>
     <row r="292">
       <c r="A292" s="11"/>
@@ -4423,12 +4716,13 @@
       <c r="D292" s="11"/>
       <c r="E292" s="11"/>
       <c r="F292" s="11"/>
-      <c r="G292" s="12"/>
-      <c r="H292" s="13"/>
-      <c r="I292" s="11"/>
+      <c r="G292" s="11"/>
+      <c r="H292" s="11"/>
+      <c r="I292" s="12"/>
       <c r="J292" s="11"/>
       <c r="K292" s="11"/>
       <c r="L292" s="11"/>
+      <c r="M292" s="11"/>
     </row>
     <row r="293">
       <c r="A293" s="11"/>
@@ -4437,12 +4731,13 @@
       <c r="D293" s="11"/>
       <c r="E293" s="11"/>
       <c r="F293" s="11"/>
-      <c r="G293" s="12"/>
-      <c r="H293" s="13"/>
-      <c r="I293" s="11"/>
+      <c r="G293" s="11"/>
+      <c r="H293" s="11"/>
+      <c r="I293" s="12"/>
       <c r="J293" s="11"/>
       <c r="K293" s="11"/>
       <c r="L293" s="11"/>
+      <c r="M293" s="11"/>
     </row>
     <row r="294">
       <c r="A294" s="11"/>
@@ -4451,12 +4746,13 @@
       <c r="D294" s="11"/>
       <c r="E294" s="11"/>
       <c r="F294" s="11"/>
-      <c r="G294" s="12"/>
-      <c r="H294" s="13"/>
-      <c r="I294" s="11"/>
+      <c r="G294" s="11"/>
+      <c r="H294" s="11"/>
+      <c r="I294" s="12"/>
       <c r="J294" s="11"/>
       <c r="K294" s="11"/>
       <c r="L294" s="11"/>
+      <c r="M294" s="11"/>
     </row>
     <row r="295">
       <c r="A295" s="11"/>
@@ -4465,12 +4761,13 @@
       <c r="D295" s="11"/>
       <c r="E295" s="11"/>
       <c r="F295" s="11"/>
-      <c r="G295" s="12"/>
-      <c r="H295" s="13"/>
-      <c r="I295" s="11"/>
+      <c r="G295" s="11"/>
+      <c r="H295" s="11"/>
+      <c r="I295" s="12"/>
       <c r="J295" s="11"/>
       <c r="K295" s="11"/>
       <c r="L295" s="11"/>
+      <c r="M295" s="11"/>
     </row>
     <row r="296">
       <c r="A296" s="11"/>
@@ -4479,12 +4776,13 @@
       <c r="D296" s="11"/>
       <c r="E296" s="11"/>
       <c r="F296" s="11"/>
-      <c r="G296" s="12"/>
-      <c r="H296" s="13"/>
-      <c r="I296" s="11"/>
+      <c r="G296" s="11"/>
+      <c r="H296" s="11"/>
+      <c r="I296" s="12"/>
       <c r="J296" s="11"/>
       <c r="K296" s="11"/>
       <c r="L296" s="11"/>
+      <c r="M296" s="11"/>
     </row>
     <row r="297">
       <c r="A297" s="11"/>
@@ -4493,12 +4791,13 @@
       <c r="D297" s="11"/>
       <c r="E297" s="11"/>
       <c r="F297" s="11"/>
-      <c r="G297" s="12"/>
-      <c r="H297" s="13"/>
-      <c r="I297" s="11"/>
+      <c r="G297" s="11"/>
+      <c r="H297" s="11"/>
+      <c r="I297" s="12"/>
       <c r="J297" s="11"/>
       <c r="K297" s="11"/>
       <c r="L297" s="11"/>
+      <c r="M297" s="11"/>
     </row>
     <row r="298">
       <c r="A298" s="11"/>
@@ -4507,12 +4806,13 @@
       <c r="D298" s="11"/>
       <c r="E298" s="11"/>
       <c r="F298" s="11"/>
-      <c r="G298" s="12"/>
-      <c r="H298" s="13"/>
-      <c r="I298" s="11"/>
+      <c r="G298" s="11"/>
+      <c r="H298" s="11"/>
+      <c r="I298" s="12"/>
       <c r="J298" s="11"/>
       <c r="K298" s="11"/>
       <c r="L298" s="11"/>
+      <c r="M298" s="11"/>
     </row>
     <row r="299">
       <c r="A299" s="11"/>
@@ -4521,12 +4821,13 @@
       <c r="D299" s="11"/>
       <c r="E299" s="11"/>
       <c r="F299" s="11"/>
-      <c r="G299" s="12"/>
-      <c r="H299" s="13"/>
-      <c r="I299" s="11"/>
+      <c r="G299" s="11"/>
+      <c r="H299" s="11"/>
+      <c r="I299" s="12"/>
       <c r="J299" s="11"/>
       <c r="K299" s="11"/>
       <c r="L299" s="11"/>
+      <c r="M299" s="11"/>
     </row>
     <row r="300">
       <c r="A300" s="11"/>
@@ -4535,12 +4836,13 @@
       <c r="D300" s="11"/>
       <c r="E300" s="11"/>
       <c r="F300" s="11"/>
-      <c r="G300" s="12"/>
-      <c r="H300" s="13"/>
-      <c r="I300" s="11"/>
+      <c r="G300" s="11"/>
+      <c r="H300" s="11"/>
+      <c r="I300" s="12"/>
       <c r="J300" s="11"/>
       <c r="K300" s="11"/>
       <c r="L300" s="11"/>
+      <c r="M300" s="11"/>
     </row>
     <row r="301">
       <c r="A301" s="11"/>
@@ -4549,12 +4851,13 @@
       <c r="D301" s="11"/>
       <c r="E301" s="11"/>
       <c r="F301" s="11"/>
-      <c r="G301" s="12"/>
-      <c r="H301" s="13"/>
-      <c r="I301" s="11"/>
+      <c r="G301" s="11"/>
+      <c r="H301" s="11"/>
+      <c r="I301" s="12"/>
       <c r="J301" s="11"/>
       <c r="K301" s="11"/>
       <c r="L301" s="11"/>
+      <c r="M301" s="11"/>
     </row>
     <row r="302">
       <c r="A302" s="11"/>
@@ -4563,12 +4866,13 @@
       <c r="D302" s="11"/>
       <c r="E302" s="11"/>
       <c r="F302" s="11"/>
-      <c r="G302" s="12"/>
-      <c r="H302" s="13"/>
-      <c r="I302" s="11"/>
+      <c r="G302" s="11"/>
+      <c r="H302" s="11"/>
+      <c r="I302" s="12"/>
       <c r="J302" s="11"/>
       <c r="K302" s="11"/>
       <c r="L302" s="11"/>
+      <c r="M302" s="11"/>
     </row>
     <row r="303">
       <c r="A303" s="11"/>
@@ -4577,12 +4881,13 @@
       <c r="D303" s="11"/>
       <c r="E303" s="11"/>
       <c r="F303" s="11"/>
-      <c r="G303" s="12"/>
-      <c r="H303" s="13"/>
-      <c r="I303" s="11"/>
+      <c r="G303" s="11"/>
+      <c r="H303" s="11"/>
+      <c r="I303" s="12"/>
       <c r="J303" s="11"/>
       <c r="K303" s="11"/>
       <c r="L303" s="11"/>
+      <c r="M303" s="11"/>
     </row>
     <row r="304">
       <c r="A304" s="11"/>
@@ -4591,12 +4896,13 @@
       <c r="D304" s="11"/>
       <c r="E304" s="11"/>
       <c r="F304" s="11"/>
-      <c r="G304" s="12"/>
-      <c r="H304" s="13"/>
-      <c r="I304" s="11"/>
+      <c r="G304" s="11"/>
+      <c r="H304" s="11"/>
+      <c r="I304" s="12"/>
       <c r="J304" s="11"/>
       <c r="K304" s="11"/>
       <c r="L304" s="11"/>
+      <c r="M304" s="11"/>
     </row>
     <row r="305">
       <c r="A305" s="11"/>
@@ -4605,12 +4911,13 @@
       <c r="D305" s="11"/>
       <c r="E305" s="11"/>
       <c r="F305" s="11"/>
-      <c r="G305" s="12"/>
-      <c r="H305" s="13"/>
-      <c r="I305" s="11"/>
+      <c r="G305" s="11"/>
+      <c r="H305" s="11"/>
+      <c r="I305" s="12"/>
       <c r="J305" s="11"/>
       <c r="K305" s="11"/>
       <c r="L305" s="11"/>
+      <c r="M305" s="11"/>
     </row>
     <row r="306">
       <c r="A306" s="11"/>
@@ -4619,12 +4926,13 @@
       <c r="D306" s="11"/>
       <c r="E306" s="11"/>
       <c r="F306" s="11"/>
-      <c r="G306" s="12"/>
-      <c r="H306" s="13"/>
-      <c r="I306" s="11"/>
+      <c r="G306" s="11"/>
+      <c r="H306" s="11"/>
+      <c r="I306" s="12"/>
       <c r="J306" s="11"/>
       <c r="K306" s="11"/>
       <c r="L306" s="11"/>
+      <c r="M306" s="11"/>
     </row>
     <row r="307">
       <c r="A307" s="11"/>
@@ -4633,12 +4941,13 @@
       <c r="D307" s="11"/>
       <c r="E307" s="11"/>
       <c r="F307" s="11"/>
-      <c r="G307" s="12"/>
-      <c r="H307" s="13"/>
-      <c r="I307" s="11"/>
+      <c r="G307" s="11"/>
+      <c r="H307" s="11"/>
+      <c r="I307" s="12"/>
       <c r="J307" s="11"/>
       <c r="K307" s="11"/>
       <c r="L307" s="11"/>
+      <c r="M307" s="11"/>
     </row>
     <row r="308">
       <c r="A308" s="11"/>
@@ -4647,12 +4956,13 @@
       <c r="D308" s="11"/>
       <c r="E308" s="11"/>
       <c r="F308" s="11"/>
-      <c r="G308" s="12"/>
-      <c r="H308" s="13"/>
-      <c r="I308" s="11"/>
+      <c r="G308" s="11"/>
+      <c r="H308" s="11"/>
+      <c r="I308" s="12"/>
       <c r="J308" s="11"/>
       <c r="K308" s="11"/>
       <c r="L308" s="11"/>
+      <c r="M308" s="11"/>
     </row>
     <row r="309">
       <c r="A309" s="11"/>
@@ -4661,12 +4971,13 @@
       <c r="D309" s="11"/>
       <c r="E309" s="11"/>
       <c r="F309" s="11"/>
-      <c r="G309" s="12"/>
-      <c r="H309" s="13"/>
-      <c r="I309" s="11"/>
+      <c r="G309" s="11"/>
+      <c r="H309" s="11"/>
+      <c r="I309" s="12"/>
       <c r="J309" s="11"/>
       <c r="K309" s="11"/>
       <c r="L309" s="11"/>
+      <c r="M309" s="11"/>
     </row>
     <row r="310">
       <c r="A310" s="11"/>
@@ -4675,12 +4986,13 @@
       <c r="D310" s="11"/>
       <c r="E310" s="11"/>
       <c r="F310" s="11"/>
-      <c r="G310" s="12"/>
-      <c r="H310" s="13"/>
-      <c r="I310" s="11"/>
+      <c r="G310" s="11"/>
+      <c r="H310" s="11"/>
+      <c r="I310" s="12"/>
       <c r="J310" s="11"/>
       <c r="K310" s="11"/>
       <c r="L310" s="11"/>
+      <c r="M310" s="11"/>
     </row>
     <row r="311">
       <c r="A311" s="11"/>
@@ -4689,12 +5001,13 @@
       <c r="D311" s="11"/>
       <c r="E311" s="11"/>
       <c r="F311" s="11"/>
-      <c r="G311" s="12"/>
-      <c r="H311" s="13"/>
-      <c r="I311" s="11"/>
+      <c r="G311" s="11"/>
+      <c r="H311" s="11"/>
+      <c r="I311" s="12"/>
       <c r="J311" s="11"/>
       <c r="K311" s="11"/>
       <c r="L311" s="11"/>
+      <c r="M311" s="11"/>
     </row>
     <row r="312">
       <c r="A312" s="11"/>
@@ -4703,12 +5016,13 @@
       <c r="D312" s="11"/>
       <c r="E312" s="11"/>
       <c r="F312" s="11"/>
-      <c r="G312" s="12"/>
-      <c r="H312" s="13"/>
-      <c r="I312" s="11"/>
+      <c r="G312" s="11"/>
+      <c r="H312" s="11"/>
+      <c r="I312" s="12"/>
       <c r="J312" s="11"/>
       <c r="K312" s="11"/>
       <c r="L312" s="11"/>
+      <c r="M312" s="11"/>
     </row>
     <row r="313">
       <c r="A313" s="11"/>
@@ -4717,12 +5031,13 @@
       <c r="D313" s="11"/>
       <c r="E313" s="11"/>
       <c r="F313" s="11"/>
-      <c r="G313" s="12"/>
-      <c r="H313" s="13"/>
-      <c r="I313" s="11"/>
+      <c r="G313" s="11"/>
+      <c r="H313" s="11"/>
+      <c r="I313" s="12"/>
       <c r="J313" s="11"/>
       <c r="K313" s="11"/>
       <c r="L313" s="11"/>
+      <c r="M313" s="11"/>
     </row>
     <row r="314">
       <c r="A314" s="11"/>
@@ -4731,12 +5046,13 @@
       <c r="D314" s="11"/>
       <c r="E314" s="11"/>
       <c r="F314" s="11"/>
-      <c r="G314" s="12"/>
-      <c r="H314" s="13"/>
-      <c r="I314" s="11"/>
+      <c r="G314" s="11"/>
+      <c r="H314" s="11"/>
+      <c r="I314" s="12"/>
       <c r="J314" s="11"/>
       <c r="K314" s="11"/>
       <c r="L314" s="11"/>
+      <c r="M314" s="11"/>
     </row>
     <row r="315">
       <c r="A315" s="11"/>
@@ -4745,12 +5061,13 @@
       <c r="D315" s="11"/>
       <c r="E315" s="11"/>
       <c r="F315" s="11"/>
-      <c r="G315" s="12"/>
-      <c r="H315" s="13"/>
-      <c r="I315" s="11"/>
+      <c r="G315" s="11"/>
+      <c r="H315" s="11"/>
+      <c r="I315" s="12"/>
       <c r="J315" s="11"/>
       <c r="K315" s="11"/>
       <c r="L315" s="11"/>
+      <c r="M315" s="11"/>
     </row>
     <row r="316">
       <c r="A316" s="11"/>
@@ -4759,12 +5076,13 @@
       <c r="D316" s="11"/>
       <c r="E316" s="11"/>
       <c r="F316" s="11"/>
-      <c r="G316" s="12"/>
-      <c r="H316" s="13"/>
-      <c r="I316" s="11"/>
+      <c r="G316" s="11"/>
+      <c r="H316" s="11"/>
+      <c r="I316" s="12"/>
       <c r="J316" s="11"/>
       <c r="K316" s="11"/>
       <c r="L316" s="11"/>
+      <c r="M316" s="11"/>
     </row>
     <row r="317">
       <c r="A317" s="11"/>
@@ -4773,12 +5091,13 @@
       <c r="D317" s="11"/>
       <c r="E317" s="11"/>
       <c r="F317" s="11"/>
-      <c r="G317" s="12"/>
-      <c r="H317" s="13"/>
-      <c r="I317" s="11"/>
+      <c r="G317" s="11"/>
+      <c r="H317" s="11"/>
+      <c r="I317" s="12"/>
       <c r="J317" s="11"/>
       <c r="K317" s="11"/>
       <c r="L317" s="11"/>
+      <c r="M317" s="11"/>
     </row>
     <row r="318">
       <c r="A318" s="11"/>
@@ -4787,12 +5106,13 @@
       <c r="D318" s="11"/>
       <c r="E318" s="11"/>
       <c r="F318" s="11"/>
-      <c r="G318" s="12"/>
-      <c r="H318" s="13"/>
-      <c r="I318" s="11"/>
+      <c r="G318" s="11"/>
+      <c r="H318" s="11"/>
+      <c r="I318" s="12"/>
       <c r="J318" s="11"/>
       <c r="K318" s="11"/>
       <c r="L318" s="11"/>
+      <c r="M318" s="11"/>
     </row>
     <row r="319">
       <c r="A319" s="11"/>
@@ -4801,12 +5121,13 @@
       <c r="D319" s="11"/>
       <c r="E319" s="11"/>
       <c r="F319" s="11"/>
-      <c r="G319" s="12"/>
-      <c r="H319" s="13"/>
-      <c r="I319" s="11"/>
+      <c r="G319" s="11"/>
+      <c r="H319" s="11"/>
+      <c r="I319" s="12"/>
       <c r="J319" s="11"/>
       <c r="K319" s="11"/>
       <c r="L319" s="11"/>
+      <c r="M319" s="11"/>
     </row>
     <row r="320">
       <c r="A320" s="11"/>
@@ -4815,12 +5136,13 @@
       <c r="D320" s="11"/>
       <c r="E320" s="11"/>
       <c r="F320" s="11"/>
-      <c r="G320" s="12"/>
-      <c r="H320" s="13"/>
-      <c r="I320" s="11"/>
+      <c r="G320" s="11"/>
+      <c r="H320" s="11"/>
+      <c r="I320" s="12"/>
       <c r="J320" s="11"/>
       <c r="K320" s="11"/>
       <c r="L320" s="11"/>
+      <c r="M320" s="11"/>
     </row>
     <row r="321">
       <c r="A321" s="11"/>
@@ -4829,12 +5151,13 @@
       <c r="D321" s="11"/>
       <c r="E321" s="11"/>
       <c r="F321" s="11"/>
-      <c r="G321" s="12"/>
-      <c r="H321" s="13"/>
-      <c r="I321" s="11"/>
+      <c r="G321" s="11"/>
+      <c r="H321" s="11"/>
+      <c r="I321" s="12"/>
       <c r="J321" s="11"/>
       <c r="K321" s="11"/>
       <c r="L321" s="11"/>
+      <c r="M321" s="11"/>
     </row>
     <row r="322">
       <c r="A322" s="11"/>
@@ -4843,12 +5166,13 @@
       <c r="D322" s="11"/>
       <c r="E322" s="11"/>
       <c r="F322" s="11"/>
-      <c r="G322" s="12"/>
-      <c r="H322" s="13"/>
-      <c r="I322" s="11"/>
+      <c r="G322" s="11"/>
+      <c r="H322" s="11"/>
+      <c r="I322" s="12"/>
       <c r="J322" s="11"/>
       <c r="K322" s="11"/>
       <c r="L322" s="11"/>
+      <c r="M322" s="11"/>
     </row>
     <row r="323">
       <c r="A323" s="11"/>
@@ -4857,12 +5181,13 @@
       <c r="D323" s="11"/>
       <c r="E323" s="11"/>
       <c r="F323" s="11"/>
-      <c r="G323" s="12"/>
-      <c r="H323" s="13"/>
-      <c r="I323" s="11"/>
+      <c r="G323" s="11"/>
+      <c r="H323" s="11"/>
+      <c r="I323" s="12"/>
       <c r="J323" s="11"/>
       <c r="K323" s="11"/>
       <c r="L323" s="11"/>
+      <c r="M323" s="11"/>
     </row>
     <row r="324">
       <c r="A324" s="11"/>
@@ -4871,12 +5196,13 @@
       <c r="D324" s="11"/>
       <c r="E324" s="11"/>
       <c r="F324" s="11"/>
-      <c r="G324" s="12"/>
-      <c r="H324" s="13"/>
-      <c r="I324" s="11"/>
+      <c r="G324" s="11"/>
+      <c r="H324" s="11"/>
+      <c r="I324" s="12"/>
       <c r="J324" s="11"/>
       <c r="K324" s="11"/>
       <c r="L324" s="11"/>
+      <c r="M324" s="11"/>
     </row>
     <row r="325">
       <c r="A325" s="11"/>
@@ -4885,12 +5211,13 @@
       <c r="D325" s="11"/>
       <c r="E325" s="11"/>
       <c r="F325" s="11"/>
-      <c r="G325" s="12"/>
-      <c r="H325" s="13"/>
-      <c r="I325" s="11"/>
+      <c r="G325" s="11"/>
+      <c r="H325" s="11"/>
+      <c r="I325" s="12"/>
       <c r="J325" s="11"/>
       <c r="K325" s="11"/>
       <c r="L325" s="11"/>
+      <c r="M325" s="11"/>
     </row>
     <row r="326">
       <c r="A326" s="11"/>
@@ -4899,12 +5226,13 @@
       <c r="D326" s="11"/>
       <c r="E326" s="11"/>
       <c r="F326" s="11"/>
-      <c r="G326" s="12"/>
-      <c r="H326" s="13"/>
-      <c r="I326" s="11"/>
+      <c r="G326" s="11"/>
+      <c r="H326" s="11"/>
+      <c r="I326" s="12"/>
       <c r="J326" s="11"/>
       <c r="K326" s="11"/>
       <c r="L326" s="11"/>
+      <c r="M326" s="11"/>
     </row>
     <row r="327">
       <c r="A327" s="11"/>
@@ -4913,12 +5241,13 @@
       <c r="D327" s="11"/>
       <c r="E327" s="11"/>
       <c r="F327" s="11"/>
-      <c r="G327" s="12"/>
-      <c r="H327" s="13"/>
-      <c r="I327" s="11"/>
+      <c r="G327" s="11"/>
+      <c r="H327" s="11"/>
+      <c r="I327" s="12"/>
       <c r="J327" s="11"/>
       <c r="K327" s="11"/>
       <c r="L327" s="11"/>
+      <c r="M327" s="11"/>
     </row>
     <row r="328">
       <c r="A328" s="11"/>
@@ -4927,12 +5256,13 @@
       <c r="D328" s="11"/>
       <c r="E328" s="11"/>
       <c r="F328" s="11"/>
-      <c r="G328" s="12"/>
-      <c r="H328" s="13"/>
-      <c r="I328" s="11"/>
+      <c r="G328" s="11"/>
+      <c r="H328" s="11"/>
+      <c r="I328" s="12"/>
       <c r="J328" s="11"/>
       <c r="K328" s="11"/>
       <c r="L328" s="11"/>
+      <c r="M328" s="11"/>
     </row>
     <row r="329">
       <c r="A329" s="11"/>
@@ -4941,12 +5271,13 @@
       <c r="D329" s="11"/>
       <c r="E329" s="11"/>
       <c r="F329" s="11"/>
-      <c r="G329" s="12"/>
-      <c r="H329" s="13"/>
-      <c r="I329" s="11"/>
+      <c r="G329" s="11"/>
+      <c r="H329" s="11"/>
+      <c r="I329" s="12"/>
       <c r="J329" s="11"/>
       <c r="K329" s="11"/>
       <c r="L329" s="11"/>
+      <c r="M329" s="11"/>
     </row>
     <row r="330">
       <c r="A330" s="11"/>
@@ -4955,12 +5286,13 @@
       <c r="D330" s="11"/>
       <c r="E330" s="11"/>
       <c r="F330" s="11"/>
-      <c r="G330" s="12"/>
-      <c r="H330" s="13"/>
-      <c r="I330" s="11"/>
+      <c r="G330" s="11"/>
+      <c r="H330" s="11"/>
+      <c r="I330" s="12"/>
       <c r="J330" s="11"/>
       <c r="K330" s="11"/>
       <c r="L330" s="11"/>
+      <c r="M330" s="11"/>
     </row>
     <row r="331">
       <c r="A331" s="11"/>
@@ -4969,12 +5301,13 @@
       <c r="D331" s="11"/>
       <c r="E331" s="11"/>
       <c r="F331" s="11"/>
-      <c r="G331" s="12"/>
-      <c r="H331" s="13"/>
-      <c r="I331" s="11"/>
+      <c r="G331" s="11"/>
+      <c r="H331" s="11"/>
+      <c r="I331" s="12"/>
       <c r="J331" s="11"/>
       <c r="K331" s="11"/>
       <c r="L331" s="11"/>
+      <c r="M331" s="11"/>
     </row>
     <row r="332">
       <c r="A332" s="11"/>
@@ -4983,12 +5316,13 @@
       <c r="D332" s="11"/>
       <c r="E332" s="11"/>
       <c r="F332" s="11"/>
-      <c r="G332" s="12"/>
-      <c r="H332" s="13"/>
-      <c r="I332" s="11"/>
+      <c r="G332" s="11"/>
+      <c r="H332" s="11"/>
+      <c r="I332" s="12"/>
       <c r="J332" s="11"/>
       <c r="K332" s="11"/>
       <c r="L332" s="11"/>
+      <c r="M332" s="11"/>
     </row>
     <row r="333">
       <c r="A333" s="11"/>
@@ -4997,12 +5331,13 @@
       <c r="D333" s="11"/>
       <c r="E333" s="11"/>
       <c r="F333" s="11"/>
-      <c r="G333" s="12"/>
-      <c r="H333" s="13"/>
-      <c r="I333" s="11"/>
+      <c r="G333" s="11"/>
+      <c r="H333" s="11"/>
+      <c r="I333" s="12"/>
       <c r="J333" s="11"/>
       <c r="K333" s="11"/>
       <c r="L333" s="11"/>
+      <c r="M333" s="11"/>
     </row>
     <row r="334">
       <c r="A334" s="11"/>
@@ -5011,12 +5346,13 @@
       <c r="D334" s="11"/>
       <c r="E334" s="11"/>
       <c r="F334" s="11"/>
-      <c r="G334" s="12"/>
-      <c r="H334" s="13"/>
-      <c r="I334" s="11"/>
+      <c r="G334" s="11"/>
+      <c r="H334" s="11"/>
+      <c r="I334" s="12"/>
       <c r="J334" s="11"/>
       <c r="K334" s="11"/>
       <c r="L334" s="11"/>
+      <c r="M334" s="11"/>
     </row>
     <row r="335">
       <c r="A335" s="11"/>
@@ -5025,12 +5361,13 @@
       <c r="D335" s="11"/>
       <c r="E335" s="11"/>
       <c r="F335" s="11"/>
-      <c r="G335" s="12"/>
-      <c r="H335" s="13"/>
-      <c r="I335" s="11"/>
+      <c r="G335" s="11"/>
+      <c r="H335" s="11"/>
+      <c r="I335" s="12"/>
       <c r="J335" s="11"/>
       <c r="K335" s="11"/>
       <c r="L335" s="11"/>
+      <c r="M335" s="11"/>
     </row>
     <row r="336">
       <c r="A336" s="11"/>
@@ -5039,12 +5376,13 @@
       <c r="D336" s="11"/>
       <c r="E336" s="11"/>
       <c r="F336" s="11"/>
-      <c r="G336" s="12"/>
-      <c r="H336" s="13"/>
-      <c r="I336" s="11"/>
+      <c r="G336" s="11"/>
+      <c r="H336" s="11"/>
+      <c r="I336" s="12"/>
       <c r="J336" s="11"/>
       <c r="K336" s="11"/>
       <c r="L336" s="11"/>
+      <c r="M336" s="11"/>
     </row>
     <row r="337">
       <c r="A337" s="11"/>
@@ -5053,12 +5391,13 @@
       <c r="D337" s="11"/>
       <c r="E337" s="11"/>
       <c r="F337" s="11"/>
-      <c r="G337" s="12"/>
-      <c r="H337" s="13"/>
-      <c r="I337" s="11"/>
+      <c r="G337" s="11"/>
+      <c r="H337" s="11"/>
+      <c r="I337" s="12"/>
       <c r="J337" s="11"/>
       <c r="K337" s="11"/>
       <c r="L337" s="11"/>
+      <c r="M337" s="11"/>
     </row>
     <row r="338">
       <c r="A338" s="11"/>
@@ -5067,12 +5406,13 @@
       <c r="D338" s="11"/>
       <c r="E338" s="11"/>
       <c r="F338" s="11"/>
-      <c r="G338" s="12"/>
-      <c r="H338" s="13"/>
-      <c r="I338" s="11"/>
+      <c r="G338" s="11"/>
+      <c r="H338" s="11"/>
+      <c r="I338" s="12"/>
       <c r="J338" s="11"/>
       <c r="K338" s="11"/>
       <c r="L338" s="11"/>
+      <c r="M338" s="11"/>
     </row>
     <row r="339">
       <c r="A339" s="11"/>
@@ -5081,12 +5421,13 @@
       <c r="D339" s="11"/>
       <c r="E339" s="11"/>
       <c r="F339" s="11"/>
-      <c r="G339" s="12"/>
-      <c r="H339" s="13"/>
-      <c r="I339" s="11"/>
+      <c r="G339" s="11"/>
+      <c r="H339" s="11"/>
+      <c r="I339" s="12"/>
       <c r="J339" s="11"/>
       <c r="K339" s="11"/>
       <c r="L339" s="11"/>
+      <c r="M339" s="11"/>
     </row>
     <row r="340">
       <c r="A340" s="11"/>
@@ -5095,12 +5436,13 @@
       <c r="D340" s="11"/>
       <c r="E340" s="11"/>
       <c r="F340" s="11"/>
-      <c r="G340" s="12"/>
-      <c r="H340" s="13"/>
-      <c r="I340" s="11"/>
+      <c r="G340" s="11"/>
+      <c r="H340" s="11"/>
+      <c r="I340" s="12"/>
       <c r="J340" s="11"/>
       <c r="K340" s="11"/>
       <c r="L340" s="11"/>
+      <c r="M340" s="11"/>
     </row>
     <row r="341">
       <c r="A341" s="11"/>
@@ -5109,12 +5451,13 @@
       <c r="D341" s="11"/>
       <c r="E341" s="11"/>
       <c r="F341" s="11"/>
-      <c r="G341" s="12"/>
-      <c r="H341" s="13"/>
-      <c r="I341" s="11"/>
+      <c r="G341" s="11"/>
+      <c r="H341" s="11"/>
+      <c r="I341" s="12"/>
       <c r="J341" s="11"/>
       <c r="K341" s="11"/>
       <c r="L341" s="11"/>
+      <c r="M341" s="11"/>
     </row>
     <row r="342">
       <c r="A342" s="11"/>
@@ -5123,12 +5466,13 @@
       <c r="D342" s="11"/>
       <c r="E342" s="11"/>
       <c r="F342" s="11"/>
-      <c r="G342" s="12"/>
-      <c r="H342" s="13"/>
-      <c r="I342" s="11"/>
+      <c r="G342" s="11"/>
+      <c r="H342" s="11"/>
+      <c r="I342" s="12"/>
       <c r="J342" s="11"/>
       <c r="K342" s="11"/>
       <c r="L342" s="11"/>
+      <c r="M342" s="11"/>
     </row>
     <row r="343">
       <c r="A343" s="11"/>
@@ -5137,12 +5481,13 @@
       <c r="D343" s="11"/>
       <c r="E343" s="11"/>
       <c r="F343" s="11"/>
-      <c r="G343" s="12"/>
-      <c r="H343" s="13"/>
-      <c r="I343" s="11"/>
+      <c r="G343" s="11"/>
+      <c r="H343" s="11"/>
+      <c r="I343" s="12"/>
       <c r="J343" s="11"/>
       <c r="K343" s="11"/>
       <c r="L343" s="11"/>
+      <c r="M343" s="11"/>
     </row>
     <row r="344">
       <c r="A344" s="11"/>
@@ -5151,12 +5496,13 @@
       <c r="D344" s="11"/>
       <c r="E344" s="11"/>
       <c r="F344" s="11"/>
-      <c r="G344" s="12"/>
-      <c r="H344" s="13"/>
-      <c r="I344" s="11"/>
+      <c r="G344" s="11"/>
+      <c r="H344" s="11"/>
+      <c r="I344" s="12"/>
       <c r="J344" s="11"/>
       <c r="K344" s="11"/>
       <c r="L344" s="11"/>
+      <c r="M344" s="11"/>
     </row>
     <row r="345">
       <c r="A345" s="11"/>
@@ -5165,12 +5511,13 @@
       <c r="D345" s="11"/>
       <c r="E345" s="11"/>
       <c r="F345" s="11"/>
-      <c r="G345" s="12"/>
-      <c r="H345" s="13"/>
-      <c r="I345" s="11"/>
+      <c r="G345" s="11"/>
+      <c r="H345" s="11"/>
+      <c r="I345" s="12"/>
       <c r="J345" s="11"/>
       <c r="K345" s="11"/>
       <c r="L345" s="11"/>
+      <c r="M345" s="11"/>
     </row>
     <row r="346">
       <c r="A346" s="11"/>
@@ -5179,12 +5526,13 @@
       <c r="D346" s="11"/>
       <c r="E346" s="11"/>
       <c r="F346" s="11"/>
-      <c r="G346" s="12"/>
-      <c r="H346" s="13"/>
-      <c r="I346" s="11"/>
+      <c r="G346" s="11"/>
+      <c r="H346" s="11"/>
+      <c r="I346" s="12"/>
       <c r="J346" s="11"/>
       <c r="K346" s="11"/>
       <c r="L346" s="11"/>
+      <c r="M346" s="11"/>
     </row>
     <row r="347">
       <c r="A347" s="11"/>
@@ -5193,12 +5541,13 @@
       <c r="D347" s="11"/>
       <c r="E347" s="11"/>
       <c r="F347" s="11"/>
-      <c r="G347" s="12"/>
-      <c r="H347" s="13"/>
-      <c r="I347" s="11"/>
+      <c r="G347" s="11"/>
+      <c r="H347" s="11"/>
+      <c r="I347" s="12"/>
       <c r="J347" s="11"/>
       <c r="K347" s="11"/>
       <c r="L347" s="11"/>
+      <c r="M347" s="11"/>
     </row>
     <row r="348">
       <c r="A348" s="11"/>
@@ -5207,12 +5556,13 @@
       <c r="D348" s="11"/>
       <c r="E348" s="11"/>
       <c r="F348" s="11"/>
-      <c r="G348" s="12"/>
-      <c r="H348" s="13"/>
-      <c r="I348" s="11"/>
+      <c r="G348" s="11"/>
+      <c r="H348" s="11"/>
+      <c r="I348" s="12"/>
       <c r="J348" s="11"/>
       <c r="K348" s="11"/>
       <c r="L348" s="11"/>
+      <c r="M348" s="11"/>
     </row>
     <row r="349">
       <c r="A349" s="11"/>
@@ -5221,12 +5571,13 @@
       <c r="D349" s="11"/>
       <c r="E349" s="11"/>
       <c r="F349" s="11"/>
-      <c r="G349" s="12"/>
-      <c r="H349" s="13"/>
-      <c r="I349" s="11"/>
+      <c r="G349" s="11"/>
+      <c r="H349" s="11"/>
+      <c r="I349" s="12"/>
       <c r="J349" s="11"/>
       <c r="K349" s="11"/>
       <c r="L349" s="11"/>
+      <c r="M349" s="11"/>
     </row>
     <row r="350">
       <c r="A350" s="11"/>
@@ -5235,12 +5586,13 @@
       <c r="D350" s="11"/>
       <c r="E350" s="11"/>
       <c r="F350" s="11"/>
-      <c r="G350" s="12"/>
-      <c r="H350" s="13"/>
-      <c r="I350" s="11"/>
+      <c r="G350" s="11"/>
+      <c r="H350" s="11"/>
+      <c r="I350" s="12"/>
       <c r="J350" s="11"/>
       <c r="K350" s="11"/>
       <c r="L350" s="11"/>
+      <c r="M350" s="11"/>
     </row>
     <row r="351">
       <c r="A351" s="11"/>
@@ -5249,12 +5601,13 @@
       <c r="D351" s="11"/>
       <c r="E351" s="11"/>
       <c r="F351" s="11"/>
-      <c r="G351" s="12"/>
-      <c r="H351" s="13"/>
-      <c r="I351" s="11"/>
+      <c r="G351" s="11"/>
+      <c r="H351" s="11"/>
+      <c r="I351" s="12"/>
       <c r="J351" s="11"/>
       <c r="K351" s="11"/>
       <c r="L351" s="11"/>
+      <c r="M351" s="11"/>
     </row>
     <row r="352">
       <c r="A352" s="11"/>
@@ -5263,12 +5616,13 @@
       <c r="D352" s="11"/>
       <c r="E352" s="11"/>
       <c r="F352" s="11"/>
-      <c r="G352" s="12"/>
-      <c r="H352" s="13"/>
-      <c r="I352" s="11"/>
+      <c r="G352" s="11"/>
+      <c r="H352" s="11"/>
+      <c r="I352" s="12"/>
       <c r="J352" s="11"/>
       <c r="K352" s="11"/>
       <c r="L352" s="11"/>
+      <c r="M352" s="11"/>
     </row>
     <row r="353">
       <c r="A353" s="11"/>
@@ -5277,12 +5631,13 @@
       <c r="D353" s="11"/>
       <c r="E353" s="11"/>
       <c r="F353" s="11"/>
-      <c r="G353" s="12"/>
-      <c r="H353" s="13"/>
-      <c r="I353" s="11"/>
+      <c r="G353" s="11"/>
+      <c r="H353" s="11"/>
+      <c r="I353" s="12"/>
       <c r="J353" s="11"/>
       <c r="K353" s="11"/>
       <c r="L353" s="11"/>
+      <c r="M353" s="11"/>
     </row>
     <row r="354">
       <c r="A354" s="11"/>
@@ -5291,12 +5646,13 @@
       <c r="D354" s="11"/>
       <c r="E354" s="11"/>
       <c r="F354" s="11"/>
-      <c r="G354" s="12"/>
-      <c r="H354" s="13"/>
-      <c r="I354" s="11"/>
+      <c r="G354" s="11"/>
+      <c r="H354" s="11"/>
+      <c r="I354" s="12"/>
       <c r="J354" s="11"/>
       <c r="K354" s="11"/>
       <c r="L354" s="11"/>
+      <c r="M354" s="11"/>
     </row>
     <row r="355">
       <c r="A355" s="11"/>
@@ -5305,12 +5661,13 @@
       <c r="D355" s="11"/>
       <c r="E355" s="11"/>
       <c r="F355" s="11"/>
-      <c r="G355" s="12"/>
-      <c r="H355" s="13"/>
-      <c r="I355" s="11"/>
+      <c r="G355" s="11"/>
+      <c r="H355" s="11"/>
+      <c r="I355" s="12"/>
       <c r="J355" s="11"/>
       <c r="K355" s="11"/>
       <c r="L355" s="11"/>
+      <c r="M355" s="11"/>
     </row>
     <row r="356">
       <c r="A356" s="11"/>
@@ -5319,12 +5676,13 @@
       <c r="D356" s="11"/>
       <c r="E356" s="11"/>
       <c r="F356" s="11"/>
-      <c r="G356" s="12"/>
-      <c r="H356" s="13"/>
-      <c r="I356" s="11"/>
+      <c r="G356" s="11"/>
+      <c r="H356" s="11"/>
+      <c r="I356" s="12"/>
       <c r="J356" s="11"/>
       <c r="K356" s="11"/>
       <c r="L356" s="11"/>
+      <c r="M356" s="11"/>
     </row>
     <row r="357">
       <c r="A357" s="11"/>
@@ -5333,12 +5691,13 @@
       <c r="D357" s="11"/>
       <c r="E357" s="11"/>
       <c r="F357" s="11"/>
-      <c r="G357" s="12"/>
-      <c r="H357" s="13"/>
-      <c r="I357" s="11"/>
+      <c r="G357" s="11"/>
+      <c r="H357" s="11"/>
+      <c r="I357" s="12"/>
       <c r="J357" s="11"/>
       <c r="K357" s="11"/>
       <c r="L357" s="11"/>
+      <c r="M357" s="11"/>
     </row>
     <row r="358">
       <c r="A358" s="11"/>
@@ -5347,12 +5706,13 @@
       <c r="D358" s="11"/>
       <c r="E358" s="11"/>
       <c r="F358" s="11"/>
-      <c r="G358" s="12"/>
-      <c r="H358" s="13"/>
-      <c r="I358" s="11"/>
+      <c r="G358" s="11"/>
+      <c r="H358" s="11"/>
+      <c r="I358" s="12"/>
       <c r="J358" s="11"/>
       <c r="K358" s="11"/>
       <c r="L358" s="11"/>
+      <c r="M358" s="11"/>
     </row>
     <row r="359">
       <c r="A359" s="11"/>
@@ -5361,12 +5721,13 @@
       <c r="D359" s="11"/>
       <c r="E359" s="11"/>
       <c r="F359" s="11"/>
-      <c r="G359" s="12"/>
-      <c r="H359" s="13"/>
-      <c r="I359" s="11"/>
+      <c r="G359" s="11"/>
+      <c r="H359" s="11"/>
+      <c r="I359" s="12"/>
       <c r="J359" s="11"/>
       <c r="K359" s="11"/>
       <c r="L359" s="11"/>
+      <c r="M359" s="11"/>
     </row>
     <row r="360">
       <c r="A360" s="11"/>
@@ -5375,12 +5736,13 @@
       <c r="D360" s="11"/>
       <c r="E360" s="11"/>
       <c r="F360" s="11"/>
-      <c r="G360" s="12"/>
-      <c r="H360" s="13"/>
-      <c r="I360" s="11"/>
+      <c r="G360" s="11"/>
+      <c r="H360" s="11"/>
+      <c r="I360" s="12"/>
       <c r="J360" s="11"/>
       <c r="K360" s="11"/>
       <c r="L360" s="11"/>
+      <c r="M360" s="11"/>
     </row>
     <row r="361">
       <c r="A361" s="11"/>
@@ -5389,12 +5751,13 @@
       <c r="D361" s="11"/>
       <c r="E361" s="11"/>
       <c r="F361" s="11"/>
-      <c r="G361" s="12"/>
-      <c r="H361" s="13"/>
-      <c r="I361" s="11"/>
+      <c r="G361" s="11"/>
+      <c r="H361" s="11"/>
+      <c r="I361" s="12"/>
       <c r="J361" s="11"/>
       <c r="K361" s="11"/>
       <c r="L361" s="11"/>
+      <c r="M361" s="11"/>
     </row>
     <row r="362">
       <c r="A362" s="11"/>
@@ -5403,12 +5766,13 @@
       <c r="D362" s="11"/>
       <c r="E362" s="11"/>
       <c r="F362" s="11"/>
-      <c r="G362" s="12"/>
-      <c r="H362" s="13"/>
-      <c r="I362" s="11"/>
+      <c r="G362" s="11"/>
+      <c r="H362" s="11"/>
+      <c r="I362" s="12"/>
       <c r="J362" s="11"/>
       <c r="K362" s="11"/>
       <c r="L362" s="11"/>
+      <c r="M362" s="11"/>
     </row>
     <row r="363">
       <c r="A363" s="11"/>
@@ -5417,12 +5781,13 @@
       <c r="D363" s="11"/>
       <c r="E363" s="11"/>
       <c r="F363" s="11"/>
-      <c r="G363" s="12"/>
-      <c r="H363" s="13"/>
-      <c r="I363" s="11"/>
+      <c r="G363" s="11"/>
+      <c r="H363" s="11"/>
+      <c r="I363" s="12"/>
       <c r="J363" s="11"/>
       <c r="K363" s="11"/>
       <c r="L363" s="11"/>
+      <c r="M363" s="11"/>
     </row>
     <row r="364">
       <c r="A364" s="11"/>
@@ -5431,12 +5796,13 @@
       <c r="D364" s="11"/>
       <c r="E364" s="11"/>
       <c r="F364" s="11"/>
-      <c r="G364" s="12"/>
-      <c r="H364" s="13"/>
-      <c r="I364" s="11"/>
+      <c r="G364" s="11"/>
+      <c r="H364" s="11"/>
+      <c r="I364" s="12"/>
       <c r="J364" s="11"/>
       <c r="K364" s="11"/>
       <c r="L364" s="11"/>
+      <c r="M364" s="11"/>
     </row>
     <row r="365">
       <c r="A365" s="11"/>
@@ -5445,12 +5811,13 @@
       <c r="D365" s="11"/>
       <c r="E365" s="11"/>
       <c r="F365" s="11"/>
-      <c r="G365" s="12"/>
-      <c r="H365" s="13"/>
-      <c r="I365" s="11"/>
+      <c r="G365" s="11"/>
+      <c r="H365" s="11"/>
+      <c r="I365" s="12"/>
       <c r="J365" s="11"/>
       <c r="K365" s="11"/>
       <c r="L365" s="11"/>
+      <c r="M365" s="11"/>
     </row>
     <row r="366">
       <c r="A366" s="11"/>
@@ -5459,12 +5826,13 @@
       <c r="D366" s="11"/>
       <c r="E366" s="11"/>
       <c r="F366" s="11"/>
-      <c r="G366" s="12"/>
-      <c r="H366" s="13"/>
-      <c r="I366" s="11"/>
+      <c r="G366" s="11"/>
+      <c r="H366" s="11"/>
+      <c r="I366" s="12"/>
       <c r="J366" s="11"/>
       <c r="K366" s="11"/>
       <c r="L366" s="11"/>
+      <c r="M366" s="11"/>
     </row>
     <row r="367">
       <c r="A367" s="11"/>
@@ -5473,12 +5841,13 @@
       <c r="D367" s="11"/>
       <c r="E367" s="11"/>
       <c r="F367" s="11"/>
-      <c r="G367" s="12"/>
-      <c r="H367" s="13"/>
-      <c r="I367" s="11"/>
+      <c r="G367" s="11"/>
+      <c r="H367" s="11"/>
+      <c r="I367" s="12"/>
       <c r="J367" s="11"/>
       <c r="K367" s="11"/>
       <c r="L367" s="11"/>
+      <c r="M367" s="11"/>
     </row>
     <row r="368">
       <c r="A368" s="11"/>
@@ -5487,12 +5856,13 @@
       <c r="D368" s="11"/>
       <c r="E368" s="11"/>
       <c r="F368" s="11"/>
-      <c r="G368" s="12"/>
-      <c r="H368" s="13"/>
-      <c r="I368" s="11"/>
+      <c r="G368" s="11"/>
+      <c r="H368" s="11"/>
+      <c r="I368" s="12"/>
       <c r="J368" s="11"/>
       <c r="K368" s="11"/>
       <c r="L368" s="11"/>
+      <c r="M368" s="11"/>
     </row>
     <row r="369">
       <c r="A369" s="11"/>
@@ -5501,12 +5871,13 @@
       <c r="D369" s="11"/>
       <c r="E369" s="11"/>
       <c r="F369" s="11"/>
-      <c r="G369" s="12"/>
-      <c r="H369" s="13"/>
-      <c r="I369" s="11"/>
+      <c r="G369" s="11"/>
+      <c r="H369" s="11"/>
+      <c r="I369" s="12"/>
       <c r="J369" s="11"/>
       <c r="K369" s="11"/>
       <c r="L369" s="11"/>
+      <c r="M369" s="11"/>
     </row>
     <row r="370">
       <c r="A370" s="11"/>
@@ -5515,12 +5886,13 @@
       <c r="D370" s="11"/>
       <c r="E370" s="11"/>
       <c r="F370" s="11"/>
-      <c r="G370" s="12"/>
-      <c r="H370" s="13"/>
-      <c r="I370" s="11"/>
+      <c r="G370" s="11"/>
+      <c r="H370" s="11"/>
+      <c r="I370" s="12"/>
       <c r="J370" s="11"/>
       <c r="K370" s="11"/>
       <c r="L370" s="11"/>
+      <c r="M370" s="11"/>
     </row>
     <row r="371">
       <c r="A371" s="11"/>
@@ -5529,12 +5901,13 @@
       <c r="D371" s="11"/>
       <c r="E371" s="11"/>
       <c r="F371" s="11"/>
-      <c r="G371" s="12"/>
-      <c r="H371" s="13"/>
-      <c r="I371" s="11"/>
+      <c r="G371" s="11"/>
+      <c r="H371" s="11"/>
+      <c r="I371" s="12"/>
       <c r="J371" s="11"/>
       <c r="K371" s="11"/>
       <c r="L371" s="11"/>
+      <c r="M371" s="11"/>
     </row>
     <row r="372">
       <c r="A372" s="11"/>
@@ -5543,12 +5916,13 @@
       <c r="D372" s="11"/>
       <c r="E372" s="11"/>
       <c r="F372" s="11"/>
-      <c r="G372" s="12"/>
-      <c r="H372" s="13"/>
-      <c r="I372" s="11"/>
+      <c r="G372" s="11"/>
+      <c r="H372" s="11"/>
+      <c r="I372" s="12"/>
       <c r="J372" s="11"/>
       <c r="K372" s="11"/>
       <c r="L372" s="11"/>
+      <c r="M372" s="11"/>
     </row>
     <row r="373">
       <c r="A373" s="11"/>
@@ -5557,12 +5931,13 @@
       <c r="D373" s="11"/>
       <c r="E373" s="11"/>
       <c r="F373" s="11"/>
-      <c r="G373" s="12"/>
-      <c r="H373" s="13"/>
-      <c r="I373" s="11"/>
+      <c r="G373" s="11"/>
+      <c r="H373" s="11"/>
+      <c r="I373" s="12"/>
       <c r="J373" s="11"/>
       <c r="K373" s="11"/>
       <c r="L373" s="11"/>
+      <c r="M373" s="11"/>
     </row>
     <row r="374">
       <c r="A374" s="11"/>
@@ -5571,12 +5946,13 @@
       <c r="D374" s="11"/>
       <c r="E374" s="11"/>
       <c r="F374" s="11"/>
-      <c r="G374" s="12"/>
-      <c r="H374" s="13"/>
-      <c r="I374" s="11"/>
+      <c r="G374" s="11"/>
+      <c r="H374" s="11"/>
+      <c r="I374" s="12"/>
       <c r="J374" s="11"/>
       <c r="K374" s="11"/>
       <c r="L374" s="11"/>
+      <c r="M374" s="11"/>
     </row>
     <row r="375">
       <c r="A375" s="11"/>
@@ -5585,12 +5961,13 @@
       <c r="D375" s="11"/>
       <c r="E375" s="11"/>
       <c r="F375" s="11"/>
-      <c r="G375" s="12"/>
-      <c r="H375" s="13"/>
-      <c r="I375" s="11"/>
+      <c r="G375" s="11"/>
+      <c r="H375" s="11"/>
+      <c r="I375" s="12"/>
       <c r="J375" s="11"/>
       <c r="K375" s="11"/>
       <c r="L375" s="11"/>
+      <c r="M375" s="11"/>
     </row>
     <row r="376">
       <c r="A376" s="11"/>
@@ -5599,12 +5976,13 @@
       <c r="D376" s="11"/>
       <c r="E376" s="11"/>
       <c r="F376" s="11"/>
-      <c r="G376" s="12"/>
-      <c r="H376" s="13"/>
-      <c r="I376" s="11"/>
+      <c r="G376" s="11"/>
+      <c r="H376" s="11"/>
+      <c r="I376" s="12"/>
       <c r="J376" s="11"/>
       <c r="K376" s="11"/>
       <c r="L376" s="11"/>
+      <c r="M376" s="11"/>
     </row>
     <row r="377">
       <c r="A377" s="11"/>
@@ -5613,12 +5991,13 @@
       <c r="D377" s="11"/>
       <c r="E377" s="11"/>
       <c r="F377" s="11"/>
-      <c r="G377" s="12"/>
-      <c r="H377" s="13"/>
-      <c r="I377" s="11"/>
+      <c r="G377" s="11"/>
+      <c r="H377" s="11"/>
+      <c r="I377" s="12"/>
       <c r="J377" s="11"/>
       <c r="K377" s="11"/>
       <c r="L377" s="11"/>
+      <c r="M377" s="11"/>
     </row>
     <row r="378">
       <c r="A378" s="11"/>
@@ -5627,12 +6006,13 @@
       <c r="D378" s="11"/>
       <c r="E378" s="11"/>
       <c r="F378" s="11"/>
-      <c r="G378" s="12"/>
-      <c r="H378" s="13"/>
-      <c r="I378" s="11"/>
+      <c r="G378" s="11"/>
+      <c r="H378" s="11"/>
+      <c r="I378" s="12"/>
       <c r="J378" s="11"/>
       <c r="K378" s="11"/>
       <c r="L378" s="11"/>
+      <c r="M378" s="11"/>
     </row>
     <row r="379">
       <c r="A379" s="11"/>
@@ -5641,12 +6021,13 @@
       <c r="D379" s="11"/>
       <c r="E379" s="11"/>
       <c r="F379" s="11"/>
-      <c r="G379" s="12"/>
-      <c r="H379" s="13"/>
-      <c r="I379" s="11"/>
+      <c r="G379" s="11"/>
+      <c r="H379" s="11"/>
+      <c r="I379" s="12"/>
       <c r="J379" s="11"/>
       <c r="K379" s="11"/>
       <c r="L379" s="11"/>
+      <c r="M379" s="11"/>
     </row>
     <row r="380">
       <c r="A380" s="11"/>
@@ -5655,12 +6036,13 @@
       <c r="D380" s="11"/>
       <c r="E380" s="11"/>
       <c r="F380" s="11"/>
-      <c r="G380" s="12"/>
-      <c r="H380" s="13"/>
-      <c r="I380" s="11"/>
+      <c r="G380" s="11"/>
+      <c r="H380" s="11"/>
+      <c r="I380" s="12"/>
       <c r="J380" s="11"/>
       <c r="K380" s="11"/>
       <c r="L380" s="11"/>
+      <c r="M380" s="11"/>
     </row>
     <row r="381">
       <c r="A381" s="11"/>
@@ -5669,12 +6051,13 @@
       <c r="D381" s="11"/>
       <c r="E381" s="11"/>
       <c r="F381" s="11"/>
-      <c r="G381" s="12"/>
-      <c r="H381" s="13"/>
-      <c r="I381" s="11"/>
+      <c r="G381" s="11"/>
+      <c r="H381" s="11"/>
+      <c r="I381" s="12"/>
       <c r="J381" s="11"/>
       <c r="K381" s="11"/>
       <c r="L381" s="11"/>
+      <c r="M381" s="11"/>
     </row>
     <row r="382">
       <c r="A382" s="11"/>
@@ -5683,12 +6066,13 @@
       <c r="D382" s="11"/>
       <c r="E382" s="11"/>
       <c r="F382" s="11"/>
-      <c r="G382" s="12"/>
-      <c r="H382" s="13"/>
-      <c r="I382" s="11"/>
+      <c r="G382" s="11"/>
+      <c r="H382" s="11"/>
+      <c r="I382" s="12"/>
       <c r="J382" s="11"/>
       <c r="K382" s="11"/>
       <c r="L382" s="11"/>
+      <c r="M382" s="11"/>
     </row>
     <row r="383">
       <c r="A383" s="11"/>
@@ -5697,12 +6081,13 @@
       <c r="D383" s="11"/>
       <c r="E383" s="11"/>
       <c r="F383" s="11"/>
-      <c r="G383" s="12"/>
-      <c r="H383" s="13"/>
-      <c r="I383" s="11"/>
+      <c r="G383" s="11"/>
+      <c r="H383" s="11"/>
+      <c r="I383" s="12"/>
       <c r="J383" s="11"/>
       <c r="K383" s="11"/>
       <c r="L383" s="11"/>
+      <c r="M383" s="11"/>
     </row>
     <row r="384">
       <c r="A384" s="11"/>
@@ -5711,12 +6096,13 @@
       <c r="D384" s="11"/>
       <c r="E384" s="11"/>
       <c r="F384" s="11"/>
-      <c r="G384" s="12"/>
-      <c r="H384" s="13"/>
-      <c r="I384" s="11"/>
+      <c r="G384" s="11"/>
+      <c r="H384" s="11"/>
+      <c r="I384" s="12"/>
       <c r="J384" s="11"/>
       <c r="K384" s="11"/>
       <c r="L384" s="11"/>
+      <c r="M384" s="11"/>
     </row>
     <row r="385">
       <c r="A385" s="11"/>
@@ -5725,12 +6111,13 @@
       <c r="D385" s="11"/>
       <c r="E385" s="11"/>
       <c r="F385" s="11"/>
-      <c r="G385" s="12"/>
-      <c r="H385" s="13"/>
-      <c r="I385" s="11"/>
+      <c r="G385" s="11"/>
+      <c r="H385" s="11"/>
+      <c r="I385" s="12"/>
       <c r="J385" s="11"/>
       <c r="K385" s="11"/>
       <c r="L385" s="11"/>
+      <c r="M385" s="11"/>
     </row>
     <row r="386">
       <c r="A386" s="11"/>
@@ -5739,12 +6126,13 @@
       <c r="D386" s="11"/>
       <c r="E386" s="11"/>
       <c r="F386" s="11"/>
-      <c r="G386" s="12"/>
-      <c r="H386" s="13"/>
-      <c r="I386" s="11"/>
+      <c r="G386" s="11"/>
+      <c r="H386" s="11"/>
+      <c r="I386" s="12"/>
       <c r="J386" s="11"/>
       <c r="K386" s="11"/>
       <c r="L386" s="11"/>
+      <c r="M386" s="11"/>
     </row>
     <row r="387">
       <c r="A387" s="11"/>
@@ -5753,12 +6141,13 @@
       <c r="D387" s="11"/>
       <c r="E387" s="11"/>
       <c r="F387" s="11"/>
-      <c r="G387" s="12"/>
-      <c r="H387" s="13"/>
-      <c r="I387" s="11"/>
+      <c r="G387" s="11"/>
+      <c r="H387" s="11"/>
+      <c r="I387" s="12"/>
       <c r="J387" s="11"/>
       <c r="K387" s="11"/>
       <c r="L387" s="11"/>
+      <c r="M387" s="11"/>
     </row>
     <row r="388">
       <c r="A388" s="11"/>
@@ -5767,12 +6156,13 @@
       <c r="D388" s="11"/>
       <c r="E388" s="11"/>
       <c r="F388" s="11"/>
-      <c r="G388" s="12"/>
-      <c r="H388" s="13"/>
-      <c r="I388" s="11"/>
+      <c r="G388" s="11"/>
+      <c r="H388" s="11"/>
+      <c r="I388" s="12"/>
       <c r="J388" s="11"/>
       <c r="K388" s="11"/>
       <c r="L388" s="11"/>
+      <c r="M388" s="11"/>
     </row>
     <row r="389">
       <c r="A389" s="11"/>
@@ -5781,12 +6171,13 @@
       <c r="D389" s="11"/>
       <c r="E389" s="11"/>
       <c r="F389" s="11"/>
-      <c r="G389" s="12"/>
-      <c r="H389" s="13"/>
-      <c r="I389" s="11"/>
+      <c r="G389" s="11"/>
+      <c r="H389" s="11"/>
+      <c r="I389" s="12"/>
       <c r="J389" s="11"/>
       <c r="K389" s="11"/>
       <c r="L389" s="11"/>
+      <c r="M389" s="11"/>
     </row>
     <row r="390">
       <c r="A390" s="11"/>
@@ -5795,12 +6186,13 @@
       <c r="D390" s="11"/>
       <c r="E390" s="11"/>
       <c r="F390" s="11"/>
-      <c r="G390" s="12"/>
-      <c r="H390" s="13"/>
-      <c r="I390" s="11"/>
+      <c r="G390" s="11"/>
+      <c r="H390" s="11"/>
+      <c r="I390" s="12"/>
       <c r="J390" s="11"/>
       <c r="K390" s="11"/>
       <c r="L390" s="11"/>
+      <c r="M390" s="11"/>
     </row>
     <row r="391">
       <c r="A391" s="11"/>
@@ -5809,12 +6201,13 @@
       <c r="D391" s="11"/>
       <c r="E391" s="11"/>
       <c r="F391" s="11"/>
-      <c r="G391" s="12"/>
-      <c r="H391" s="13"/>
-      <c r="I391" s="11"/>
+      <c r="G391" s="11"/>
+      <c r="H391" s="11"/>
+      <c r="I391" s="12"/>
       <c r="J391" s="11"/>
       <c r="K391" s="11"/>
       <c r="L391" s="11"/>
+      <c r="M391" s="11"/>
     </row>
     <row r="392">
       <c r="A392" s="11"/>
@@ -5823,12 +6216,13 @@
       <c r="D392" s="11"/>
       <c r="E392" s="11"/>
       <c r="F392" s="11"/>
-      <c r="G392" s="12"/>
-      <c r="H392" s="13"/>
-      <c r="I392" s="11"/>
+      <c r="G392" s="11"/>
+      <c r="H392" s="11"/>
+      <c r="I392" s="12"/>
       <c r="J392" s="11"/>
       <c r="K392" s="11"/>
       <c r="L392" s="11"/>
+      <c r="M392" s="11"/>
     </row>
     <row r="393">
       <c r="A393" s="11"/>
@@ -5837,12 +6231,13 @@
       <c r="D393" s="11"/>
       <c r="E393" s="11"/>
       <c r="F393" s="11"/>
-      <c r="G393" s="12"/>
-      <c r="H393" s="13"/>
-      <c r="I393" s="11"/>
+      <c r="G393" s="11"/>
+      <c r="H393" s="11"/>
+      <c r="I393" s="12"/>
       <c r="J393" s="11"/>
       <c r="K393" s="11"/>
       <c r="L393" s="11"/>
+      <c r="M393" s="11"/>
     </row>
     <row r="394">
       <c r="A394" s="11"/>
@@ -5851,12 +6246,13 @@
       <c r="D394" s="11"/>
       <c r="E394" s="11"/>
       <c r="F394" s="11"/>
-      <c r="G394" s="12"/>
-      <c r="H394" s="13"/>
-      <c r="I394" s="11"/>
+      <c r="G394" s="11"/>
+      <c r="H394" s="11"/>
+      <c r="I394" s="12"/>
       <c r="J394" s="11"/>
       <c r="K394" s="11"/>
       <c r="L394" s="11"/>
+      <c r="M394" s="11"/>
     </row>
     <row r="395">
       <c r="A395" s="11"/>
@@ -5865,12 +6261,13 @@
       <c r="D395" s="11"/>
       <c r="E395" s="11"/>
       <c r="F395" s="11"/>
-      <c r="G395" s="12"/>
-      <c r="H395" s="13"/>
-      <c r="I395" s="11"/>
+      <c r="G395" s="11"/>
+      <c r="H395" s="11"/>
+      <c r="I395" s="12"/>
       <c r="J395" s="11"/>
       <c r="K395" s="11"/>
       <c r="L395" s="11"/>
+      <c r="M395" s="11"/>
     </row>
     <row r="396">
       <c r="A396" s="11"/>
@@ -5879,12 +6276,13 @@
       <c r="D396" s="11"/>
       <c r="E396" s="11"/>
       <c r="F396" s="11"/>
-      <c r="G396" s="12"/>
-      <c r="H396" s="13"/>
-      <c r="I396" s="11"/>
+      <c r="G396" s="11"/>
+      <c r="H396" s="11"/>
+      <c r="I396" s="12"/>
       <c r="J396" s="11"/>
       <c r="K396" s="11"/>
       <c r="L396" s="11"/>
+      <c r="M396" s="11"/>
     </row>
     <row r="397">
       <c r="A397" s="11"/>
@@ -5893,12 +6291,13 @@
       <c r="D397" s="11"/>
       <c r="E397" s="11"/>
       <c r="F397" s="11"/>
-      <c r="G397" s="12"/>
-      <c r="H397" s="13"/>
-      <c r="I397" s="11"/>
+      <c r="G397" s="11"/>
+      <c r="H397" s="11"/>
+      <c r="I397" s="12"/>
       <c r="J397" s="11"/>
       <c r="K397" s="11"/>
       <c r="L397" s="11"/>
+      <c r="M397" s="11"/>
     </row>
     <row r="398">
       <c r="A398" s="11"/>
@@ -5907,12 +6306,13 @@
       <c r="D398" s="11"/>
       <c r="E398" s="11"/>
       <c r="F398" s="11"/>
-      <c r="G398" s="12"/>
-      <c r="H398" s="13"/>
-      <c r="I398" s="11"/>
+      <c r="G398" s="11"/>
+      <c r="H398" s="11"/>
+      <c r="I398" s="12"/>
       <c r="J398" s="11"/>
       <c r="K398" s="11"/>
       <c r="L398" s="11"/>
+      <c r="M398" s="11"/>
     </row>
     <row r="399">
       <c r="A399" s="11"/>
@@ -5921,12 +6321,13 @@
       <c r="D399" s="11"/>
       <c r="E399" s="11"/>
       <c r="F399" s="11"/>
-      <c r="G399" s="12"/>
-      <c r="H399" s="13"/>
-      <c r="I399" s="11"/>
+      <c r="G399" s="11"/>
+      <c r="H399" s="11"/>
+      <c r="I399" s="12"/>
       <c r="J399" s="11"/>
       <c r="K399" s="11"/>
       <c r="L399" s="11"/>
+      <c r="M399" s="11"/>
     </row>
     <row r="400">
       <c r="A400" s="11"/>
@@ -5935,12 +6336,13 @@
       <c r="D400" s="11"/>
       <c r="E400" s="11"/>
       <c r="F400" s="11"/>
-      <c r="G400" s="12"/>
-      <c r="H400" s="13"/>
-      <c r="I400" s="11"/>
+      <c r="G400" s="11"/>
+      <c r="H400" s="11"/>
+      <c r="I400" s="12"/>
       <c r="J400" s="11"/>
       <c r="K400" s="11"/>
       <c r="L400" s="11"/>
+      <c r="M400" s="11"/>
     </row>
     <row r="401">
       <c r="A401" s="11"/>
@@ -5949,12 +6351,13 @@
       <c r="D401" s="11"/>
       <c r="E401" s="11"/>
       <c r="F401" s="11"/>
-      <c r="G401" s="12"/>
-      <c r="H401" s="13"/>
-      <c r="I401" s="11"/>
+      <c r="G401" s="11"/>
+      <c r="H401" s="11"/>
+      <c r="I401" s="12"/>
       <c r="J401" s="11"/>
       <c r="K401" s="11"/>
       <c r="L401" s="11"/>
+      <c r="M401" s="11"/>
     </row>
     <row r="402">
       <c r="A402" s="11"/>
@@ -5963,12 +6366,13 @@
       <c r="D402" s="11"/>
       <c r="E402" s="11"/>
       <c r="F402" s="11"/>
-      <c r="G402" s="12"/>
-      <c r="H402" s="13"/>
-      <c r="I402" s="11"/>
+      <c r="G402" s="11"/>
+      <c r="H402" s="11"/>
+      <c r="I402" s="12"/>
       <c r="J402" s="11"/>
       <c r="K402" s="11"/>
       <c r="L402" s="11"/>
+      <c r="M402" s="11"/>
     </row>
     <row r="403">
       <c r="A403" s="11"/>
@@ -5977,12 +6381,13 @@
       <c r="D403" s="11"/>
       <c r="E403" s="11"/>
       <c r="F403" s="11"/>
-      <c r="G403" s="12"/>
-      <c r="H403" s="13"/>
-      <c r="I403" s="11"/>
+      <c r="G403" s="11"/>
+      <c r="H403" s="11"/>
+      <c r="I403" s="12"/>
       <c r="J403" s="11"/>
       <c r="K403" s="11"/>
       <c r="L403" s="11"/>
+      <c r="M403" s="11"/>
     </row>
     <row r="404">
       <c r="A404" s="11"/>
@@ -5991,12 +6396,13 @@
       <c r="D404" s="11"/>
       <c r="E404" s="11"/>
       <c r="F404" s="11"/>
-      <c r="G404" s="12"/>
-      <c r="H404" s="13"/>
-      <c r="I404" s="11"/>
+      <c r="G404" s="11"/>
+      <c r="H404" s="11"/>
+      <c r="I404" s="12"/>
       <c r="J404" s="11"/>
       <c r="K404" s="11"/>
       <c r="L404" s="11"/>
+      <c r="M404" s="11"/>
     </row>
     <row r="405">
       <c r="A405" s="11"/>
@@ -6005,12 +6411,13 @@
       <c r="D405" s="11"/>
       <c r="E405" s="11"/>
       <c r="F405" s="11"/>
-      <c r="G405" s="12"/>
-      <c r="H405" s="13"/>
-      <c r="I405" s="11"/>
+      <c r="G405" s="11"/>
+      <c r="H405" s="11"/>
+      <c r="I405" s="12"/>
       <c r="J405" s="11"/>
       <c r="K405" s="11"/>
       <c r="L405" s="11"/>
+      <c r="M405" s="11"/>
     </row>
     <row r="406">
       <c r="A406" s="11"/>
@@ -6019,12 +6426,13 @@
       <c r="D406" s="11"/>
       <c r="E406" s="11"/>
       <c r="F406" s="11"/>
-      <c r="G406" s="12"/>
-      <c r="H406" s="13"/>
-      <c r="I406" s="11"/>
+      <c r="G406" s="11"/>
+      <c r="H406" s="11"/>
+      <c r="I406" s="12"/>
       <c r="J406" s="11"/>
       <c r="K406" s="11"/>
       <c r="L406" s="11"/>
+      <c r="M406" s="11"/>
     </row>
     <row r="407">
       <c r="A407" s="11"/>
@@ -6033,12 +6441,13 @@
       <c r="D407" s="11"/>
       <c r="E407" s="11"/>
       <c r="F407" s="11"/>
-      <c r="G407" s="12"/>
-      <c r="H407" s="13"/>
-      <c r="I407" s="11"/>
+      <c r="G407" s="11"/>
+      <c r="H407" s="11"/>
+      <c r="I407" s="12"/>
       <c r="J407" s="11"/>
       <c r="K407" s="11"/>
       <c r="L407" s="11"/>
+      <c r="M407" s="11"/>
     </row>
     <row r="408">
       <c r="A408" s="11"/>
@@ -6047,12 +6456,13 @@
       <c r="D408" s="11"/>
       <c r="E408" s="11"/>
       <c r="F408" s="11"/>
-      <c r="G408" s="12"/>
-      <c r="H408" s="13"/>
-      <c r="I408" s="11"/>
+      <c r="G408" s="11"/>
+      <c r="H408" s="11"/>
+      <c r="I408" s="12"/>
       <c r="J408" s="11"/>
       <c r="K408" s="11"/>
       <c r="L408" s="11"/>
+      <c r="M408" s="11"/>
     </row>
     <row r="409">
       <c r="A409" s="11"/>
@@ -6061,12 +6471,13 @@
       <c r="D409" s="11"/>
       <c r="E409" s="11"/>
       <c r="F409" s="11"/>
-      <c r="G409" s="12"/>
-      <c r="H409" s="13"/>
-      <c r="I409" s="11"/>
+      <c r="G409" s="11"/>
+      <c r="H409" s="11"/>
+      <c r="I409" s="12"/>
       <c r="J409" s="11"/>
       <c r="K409" s="11"/>
       <c r="L409" s="11"/>
+      <c r="M409" s="11"/>
     </row>
     <row r="410">
       <c r="A410" s="11"/>
@@ -6075,12 +6486,13 @@
       <c r="D410" s="11"/>
       <c r="E410" s="11"/>
       <c r="F410" s="11"/>
-      <c r="G410" s="12"/>
-      <c r="H410" s="13"/>
-      <c r="I410" s="11"/>
+      <c r="G410" s="11"/>
+      <c r="H410" s="11"/>
+      <c r="I410" s="12"/>
       <c r="J410" s="11"/>
       <c r="K410" s="11"/>
       <c r="L410" s="11"/>
+      <c r="M410" s="11"/>
     </row>
     <row r="411">
       <c r="A411" s="11"/>
@@ -6089,12 +6501,13 @@
       <c r="D411" s="11"/>
       <c r="E411" s="11"/>
       <c r="F411" s="11"/>
-      <c r="G411" s="12"/>
-      <c r="H411" s="13"/>
-      <c r="I411" s="11"/>
+      <c r="G411" s="11"/>
+      <c r="H411" s="11"/>
+      <c r="I411" s="12"/>
       <c r="J411" s="11"/>
       <c r="K411" s="11"/>
       <c r="L411" s="11"/>
+      <c r="M411" s="11"/>
     </row>
     <row r="412">
       <c r="A412" s="11"/>
@@ -6103,12 +6516,13 @@
       <c r="D412" s="11"/>
       <c r="E412" s="11"/>
       <c r="F412" s="11"/>
-      <c r="G412" s="12"/>
-      <c r="H412" s="13"/>
-      <c r="I412" s="11"/>
+      <c r="G412" s="11"/>
+      <c r="H412" s="11"/>
+      <c r="I412" s="12"/>
       <c r="J412" s="11"/>
       <c r="K412" s="11"/>
       <c r="L412" s="11"/>
+      <c r="M412" s="11"/>
     </row>
     <row r="413">
       <c r="A413" s="11"/>
@@ -6117,12 +6531,13 @@
       <c r="D413" s="11"/>
       <c r="E413" s="11"/>
       <c r="F413" s="11"/>
-      <c r="G413" s="12"/>
-      <c r="H413" s="13"/>
-      <c r="I413" s="11"/>
+      <c r="G413" s="11"/>
+      <c r="H413" s="11"/>
+      <c r="I413" s="12"/>
       <c r="J413" s="11"/>
       <c r="K413" s="11"/>
       <c r="L413" s="11"/>
+      <c r="M413" s="11"/>
     </row>
     <row r="414">
       <c r="A414" s="11"/>
@@ -6131,12 +6546,13 @@
       <c r="D414" s="11"/>
       <c r="E414" s="11"/>
       <c r="F414" s="11"/>
-      <c r="G414" s="12"/>
-      <c r="H414" s="13"/>
-      <c r="I414" s="11"/>
+      <c r="G414" s="11"/>
+      <c r="H414" s="11"/>
+      <c r="I414" s="12"/>
       <c r="J414" s="11"/>
       <c r="K414" s="11"/>
       <c r="L414" s="11"/>
+      <c r="M414" s="11"/>
     </row>
     <row r="415">
       <c r="A415" s="11"/>
@@ -6145,12 +6561,13 @@
       <c r="D415" s="11"/>
       <c r="E415" s="11"/>
       <c r="F415" s="11"/>
-      <c r="G415" s="12"/>
-      <c r="H415" s="13"/>
-      <c r="I415" s="11"/>
+      <c r="G415" s="11"/>
+      <c r="H415" s="11"/>
+      <c r="I415" s="12"/>
       <c r="J415" s="11"/>
       <c r="K415" s="11"/>
       <c r="L415" s="11"/>
+      <c r="M415" s="11"/>
     </row>
     <row r="416">
       <c r="A416" s="11"/>
@@ -6159,12 +6576,13 @@
       <c r="D416" s="11"/>
       <c r="E416" s="11"/>
       <c r="F416" s="11"/>
-      <c r="G416" s="12"/>
-      <c r="H416" s="13"/>
-      <c r="I416" s="11"/>
+      <c r="G416" s="11"/>
+      <c r="H416" s="11"/>
+      <c r="I416" s="12"/>
       <c r="J416" s="11"/>
       <c r="K416" s="11"/>
       <c r="L416" s="11"/>
+      <c r="M416" s="11"/>
     </row>
     <row r="417">
       <c r="A417" s="11"/>
@@ -6173,12 +6591,13 @@
       <c r="D417" s="11"/>
       <c r="E417" s="11"/>
       <c r="F417" s="11"/>
-      <c r="G417" s="12"/>
-      <c r="H417" s="13"/>
-      <c r="I417" s="11"/>
+      <c r="G417" s="11"/>
+      <c r="H417" s="11"/>
+      <c r="I417" s="12"/>
       <c r="J417" s="11"/>
       <c r="K417" s="11"/>
       <c r="L417" s="11"/>
+      <c r="M417" s="11"/>
     </row>
     <row r="418">
       <c r="A418" s="11"/>
@@ -6187,12 +6606,13 @@
       <c r="D418" s="11"/>
       <c r="E418" s="11"/>
       <c r="F418" s="11"/>
-      <c r="G418" s="12"/>
-      <c r="H418" s="13"/>
-      <c r="I418" s="11"/>
+      <c r="G418" s="11"/>
+      <c r="H418" s="11"/>
+      <c r="I418" s="12"/>
       <c r="J418" s="11"/>
       <c r="K418" s="11"/>
       <c r="L418" s="11"/>
+      <c r="M418" s="11"/>
     </row>
     <row r="419">
       <c r="A419" s="11"/>
@@ -6201,12 +6621,13 @@
       <c r="D419" s="11"/>
       <c r="E419" s="11"/>
       <c r="F419" s="11"/>
-      <c r="G419" s="12"/>
-      <c r="H419" s="13"/>
-      <c r="I419" s="11"/>
+      <c r="G419" s="11"/>
+      <c r="H419" s="11"/>
+      <c r="I419" s="12"/>
       <c r="J419" s="11"/>
       <c r="K419" s="11"/>
       <c r="L419" s="11"/>
+      <c r="M419" s="11"/>
     </row>
     <row r="420">
       <c r="A420" s="11"/>
@@ -6215,12 +6636,13 @@
       <c r="D420" s="11"/>
       <c r="E420" s="11"/>
       <c r="F420" s="11"/>
-      <c r="G420" s="12"/>
-      <c r="H420" s="13"/>
-      <c r="I420" s="11"/>
+      <c r="G420" s="11"/>
+      <c r="H420" s="11"/>
+      <c r="I420" s="12"/>
       <c r="J420" s="11"/>
       <c r="K420" s="11"/>
       <c r="L420" s="11"/>
+      <c r="M420" s="11"/>
     </row>
     <row r="421">
       <c r="A421" s="11"/>
@@ -6229,12 +6651,13 @@
       <c r="D421" s="11"/>
       <c r="E421" s="11"/>
       <c r="F421" s="11"/>
-      <c r="G421" s="12"/>
-      <c r="H421" s="13"/>
-      <c r="I421" s="11"/>
+      <c r="G421" s="11"/>
+      <c r="H421" s="11"/>
+      <c r="I421" s="12"/>
       <c r="J421" s="11"/>
       <c r="K421" s="11"/>
       <c r="L421" s="11"/>
+      <c r="M421" s="11"/>
     </row>
     <row r="422">
       <c r="A422" s="11"/>
@@ -6243,12 +6666,13 @@
       <c r="D422" s="11"/>
       <c r="E422" s="11"/>
       <c r="F422" s="11"/>
-      <c r="G422" s="12"/>
-      <c r="H422" s="13"/>
-      <c r="I422" s="11"/>
+      <c r="G422" s="11"/>
+      <c r="H422" s="11"/>
+      <c r="I422" s="12"/>
       <c r="J422" s="11"/>
       <c r="K422" s="11"/>
       <c r="L422" s="11"/>
+      <c r="M422" s="11"/>
     </row>
     <row r="423">
       <c r="A423" s="11"/>
@@ -6257,12 +6681,13 @@
       <c r="D423" s="11"/>
       <c r="E423" s="11"/>
       <c r="F423" s="11"/>
-      <c r="G423" s="12"/>
-      <c r="H423" s="13"/>
-      <c r="I423" s="11"/>
+      <c r="G423" s="11"/>
+      <c r="H423" s="11"/>
+      <c r="I423" s="12"/>
       <c r="J423" s="11"/>
       <c r="K423" s="11"/>
       <c r="L423" s="11"/>
+      <c r="M423" s="11"/>
     </row>
     <row r="424">
       <c r="A424" s="11"/>
@@ -6271,12 +6696,13 @@
       <c r="D424" s="11"/>
       <c r="E424" s="11"/>
       <c r="F424" s="11"/>
-      <c r="G424" s="12"/>
-      <c r="H424" s="13"/>
-      <c r="I424" s="11"/>
+      <c r="G424" s="11"/>
+      <c r="H424" s="11"/>
+      <c r="I424" s="12"/>
       <c r="J424" s="11"/>
       <c r="K424" s="11"/>
       <c r="L424" s="11"/>
+      <c r="M424" s="11"/>
     </row>
     <row r="425">
       <c r="A425" s="11"/>
@@ -6285,12 +6711,13 @@
       <c r="D425" s="11"/>
       <c r="E425" s="11"/>
       <c r="F425" s="11"/>
-      <c r="G425" s="12"/>
-      <c r="H425" s="13"/>
-      <c r="I425" s="11"/>
+      <c r="G425" s="11"/>
+      <c r="H425" s="11"/>
+      <c r="I425" s="12"/>
       <c r="J425" s="11"/>
       <c r="K425" s="11"/>
       <c r="L425" s="11"/>
+      <c r="M425" s="11"/>
     </row>
     <row r="426">
       <c r="A426" s="11"/>
@@ -6299,12 +6726,13 @@
       <c r="D426" s="11"/>
       <c r="E426" s="11"/>
       <c r="F426" s="11"/>
-      <c r="G426" s="12"/>
-      <c r="H426" s="13"/>
-      <c r="I426" s="11"/>
+      <c r="G426" s="11"/>
+      <c r="H426" s="11"/>
+      <c r="I426" s="12"/>
       <c r="J426" s="11"/>
       <c r="K426" s="11"/>
       <c r="L426" s="11"/>
+      <c r="M426" s="11"/>
     </row>
     <row r="427">
       <c r="A427" s="11"/>
@@ -6313,12 +6741,13 @@
       <c r="D427" s="11"/>
       <c r="E427" s="11"/>
       <c r="F427" s="11"/>
-      <c r="G427" s="12"/>
-      <c r="H427" s="13"/>
-      <c r="I427" s="11"/>
+      <c r="G427" s="11"/>
+      <c r="H427" s="11"/>
+      <c r="I427" s="12"/>
       <c r="J427" s="11"/>
       <c r="K427" s="11"/>
       <c r="L427" s="11"/>
+      <c r="M427" s="11"/>
     </row>
     <row r="428">
       <c r="A428" s="11"/>
@@ -6327,12 +6756,13 @@
       <c r="D428" s="11"/>
       <c r="E428" s="11"/>
       <c r="F428" s="11"/>
-      <c r="G428" s="12"/>
-      <c r="H428" s="13"/>
-      <c r="I428" s="11"/>
+      <c r="G428" s="11"/>
+      <c r="H428" s="11"/>
+      <c r="I428" s="12"/>
       <c r="J428" s="11"/>
       <c r="K428" s="11"/>
       <c r="L428" s="11"/>
+      <c r="M428" s="11"/>
     </row>
     <row r="429">
       <c r="A429" s="11"/>
@@ -6341,12 +6771,13 @@
       <c r="D429" s="11"/>
       <c r="E429" s="11"/>
       <c r="F429" s="11"/>
-      <c r="G429" s="12"/>
-      <c r="H429" s="13"/>
-      <c r="I429" s="11"/>
+      <c r="G429" s="11"/>
+      <c r="H429" s="11"/>
+      <c r="I429" s="12"/>
       <c r="J429" s="11"/>
       <c r="K429" s="11"/>
       <c r="L429" s="11"/>
+      <c r="M429" s="11"/>
     </row>
     <row r="430">
       <c r="A430" s="11"/>
@@ -6355,12 +6786,13 @@
       <c r="D430" s="11"/>
       <c r="E430" s="11"/>
       <c r="F430" s="11"/>
-      <c r="G430" s="12"/>
-      <c r="H430" s="13"/>
-      <c r="I430" s="11"/>
+      <c r="G430" s="11"/>
+      <c r="H430" s="11"/>
+      <c r="I430" s="12"/>
       <c r="J430" s="11"/>
       <c r="K430" s="11"/>
       <c r="L430" s="11"/>
+      <c r="M430" s="11"/>
     </row>
     <row r="431">
       <c r="A431" s="11"/>
@@ -6369,12 +6801,13 @@
       <c r="D431" s="11"/>
       <c r="E431" s="11"/>
       <c r="F431" s="11"/>
-      <c r="G431" s="12"/>
-      <c r="H431" s="13"/>
-      <c r="I431" s="11"/>
+      <c r="G431" s="11"/>
+      <c r="H431" s="11"/>
+      <c r="I431" s="12"/>
       <c r="J431" s="11"/>
       <c r="K431" s="11"/>
       <c r="L431" s="11"/>
+      <c r="M431" s="11"/>
     </row>
     <row r="432">
       <c r="A432" s="11"/>
@@ -6383,12 +6816,13 @@
       <c r="D432" s="11"/>
       <c r="E432" s="11"/>
       <c r="F432" s="11"/>
-      <c r="G432" s="12"/>
-      <c r="H432" s="13"/>
-      <c r="I432" s="11"/>
+      <c r="G432" s="11"/>
+      <c r="H432" s="11"/>
+      <c r="I432" s="12"/>
       <c r="J432" s="11"/>
       <c r="K432" s="11"/>
       <c r="L432" s="11"/>
+      <c r="M432" s="11"/>
     </row>
     <row r="433">
       <c r="A433" s="11"/>
@@ -6397,12 +6831,13 @@
       <c r="D433" s="11"/>
       <c r="E433" s="11"/>
       <c r="F433" s="11"/>
-      <c r="G433" s="12"/>
-      <c r="H433" s="13"/>
-      <c r="I433" s="11"/>
+      <c r="G433" s="11"/>
+      <c r="H433" s="11"/>
+      <c r="I433" s="12"/>
       <c r="J433" s="11"/>
       <c r="K433" s="11"/>
       <c r="L433" s="11"/>
+      <c r="M433" s="11"/>
     </row>
     <row r="434">
       <c r="A434" s="11"/>
@@ -6411,12 +6846,13 @@
       <c r="D434" s="11"/>
       <c r="E434" s="11"/>
       <c r="F434" s="11"/>
-      <c r="G434" s="12"/>
-      <c r="H434" s="13"/>
-      <c r="I434" s="11"/>
+      <c r="G434" s="11"/>
+      <c r="H434" s="11"/>
+      <c r="I434" s="12"/>
       <c r="J434" s="11"/>
       <c r="K434" s="11"/>
       <c r="L434" s="11"/>
+      <c r="M434" s="11"/>
     </row>
     <row r="435">
       <c r="A435" s="11"/>
@@ -6425,12 +6861,13 @@
       <c r="D435" s="11"/>
       <c r="E435" s="11"/>
       <c r="F435" s="11"/>
-      <c r="G435" s="12"/>
-      <c r="H435" s="13"/>
-      <c r="I435" s="11"/>
+      <c r="G435" s="11"/>
+      <c r="H435" s="11"/>
+      <c r="I435" s="12"/>
       <c r="J435" s="11"/>
       <c r="K435" s="11"/>
       <c r="L435" s="11"/>
+      <c r="M435" s="11"/>
     </row>
     <row r="436">
       <c r="A436" s="11"/>
@@ -6439,12 +6876,13 @@
       <c r="D436" s="11"/>
       <c r="E436" s="11"/>
       <c r="F436" s="11"/>
-      <c r="G436" s="12"/>
-      <c r="H436" s="13"/>
-      <c r="I436" s="11"/>
+      <c r="G436" s="11"/>
+      <c r="H436" s="11"/>
+      <c r="I436" s="12"/>
       <c r="J436" s="11"/>
       <c r="K436" s="11"/>
       <c r="L436" s="11"/>
+      <c r="M436" s="11"/>
     </row>
     <row r="437">
       <c r="A437" s="11"/>
@@ -6453,12 +6891,13 @@
       <c r="D437" s="11"/>
       <c r="E437" s="11"/>
       <c r="F437" s="11"/>
-      <c r="G437" s="12"/>
-      <c r="H437" s="13"/>
-      <c r="I437" s="11"/>
+      <c r="G437" s="11"/>
+      <c r="H437" s="11"/>
+      <c r="I437" s="12"/>
       <c r="J437" s="11"/>
       <c r="K437" s="11"/>
       <c r="L437" s="11"/>
+      <c r="M437" s="11"/>
     </row>
     <row r="438">
       <c r="A438" s="11"/>
@@ -6467,12 +6906,13 @@
       <c r="D438" s="11"/>
       <c r="E438" s="11"/>
       <c r="F438" s="11"/>
-      <c r="G438" s="12"/>
-      <c r="H438" s="13"/>
-      <c r="I438" s="11"/>
+      <c r="G438" s="11"/>
+      <c r="H438" s="11"/>
+      <c r="I438" s="12"/>
       <c r="J438" s="11"/>
       <c r="K438" s="11"/>
       <c r="L438" s="11"/>
+      <c r="M438" s="11"/>
     </row>
     <row r="439">
       <c r="A439" s="11"/>
@@ -6481,12 +6921,13 @@
       <c r="D439" s="11"/>
       <c r="E439" s="11"/>
       <c r="F439" s="11"/>
-      <c r="G439" s="12"/>
-      <c r="H439" s="13"/>
-      <c r="I439" s="11"/>
+      <c r="G439" s="11"/>
+      <c r="H439" s="11"/>
+      <c r="I439" s="12"/>
       <c r="J439" s="11"/>
       <c r="K439" s="11"/>
       <c r="L439" s="11"/>
+      <c r="M439" s="11"/>
     </row>
     <row r="440">
       <c r="A440" s="11"/>
@@ -6495,12 +6936,13 @@
       <c r="D440" s="11"/>
       <c r="E440" s="11"/>
       <c r="F440" s="11"/>
-      <c r="G440" s="12"/>
-      <c r="H440" s="13"/>
-      <c r="I440" s="11"/>
+      <c r="G440" s="11"/>
+      <c r="H440" s="11"/>
+      <c r="I440" s="12"/>
       <c r="J440" s="11"/>
       <c r="K440" s="11"/>
       <c r="L440" s="11"/>
+      <c r="M440" s="11"/>
     </row>
     <row r="441">
       <c r="A441" s="11"/>
@@ -6509,12 +6951,13 @@
       <c r="D441" s="11"/>
       <c r="E441" s="11"/>
       <c r="F441" s="11"/>
-      <c r="G441" s="12"/>
-      <c r="H441" s="13"/>
-      <c r="I441" s="11"/>
+      <c r="G441" s="11"/>
+      <c r="H441" s="11"/>
+      <c r="I441" s="12"/>
       <c r="J441" s="11"/>
       <c r="K441" s="11"/>
       <c r="L441" s="11"/>
+      <c r="M441" s="11"/>
     </row>
     <row r="442">
       <c r="A442" s="11"/>
@@ -6523,12 +6966,13 @@
       <c r="D442" s="11"/>
       <c r="E442" s="11"/>
       <c r="F442" s="11"/>
-      <c r="G442" s="12"/>
-      <c r="H442" s="13"/>
-      <c r="I442" s="11"/>
+      <c r="G442" s="11"/>
+      <c r="H442" s="11"/>
+      <c r="I442" s="12"/>
       <c r="J442" s="11"/>
       <c r="K442" s="11"/>
       <c r="L442" s="11"/>
+      <c r="M442" s="11"/>
     </row>
     <row r="443">
       <c r="A443" s="11"/>
@@ -6537,12 +6981,13 @@
       <c r="D443" s="11"/>
       <c r="E443" s="11"/>
       <c r="F443" s="11"/>
-      <c r="G443" s="12"/>
-      <c r="H443" s="13"/>
-      <c r="I443" s="11"/>
+      <c r="G443" s="11"/>
+      <c r="H443" s="11"/>
+      <c r="I443" s="12"/>
       <c r="J443" s="11"/>
       <c r="K443" s="11"/>
       <c r="L443" s="11"/>
+      <c r="M443" s="11"/>
     </row>
     <row r="444">
       <c r="A444" s="11"/>
@@ -6551,12 +6996,13 @@
       <c r="D444" s="11"/>
       <c r="E444" s="11"/>
       <c r="F444" s="11"/>
-      <c r="G444" s="12"/>
-      <c r="H444" s="13"/>
-      <c r="I444" s="11"/>
+      <c r="G444" s="11"/>
+      <c r="H444" s="11"/>
+      <c r="I444" s="12"/>
       <c r="J444" s="11"/>
       <c r="K444" s="11"/>
       <c r="L444" s="11"/>
+      <c r="M444" s="11"/>
     </row>
     <row r="445">
       <c r="A445" s="11"/>
@@ -6565,12 +7011,13 @@
       <c r="D445" s="11"/>
       <c r="E445" s="11"/>
       <c r="F445" s="11"/>
-      <c r="G445" s="12"/>
-      <c r="H445" s="13"/>
-      <c r="I445" s="11"/>
+      <c r="G445" s="11"/>
+      <c r="H445" s="11"/>
+      <c r="I445" s="12"/>
       <c r="J445" s="11"/>
       <c r="K445" s="11"/>
       <c r="L445" s="11"/>
+      <c r="M445" s="11"/>
     </row>
     <row r="446">
       <c r="A446" s="11"/>
@@ -6579,12 +7026,13 @@
       <c r="D446" s="11"/>
       <c r="E446" s="11"/>
       <c r="F446" s="11"/>
-      <c r="G446" s="12"/>
-      <c r="H446" s="13"/>
-      <c r="I446" s="11"/>
+      <c r="G446" s="11"/>
+      <c r="H446" s="11"/>
+      <c r="I446" s="12"/>
       <c r="J446" s="11"/>
       <c r="K446" s="11"/>
       <c r="L446" s="11"/>
+      <c r="M446" s="11"/>
     </row>
     <row r="447">
       <c r="A447" s="11"/>
@@ -6593,12 +7041,13 @@
       <c r="D447" s="11"/>
       <c r="E447" s="11"/>
       <c r="F447" s="11"/>
-      <c r="G447" s="12"/>
-      <c r="H447" s="13"/>
-      <c r="I447" s="11"/>
+      <c r="G447" s="11"/>
+      <c r="H447" s="11"/>
+      <c r="I447" s="12"/>
       <c r="J447" s="11"/>
       <c r="K447" s="11"/>
       <c r="L447" s="11"/>
+      <c r="M447" s="11"/>
     </row>
     <row r="448">
       <c r="A448" s="11"/>
@@ -6607,12 +7056,13 @@
       <c r="D448" s="11"/>
       <c r="E448" s="11"/>
       <c r="F448" s="11"/>
-      <c r="G448" s="12"/>
-      <c r="H448" s="13"/>
-      <c r="I448" s="11"/>
+      <c r="G448" s="11"/>
+      <c r="H448" s="11"/>
+      <c r="I448" s="12"/>
       <c r="J448" s="11"/>
       <c r="K448" s="11"/>
       <c r="L448" s="11"/>
+      <c r="M448" s="11"/>
     </row>
     <row r="449">
       <c r="A449" s="11"/>
@@ -6621,12 +7071,13 @@
       <c r="D449" s="11"/>
       <c r="E449" s="11"/>
       <c r="F449" s="11"/>
-      <c r="G449" s="12"/>
-      <c r="H449" s="13"/>
-      <c r="I449" s="11"/>
+      <c r="G449" s="11"/>
+      <c r="H449" s="11"/>
+      <c r="I449" s="12"/>
       <c r="J449" s="11"/>
       <c r="K449" s="11"/>
       <c r="L449" s="11"/>
+      <c r="M449" s="11"/>
     </row>
     <row r="450">
       <c r="A450" s="11"/>
@@ -6635,12 +7086,13 @@
       <c r="D450" s="11"/>
       <c r="E450" s="11"/>
       <c r="F450" s="11"/>
-      <c r="G450" s="12"/>
-      <c r="H450" s="13"/>
-      <c r="I450" s="11"/>
+      <c r="G450" s="11"/>
+      <c r="H450" s="11"/>
+      <c r="I450" s="12"/>
       <c r="J450" s="11"/>
       <c r="K450" s="11"/>
       <c r="L450" s="11"/>
+      <c r="M450" s="11"/>
     </row>
     <row r="451">
       <c r="A451" s="11"/>
@@ -6649,12 +7101,13 @@
       <c r="D451" s="11"/>
       <c r="E451" s="11"/>
       <c r="F451" s="11"/>
-      <c r="G451" s="12"/>
-      <c r="H451" s="13"/>
-      <c r="I451" s="11"/>
+      <c r="G451" s="11"/>
+      <c r="H451" s="11"/>
+      <c r="I451" s="12"/>
       <c r="J451" s="11"/>
       <c r="K451" s="11"/>
       <c r="L451" s="11"/>
+      <c r="M451" s="11"/>
     </row>
     <row r="452">
       <c r="A452" s="11"/>
@@ -6663,12 +7116,13 @@
       <c r="D452" s="11"/>
       <c r="E452" s="11"/>
       <c r="F452" s="11"/>
-      <c r="G452" s="12"/>
-      <c r="H452" s="13"/>
-      <c r="I452" s="11"/>
+      <c r="G452" s="11"/>
+      <c r="H452" s="11"/>
+      <c r="I452" s="12"/>
       <c r="J452" s="11"/>
       <c r="K452" s="11"/>
       <c r="L452" s="11"/>
+      <c r="M452" s="11"/>
     </row>
     <row r="453">
       <c r="A453" s="11"/>
@@ -6677,12 +7131,13 @@
       <c r="D453" s="11"/>
       <c r="E453" s="11"/>
       <c r="F453" s="11"/>
-      <c r="G453" s="12"/>
-      <c r="H453" s="13"/>
-      <c r="I453" s="11"/>
+      <c r="G453" s="11"/>
+      <c r="H453" s="11"/>
+      <c r="I453" s="12"/>
       <c r="J453" s="11"/>
       <c r="K453" s="11"/>
       <c r="L453" s="11"/>
+      <c r="M453" s="11"/>
     </row>
     <row r="454">
       <c r="A454" s="11"/>
@@ -6691,12 +7146,13 @@
       <c r="D454" s="11"/>
       <c r="E454" s="11"/>
       <c r="F454" s="11"/>
-      <c r="G454" s="12"/>
-      <c r="H454" s="13"/>
-      <c r="I454" s="11"/>
+      <c r="G454" s="11"/>
+      <c r="H454" s="11"/>
+      <c r="I454" s="12"/>
       <c r="J454" s="11"/>
       <c r="K454" s="11"/>
       <c r="L454" s="11"/>
+      <c r="M454" s="11"/>
     </row>
     <row r="455">
       <c r="A455" s="11"/>
@@ -6705,12 +7161,13 @@
       <c r="D455" s="11"/>
       <c r="E455" s="11"/>
       <c r="F455" s="11"/>
-      <c r="G455" s="12"/>
-      <c r="H455" s="13"/>
-      <c r="I455" s="11"/>
+      <c r="G455" s="11"/>
+      <c r="H455" s="11"/>
+      <c r="I455" s="12"/>
       <c r="J455" s="11"/>
       <c r="K455" s="11"/>
       <c r="L455" s="11"/>
+      <c r="M455" s="11"/>
     </row>
     <row r="456">
       <c r="A456" s="11"/>
@@ -6719,12 +7176,13 @@
       <c r="D456" s="11"/>
       <c r="E456" s="11"/>
       <c r="F456" s="11"/>
-      <c r="G456" s="12"/>
-      <c r="H456" s="13"/>
-      <c r="I456" s="11"/>
+      <c r="G456" s="11"/>
+      <c r="H456" s="11"/>
+      <c r="I456" s="12"/>
       <c r="J456" s="11"/>
       <c r="K456" s="11"/>
       <c r="L456" s="11"/>
+      <c r="M456" s="11"/>
     </row>
     <row r="457">
       <c r="A457" s="11"/>
@@ -6733,12 +7191,13 @@
       <c r="D457" s="11"/>
       <c r="E457" s="11"/>
       <c r="F457" s="11"/>
-      <c r="G457" s="12"/>
-      <c r="H457" s="13"/>
-      <c r="I457" s="11"/>
+      <c r="G457" s="11"/>
+      <c r="H457" s="11"/>
+      <c r="I457" s="12"/>
       <c r="J457" s="11"/>
       <c r="K457" s="11"/>
       <c r="L457" s="11"/>
+      <c r="M457" s="11"/>
     </row>
     <row r="458">
       <c r="A458" s="11"/>
@@ -6747,12 +7206,13 @@
       <c r="D458" s="11"/>
       <c r="E458" s="11"/>
       <c r="F458" s="11"/>
-      <c r="G458" s="12"/>
-      <c r="H458" s="13"/>
-      <c r="I458" s="11"/>
+      <c r="G458" s="11"/>
+      <c r="H458" s="11"/>
+      <c r="I458" s="12"/>
       <c r="J458" s="11"/>
       <c r="K458" s="11"/>
       <c r="L458" s="11"/>
+      <c r="M458" s="11"/>
     </row>
     <row r="459">
       <c r="A459" s="11"/>
@@ -6761,12 +7221,13 @@
       <c r="D459" s="11"/>
       <c r="E459" s="11"/>
       <c r="F459" s="11"/>
-      <c r="G459" s="12"/>
-      <c r="H459" s="13"/>
-      <c r="I459" s="11"/>
+      <c r="G459" s="11"/>
+      <c r="H459" s="11"/>
+      <c r="I459" s="12"/>
       <c r="J459" s="11"/>
       <c r="K459" s="11"/>
       <c r="L459" s="11"/>
+      <c r="M459" s="11"/>
     </row>
     <row r="460">
       <c r="A460" s="11"/>
@@ -6775,12 +7236,13 @@
       <c r="D460" s="11"/>
       <c r="E460" s="11"/>
       <c r="F460" s="11"/>
-      <c r="G460" s="12"/>
-      <c r="H460" s="13"/>
-      <c r="I460" s="11"/>
+      <c r="G460" s="11"/>
+      <c r="H460" s="11"/>
+      <c r="I460" s="12"/>
       <c r="J460" s="11"/>
       <c r="K460" s="11"/>
       <c r="L460" s="11"/>
+      <c r="M460" s="11"/>
     </row>
     <row r="461">
       <c r="A461" s="11"/>
@@ -6789,12 +7251,13 @@
       <c r="D461" s="11"/>
       <c r="E461" s="11"/>
       <c r="F461" s="11"/>
-      <c r="G461" s="12"/>
-      <c r="H461" s="13"/>
-      <c r="I461" s="11"/>
+      <c r="G461" s="11"/>
+      <c r="H461" s="11"/>
+      <c r="I461" s="12"/>
       <c r="J461" s="11"/>
       <c r="K461" s="11"/>
       <c r="L461" s="11"/>
+      <c r="M461" s="11"/>
     </row>
     <row r="462">
       <c r="A462" s="11"/>
@@ -6803,12 +7266,13 @@
       <c r="D462" s="11"/>
       <c r="E462" s="11"/>
       <c r="F462" s="11"/>
-      <c r="G462" s="12"/>
-      <c r="H462" s="13"/>
-      <c r="I462" s="11"/>
+      <c r="G462" s="11"/>
+      <c r="H462" s="11"/>
+      <c r="I462" s="12"/>
       <c r="J462" s="11"/>
       <c r="K462" s="11"/>
       <c r="L462" s="11"/>
+      <c r="M462" s="11"/>
     </row>
     <row r="463">
       <c r="A463" s="11"/>
@@ -6817,12 +7281,13 @@
       <c r="D463" s="11"/>
       <c r="E463" s="11"/>
       <c r="F463" s="11"/>
-      <c r="G463" s="12"/>
-      <c r="H463" s="13"/>
-      <c r="I463" s="11"/>
+      <c r="G463" s="11"/>
+      <c r="H463" s="11"/>
+      <c r="I463" s="12"/>
       <c r="J463" s="11"/>
       <c r="K463" s="11"/>
       <c r="L463" s="11"/>
+      <c r="M463" s="11"/>
     </row>
     <row r="464">
       <c r="A464" s="11"/>
@@ -6831,12 +7296,13 @@
       <c r="D464" s="11"/>
       <c r="E464" s="11"/>
       <c r="F464" s="11"/>
-      <c r="G464" s="12"/>
-      <c r="H464" s="13"/>
-      <c r="I464" s="11"/>
+      <c r="G464" s="11"/>
+      <c r="H464" s="11"/>
+      <c r="I464" s="12"/>
       <c r="J464" s="11"/>
       <c r="K464" s="11"/>
       <c r="L464" s="11"/>
+      <c r="M464" s="11"/>
     </row>
     <row r="465">
       <c r="A465" s="11"/>
@@ -6845,12 +7311,13 @@
       <c r="D465" s="11"/>
       <c r="E465" s="11"/>
       <c r="F465" s="11"/>
-      <c r="G465" s="12"/>
-      <c r="H465" s="13"/>
-      <c r="I465" s="11"/>
+      <c r="G465" s="11"/>
+      <c r="H465" s="11"/>
+      <c r="I465" s="12"/>
       <c r="J465" s="11"/>
       <c r="K465" s="11"/>
       <c r="L465" s="11"/>
+      <c r="M465" s="11"/>
     </row>
     <row r="466">
       <c r="A466" s="11"/>
@@ -6859,12 +7326,13 @@
       <c r="D466" s="11"/>
       <c r="E466" s="11"/>
       <c r="F466" s="11"/>
-      <c r="G466" s="12"/>
-      <c r="H466" s="13"/>
-      <c r="I466" s="11"/>
+      <c r="G466" s="11"/>
+      <c r="H466" s="11"/>
+      <c r="I466" s="12"/>
       <c r="J466" s="11"/>
       <c r="K466" s="11"/>
       <c r="L466" s="11"/>
+      <c r="M466" s="11"/>
     </row>
     <row r="467">
       <c r="A467" s="11"/>
@@ -6873,12 +7341,13 @@
       <c r="D467" s="11"/>
       <c r="E467" s="11"/>
       <c r="F467" s="11"/>
-      <c r="G467" s="12"/>
-      <c r="H467" s="13"/>
-      <c r="I467" s="11"/>
+      <c r="G467" s="11"/>
+      <c r="H467" s="11"/>
+      <c r="I467" s="12"/>
       <c r="J467" s="11"/>
       <c r="K467" s="11"/>
       <c r="L467" s="11"/>
+      <c r="M467" s="11"/>
     </row>
     <row r="468">
       <c r="A468" s="11"/>
@@ -6887,12 +7356,13 @@
       <c r="D468" s="11"/>
       <c r="E468" s="11"/>
       <c r="F468" s="11"/>
-      <c r="G468" s="12"/>
-      <c r="H468" s="13"/>
-      <c r="I468" s="11"/>
+      <c r="G468" s="11"/>
+      <c r="H468" s="11"/>
+      <c r="I468" s="12"/>
       <c r="J468" s="11"/>
       <c r="K468" s="11"/>
       <c r="L468" s="11"/>
+      <c r="M468" s="11"/>
     </row>
     <row r="469">
       <c r="A469" s="11"/>
@@ -6901,12 +7371,13 @@
       <c r="D469" s="11"/>
       <c r="E469" s="11"/>
       <c r="F469" s="11"/>
-      <c r="G469" s="12"/>
-      <c r="H469" s="13"/>
-      <c r="I469" s="11"/>
+      <c r="G469" s="11"/>
+      <c r="H469" s="11"/>
+      <c r="I469" s="12"/>
       <c r="J469" s="11"/>
       <c r="K469" s="11"/>
       <c r="L469" s="11"/>
+      <c r="M469" s="11"/>
     </row>
     <row r="470">
       <c r="A470" s="11"/>
@@ -6915,12 +7386,13 @@
       <c r="D470" s="11"/>
       <c r="E470" s="11"/>
       <c r="F470" s="11"/>
-      <c r="G470" s="12"/>
-      <c r="H470" s="13"/>
-      <c r="I470" s="11"/>
+      <c r="G470" s="11"/>
+      <c r="H470" s="11"/>
+      <c r="I470" s="12"/>
       <c r="J470" s="11"/>
       <c r="K470" s="11"/>
       <c r="L470" s="11"/>
+      <c r="M470" s="11"/>
     </row>
     <row r="471">
       <c r="A471" s="11"/>
@@ -6929,12 +7401,13 @@
       <c r="D471" s="11"/>
       <c r="E471" s="11"/>
       <c r="F471" s="11"/>
-      <c r="G471" s="12"/>
-      <c r="H471" s="13"/>
-      <c r="I471" s="11"/>
+      <c r="G471" s="11"/>
+      <c r="H471" s="11"/>
+      <c r="I471" s="12"/>
       <c r="J471" s="11"/>
       <c r="K471" s="11"/>
       <c r="L471" s="11"/>
+      <c r="M471" s="11"/>
     </row>
     <row r="472">
       <c r="A472" s="11"/>
@@ -6943,12 +7416,13 @@
       <c r="D472" s="11"/>
       <c r="E472" s="11"/>
       <c r="F472" s="11"/>
-      <c r="G472" s="12"/>
-      <c r="H472" s="13"/>
-      <c r="I472" s="11"/>
+      <c r="G472" s="11"/>
+      <c r="H472" s="11"/>
+      <c r="I472" s="12"/>
       <c r="J472" s="11"/>
       <c r="K472" s="11"/>
       <c r="L472" s="11"/>
+      <c r="M472" s="11"/>
     </row>
     <row r="473">
       <c r="A473" s="11"/>
@@ -6957,12 +7431,13 @@
       <c r="D473" s="11"/>
       <c r="E473" s="11"/>
       <c r="F473" s="11"/>
-      <c r="G473" s="12"/>
-      <c r="H473" s="13"/>
-      <c r="I473" s="11"/>
+      <c r="G473" s="11"/>
+      <c r="H473" s="11"/>
+      <c r="I473" s="12"/>
       <c r="J473" s="11"/>
       <c r="K473" s="11"/>
       <c r="L473" s="11"/>
+      <c r="M473" s="11"/>
     </row>
     <row r="474">
       <c r="A474" s="11"/>
@@ -6971,12 +7446,13 @@
       <c r="D474" s="11"/>
       <c r="E474" s="11"/>
       <c r="F474" s="11"/>
-      <c r="G474" s="12"/>
-      <c r="H474" s="13"/>
-      <c r="I474" s="11"/>
+      <c r="G474" s="11"/>
+      <c r="H474" s="11"/>
+      <c r="I474" s="12"/>
       <c r="J474" s="11"/>
       <c r="K474" s="11"/>
       <c r="L474" s="11"/>
+      <c r="M474" s="11"/>
     </row>
     <row r="475">
       <c r="A475" s="11"/>
@@ -6985,12 +7461,13 @@
       <c r="D475" s="11"/>
       <c r="E475" s="11"/>
       <c r="F475" s="11"/>
-      <c r="G475" s="12"/>
-      <c r="H475" s="13"/>
-      <c r="I475" s="11"/>
+      <c r="G475" s="11"/>
+      <c r="H475" s="11"/>
+      <c r="I475" s="12"/>
       <c r="J475" s="11"/>
       <c r="K475" s="11"/>
       <c r="L475" s="11"/>
+      <c r="M475" s="11"/>
     </row>
     <row r="476">
       <c r="A476" s="11"/>
@@ -6999,12 +7476,13 @@
       <c r="D476" s="11"/>
       <c r="E476" s="11"/>
       <c r="F476" s="11"/>
-      <c r="G476" s="12"/>
-      <c r="H476" s="13"/>
-      <c r="I476" s="11"/>
+      <c r="G476" s="11"/>
+      <c r="H476" s="11"/>
+      <c r="I476" s="12"/>
       <c r="J476" s="11"/>
       <c r="K476" s="11"/>
       <c r="L476" s="11"/>
+      <c r="M476" s="11"/>
     </row>
     <row r="477">
       <c r="A477" s="11"/>
@@ -7013,12 +7491,13 @@
       <c r="D477" s="11"/>
       <c r="E477" s="11"/>
       <c r="F477" s="11"/>
-      <c r="G477" s="12"/>
-      <c r="H477" s="13"/>
-      <c r="I477" s="11"/>
+      <c r="G477" s="11"/>
+      <c r="H477" s="11"/>
+      <c r="I477" s="12"/>
       <c r="J477" s="11"/>
       <c r="K477" s="11"/>
       <c r="L477" s="11"/>
+      <c r="M477" s="11"/>
     </row>
     <row r="478">
       <c r="A478" s="11"/>
@@ -7027,12 +7506,13 @@
       <c r="D478" s="11"/>
       <c r="E478" s="11"/>
       <c r="F478" s="11"/>
-      <c r="G478" s="12"/>
-      <c r="H478" s="13"/>
-      <c r="I478" s="11"/>
+      <c r="G478" s="11"/>
+      <c r="H478" s="11"/>
+      <c r="I478" s="12"/>
       <c r="J478" s="11"/>
       <c r="K478" s="11"/>
       <c r="L478" s="11"/>
+      <c r="M478" s="11"/>
     </row>
     <row r="479">
       <c r="A479" s="11"/>
@@ -7041,12 +7521,13 @@
       <c r="D479" s="11"/>
       <c r="E479" s="11"/>
       <c r="F479" s="11"/>
-      <c r="G479" s="12"/>
-      <c r="H479" s="13"/>
-      <c r="I479" s="11"/>
+      <c r="G479" s="11"/>
+      <c r="H479" s="11"/>
+      <c r="I479" s="12"/>
       <c r="J479" s="11"/>
       <c r="K479" s="11"/>
       <c r="L479" s="11"/>
+      <c r="M479" s="11"/>
     </row>
     <row r="480">
       <c r="A480" s="11"/>
@@ -7055,12 +7536,13 @@
       <c r="D480" s="11"/>
       <c r="E480" s="11"/>
       <c r="F480" s="11"/>
-      <c r="G480" s="12"/>
-      <c r="H480" s="13"/>
-      <c r="I480" s="11"/>
+      <c r="G480" s="11"/>
+      <c r="H480" s="11"/>
+      <c r="I480" s="12"/>
       <c r="J480" s="11"/>
       <c r="K480" s="11"/>
       <c r="L480" s="11"/>
+      <c r="M480" s="11"/>
     </row>
     <row r="481">
       <c r="A481" s="11"/>
@@ -7069,12 +7551,13 @@
       <c r="D481" s="11"/>
       <c r="E481" s="11"/>
       <c r="F481" s="11"/>
-      <c r="G481" s="12"/>
-      <c r="H481" s="13"/>
-      <c r="I481" s="11"/>
+      <c r="G481" s="11"/>
+      <c r="H481" s="11"/>
+      <c r="I481" s="12"/>
       <c r="J481" s="11"/>
       <c r="K481" s="11"/>
       <c r="L481" s="11"/>
+      <c r="M481" s="11"/>
     </row>
     <row r="482">
       <c r="A482" s="11"/>
@@ -7083,12 +7566,13 @@
       <c r="D482" s="11"/>
       <c r="E482" s="11"/>
       <c r="F482" s="11"/>
-      <c r="G482" s="12"/>
-      <c r="H482" s="13"/>
-      <c r="I482" s="11"/>
+      <c r="G482" s="11"/>
+      <c r="H482" s="11"/>
+      <c r="I482" s="12"/>
       <c r="J482" s="11"/>
       <c r="K482" s="11"/>
       <c r="L482" s="11"/>
+      <c r="M482" s="11"/>
     </row>
     <row r="483">
       <c r="A483" s="11"/>
@@ -7097,12 +7581,13 @@
       <c r="D483" s="11"/>
       <c r="E483" s="11"/>
       <c r="F483" s="11"/>
-      <c r="G483" s="12"/>
-      <c r="H483" s="13"/>
-      <c r="I483" s="11"/>
+      <c r="G483" s="11"/>
+      <c r="H483" s="11"/>
+      <c r="I483" s="12"/>
       <c r="J483" s="11"/>
       <c r="K483" s="11"/>
       <c r="L483" s="11"/>
+      <c r="M483" s="11"/>
     </row>
     <row r="484">
       <c r="A484" s="11"/>
@@ -7111,12 +7596,13 @@
       <c r="D484" s="11"/>
       <c r="E484" s="11"/>
       <c r="F484" s="11"/>
-      <c r="G484" s="12"/>
-      <c r="H484" s="13"/>
-      <c r="I484" s="11"/>
+      <c r="G484" s="11"/>
+      <c r="H484" s="11"/>
+      <c r="I484" s="12"/>
       <c r="J484" s="11"/>
       <c r="K484" s="11"/>
       <c r="L484" s="11"/>
+      <c r="M484" s="11"/>
     </row>
     <row r="485">
       <c r="A485" s="11"/>
@@ -7125,12 +7611,13 @@
       <c r="D485" s="11"/>
       <c r="E485" s="11"/>
       <c r="F485" s="11"/>
-      <c r="G485" s="12"/>
-      <c r="H485" s="13"/>
-      <c r="I485" s="11"/>
+      <c r="G485" s="11"/>
+      <c r="H485" s="11"/>
+      <c r="I485" s="12"/>
       <c r="J485" s="11"/>
       <c r="K485" s="11"/>
       <c r="L485" s="11"/>
+      <c r="M485" s="11"/>
     </row>
     <row r="486">
       <c r="A486" s="11"/>
@@ -7139,12 +7626,13 @@
       <c r="D486" s="11"/>
       <c r="E486" s="11"/>
       <c r="F486" s="11"/>
-      <c r="G486" s="12"/>
-      <c r="H486" s="13"/>
-      <c r="I486" s="11"/>
+      <c r="G486" s="11"/>
+      <c r="H486" s="11"/>
+      <c r="I486" s="12"/>
       <c r="J486" s="11"/>
       <c r="K486" s="11"/>
       <c r="L486" s="11"/>
+      <c r="M486" s="11"/>
     </row>
     <row r="487">
       <c r="A487" s="11"/>
@@ -7153,12 +7641,13 @@
       <c r="D487" s="11"/>
       <c r="E487" s="11"/>
       <c r="F487" s="11"/>
-      <c r="G487" s="12"/>
-      <c r="H487" s="13"/>
-      <c r="I487" s="11"/>
+      <c r="G487" s="11"/>
+      <c r="H487" s="11"/>
+      <c r="I487" s="12"/>
       <c r="J487" s="11"/>
       <c r="K487" s="11"/>
       <c r="L487" s="11"/>
+      <c r="M487" s="11"/>
     </row>
     <row r="488">
       <c r="A488" s="11"/>
@@ -7167,12 +7656,13 @@
       <c r="D488" s="11"/>
       <c r="E488" s="11"/>
       <c r="F488" s="11"/>
-      <c r="G488" s="12"/>
-      <c r="H488" s="13"/>
-      <c r="I488" s="11"/>
+      <c r="G488" s="11"/>
+      <c r="H488" s="11"/>
+      <c r="I488" s="12"/>
       <c r="J488" s="11"/>
       <c r="K488" s="11"/>
       <c r="L488" s="11"/>
+      <c r="M488" s="11"/>
     </row>
     <row r="489">
       <c r="A489" s="11"/>
@@ -7181,12 +7671,13 @@
       <c r="D489" s="11"/>
       <c r="E489" s="11"/>
       <c r="F489" s="11"/>
-      <c r="G489" s="12"/>
-      <c r="H489" s="13"/>
-      <c r="I489" s="11"/>
+      <c r="G489" s="11"/>
+      <c r="H489" s="11"/>
+      <c r="I489" s="12"/>
       <c r="J489" s="11"/>
       <c r="K489" s="11"/>
       <c r="L489" s="11"/>
+      <c r="M489" s="11"/>
     </row>
     <row r="490">
       <c r="A490" s="11"/>
@@ -7195,12 +7686,13 @@
       <c r="D490" s="11"/>
       <c r="E490" s="11"/>
       <c r="F490" s="11"/>
-      <c r="G490" s="12"/>
-      <c r="H490" s="13"/>
-      <c r="I490" s="11"/>
+      <c r="G490" s="11"/>
+      <c r="H490" s="11"/>
+      <c r="I490" s="12"/>
       <c r="J490" s="11"/>
       <c r="K490" s="11"/>
       <c r="L490" s="11"/>
+      <c r="M490" s="11"/>
     </row>
     <row r="491">
       <c r="A491" s="11"/>
@@ -7209,12 +7701,13 @@
       <c r="D491" s="11"/>
       <c r="E491" s="11"/>
       <c r="F491" s="11"/>
-      <c r="G491" s="12"/>
-      <c r="H491" s="13"/>
-      <c r="I491" s="11"/>
+      <c r="G491" s="11"/>
+      <c r="H491" s="11"/>
+      <c r="I491" s="12"/>
       <c r="J491" s="11"/>
       <c r="K491" s="11"/>
       <c r="L491" s="11"/>
+      <c r="M491" s="11"/>
     </row>
     <row r="492">
       <c r="A492" s="11"/>
@@ -7223,12 +7716,13 @@
       <c r="D492" s="11"/>
       <c r="E492" s="11"/>
       <c r="F492" s="11"/>
-      <c r="G492" s="12"/>
-      <c r="H492" s="13"/>
-      <c r="I492" s="11"/>
+      <c r="G492" s="11"/>
+      <c r="H492" s="11"/>
+      <c r="I492" s="12"/>
       <c r="J492" s="11"/>
       <c r="K492" s="11"/>
       <c r="L492" s="11"/>
+      <c r="M492" s="11"/>
     </row>
     <row r="493">
       <c r="A493" s="11"/>
@@ -7237,12 +7731,13 @@
       <c r="D493" s="11"/>
       <c r="E493" s="11"/>
       <c r="F493" s="11"/>
-      <c r="G493" s="12"/>
-      <c r="H493" s="13"/>
-      <c r="I493" s="11"/>
+      <c r="G493" s="11"/>
+      <c r="H493" s="11"/>
+      <c r="I493" s="12"/>
       <c r="J493" s="11"/>
       <c r="K493" s="11"/>
       <c r="L493" s="11"/>
+      <c r="M493" s="11"/>
     </row>
     <row r="494">
       <c r="A494" s="11"/>
@@ -7251,12 +7746,13 @@
       <c r="D494" s="11"/>
       <c r="E494" s="11"/>
       <c r="F494" s="11"/>
-      <c r="G494" s="12"/>
-      <c r="H494" s="13"/>
-      <c r="I494" s="11"/>
+      <c r="G494" s="11"/>
+      <c r="H494" s="11"/>
+      <c r="I494" s="12"/>
       <c r="J494" s="11"/>
       <c r="K494" s="11"/>
       <c r="L494" s="11"/>
+      <c r="M494" s="11"/>
     </row>
     <row r="495">
       <c r="A495" s="11"/>
@@ -7265,12 +7761,13 @@
       <c r="D495" s="11"/>
       <c r="E495" s="11"/>
       <c r="F495" s="11"/>
-      <c r="G495" s="12"/>
-      <c r="H495" s="13"/>
-      <c r="I495" s="11"/>
+      <c r="G495" s="11"/>
+      <c r="H495" s="11"/>
+      <c r="I495" s="12"/>
       <c r="J495" s="11"/>
       <c r="K495" s="11"/>
       <c r="L495" s="11"/>
+      <c r="M495" s="11"/>
     </row>
     <row r="496">
       <c r="A496" s="11"/>
@@ -7279,12 +7776,13 @@
       <c r="D496" s="11"/>
       <c r="E496" s="11"/>
       <c r="F496" s="11"/>
-      <c r="G496" s="12"/>
-      <c r="H496" s="13"/>
-      <c r="I496" s="11"/>
+      <c r="G496" s="11"/>
+      <c r="H496" s="11"/>
+      <c r="I496" s="12"/>
       <c r="J496" s="11"/>
       <c r="K496" s="11"/>
       <c r="L496" s="11"/>
+      <c r="M496" s="11"/>
     </row>
     <row r="497">
       <c r="A497" s="11"/>
@@ -7293,12 +7791,13 @@
       <c r="D497" s="11"/>
       <c r="E497" s="11"/>
       <c r="F497" s="11"/>
-      <c r="G497" s="12"/>
-      <c r="H497" s="13"/>
-      <c r="I497" s="11"/>
+      <c r="G497" s="11"/>
+      <c r="H497" s="11"/>
+      <c r="I497" s="12"/>
       <c r="J497" s="11"/>
       <c r="K497" s="11"/>
       <c r="L497" s="11"/>
+      <c r="M497" s="11"/>
     </row>
     <row r="498">
       <c r="A498" s="11"/>
@@ -7307,12 +7806,13 @@
       <c r="D498" s="11"/>
       <c r="E498" s="11"/>
       <c r="F498" s="11"/>
-      <c r="G498" s="12"/>
-      <c r="H498" s="13"/>
-      <c r="I498" s="11"/>
+      <c r="G498" s="11"/>
+      <c r="H498" s="11"/>
+      <c r="I498" s="12"/>
       <c r="J498" s="11"/>
       <c r="K498" s="11"/>
       <c r="L498" s="11"/>
+      <c r="M498" s="11"/>
     </row>
     <row r="499">
       <c r="A499" s="11"/>
@@ -7321,12 +7821,13 @@
       <c r="D499" s="11"/>
       <c r="E499" s="11"/>
       <c r="F499" s="11"/>
-      <c r="G499" s="12"/>
-      <c r="H499" s="13"/>
-      <c r="I499" s="11"/>
+      <c r="G499" s="11"/>
+      <c r="H499" s="11"/>
+      <c r="I499" s="12"/>
       <c r="J499" s="11"/>
       <c r="K499" s="11"/>
       <c r="L499" s="11"/>
+      <c r="M499" s="11"/>
     </row>
     <row r="500">
       <c r="A500" s="11"/>
@@ -7335,12 +7836,13 @@
       <c r="D500" s="11"/>
       <c r="E500" s="11"/>
       <c r="F500" s="11"/>
-      <c r="G500" s="12"/>
-      <c r="H500" s="13"/>
-      <c r="I500" s="11"/>
+      <c r="G500" s="11"/>
+      <c r="H500" s="11"/>
+      <c r="I500" s="12"/>
       <c r="J500" s="11"/>
       <c r="K500" s="11"/>
       <c r="L500" s="11"/>
+      <c r="M500" s="11"/>
     </row>
     <row r="501">
       <c r="A501" s="11"/>
@@ -7349,12 +7851,13 @@
       <c r="D501" s="11"/>
       <c r="E501" s="11"/>
       <c r="F501" s="11"/>
-      <c r="G501" s="12"/>
-      <c r="H501" s="13"/>
-      <c r="I501" s="11"/>
+      <c r="G501" s="11"/>
+      <c r="H501" s="11"/>
+      <c r="I501" s="12"/>
       <c r="J501" s="11"/>
       <c r="K501" s="11"/>
       <c r="L501" s="11"/>
+      <c r="M501" s="11"/>
     </row>
     <row r="502">
       <c r="A502" s="11"/>
@@ -7363,12 +7866,13 @@
       <c r="D502" s="11"/>
       <c r="E502" s="11"/>
       <c r="F502" s="11"/>
-      <c r="G502" s="12"/>
-      <c r="H502" s="13"/>
-      <c r="I502" s="11"/>
+      <c r="G502" s="11"/>
+      <c r="H502" s="11"/>
+      <c r="I502" s="12"/>
       <c r="J502" s="11"/>
       <c r="K502" s="11"/>
       <c r="L502" s="11"/>
+      <c r="M502" s="11"/>
     </row>
     <row r="503">
       <c r="A503" s="11"/>
@@ -7377,12 +7881,13 @@
       <c r="D503" s="11"/>
       <c r="E503" s="11"/>
       <c r="F503" s="11"/>
-      <c r="G503" s="12"/>
-      <c r="H503" s="13"/>
-      <c r="I503" s="11"/>
+      <c r="G503" s="11"/>
+      <c r="H503" s="11"/>
+      <c r="I503" s="12"/>
       <c r="J503" s="11"/>
       <c r="K503" s="11"/>
       <c r="L503" s="11"/>
+      <c r="M503" s="11"/>
     </row>
     <row r="504">
       <c r="A504" s="11"/>
@@ -7391,42 +7896,43 @@
       <c r="D504" s="11"/>
       <c r="E504" s="11"/>
       <c r="F504" s="11"/>
-      <c r="G504" s="12"/>
-      <c r="H504" s="13"/>
-      <c r="I504" s="11"/>
+      <c r="G504" s="11"/>
+      <c r="H504" s="11"/>
+      <c r="I504" s="12"/>
       <c r="J504" s="11"/>
       <c r="K504" s="11"/>
       <c r="L504" s="11"/>
+      <c r="M504" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L504"/>
+  <autoFilter ref="A4:M504"/>
   <mergeCells count="4">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="D3:M3"/>
   </mergeCells>
   <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="warning" promptTitle="Số đơn / PO khách" prompt="Số đơn DH-… hoặc số PO khách duy nhất; TRỐNG hoặc &quot;chung&quot; = chi phí chung; chia nhiều đơn: DH-1:60%;DH-2:40% (theo %), DH-1:700.000;DH-2:300.000 (theo số tiền) hoặc chỉ liệt kê các đơn để chia đều." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị chưa có trong danh sách (vẫn có thể giữ nếu đúng tên/số)." sqref="A5:A504">
       <formula1>'Danh mục'!$K$2:$K$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="warning" promptTitle="Nhà cung cấp" prompt="Nhà cung cấp (tên viết tắt hoặc tên pháp lý)." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị chưa có trong danh sách (vẫn có thể giữ nếu đúng tên/số)." sqref="B5:B504">
-      <formula1>'Danh mục'!$J$2:$J$2</formula1>
+      <formula1>'Danh mục'!$J$2:$J$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="warning" promptTitle="Loại phí" prompt="Tên hoặc mã loại phí." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="E5:E504">
-      <formula1>'Danh mục'!$A$2:$A$6</formula1>
+      <formula1>'Danh mục'!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="warning" promptTitle="Thuế" prompt="KCT / số % / trống = chưa xác nhận." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="I5:I504">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="warning" promptTitle="Thuế" prompt="KCT / số % / trống = chưa xác nhận." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="J5:J504">
       <formula1>'Danh mục'!$H$2:$H$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Chi hộ (1/0)" prompt="1 = chi hộ." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="J5:J504">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Thu hộ (1/0)" prompt="1 = thu hộ (mình thu hộ, phải trả lại)." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="K5:K504">
       <formula1>'Danh mục'!$I$2:$I$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Tiền tệ" prompt="Để trống = tiền tệ của đơn (bắt buộc với chi phí chung)." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="K5:K504">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Tiền tệ" prompt="Để trống = tiền tệ của đơn (bắt buộc với chi phí chung)." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="L5:L504">
       <formula1>'Danh mục'!$E$2:$E$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Mã dịch vụ" prompt="Bắt buộc nếu PO có nhiều mã dịch vụ." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="L5:L504">
-      <formula1>'Danh mục'!$F$2:$F$4</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Mã dịch vụ" prompt="Bắt buộc nếu PO có nhiều mã dịch vụ." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="M5:M504">
+      <formula1>'Danh mục'!$F$2:$F$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -7440,7 +7946,7 @@
     <tabColor rgb="FF12304A"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -7452,55 +7958,55 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">BIỂU MẪU NHẬP HÀNG LOẠT — CHI PHÍ</t>
         </is>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" ht="8" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">CÁCH SỬ DỤNG</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Điền dữ liệu vào sheet "Nhập liệu" từ dòng 5 (mỗi dòng một bản ghi/dòng phí). Xóa dữ liệu mẫu nếu bạn sao chép từ sheet "Ví dụ".</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Trong ứng dụng: menu Nhập hàng loạt → chọn đúng tab → nút "Chọn tệp" và chọn tệp .xlsx này (hoặc copy vùng dữ liệu kể cả dòng tiêu đề rồi dán).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Bấm "Xem trước" để kiểm tra: lỗi được báo đúng dòng, đúng ô. Có lỗi thì sửa tệp và tải lại — hệ thống KHÔNG ghi gì cho đến khi tất cả dòng hợp lệ.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Khi hợp lệ, bấm ghi. Dữ liệu vào trạng thái nháp/chờ duyệt theo đúng quy trình thông thường.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">• Mỗi dòng là một khoản chi phí chưa nhận hóa đơn; sau đó nhận hóa đơn NCC ở màn COST/đơn hàng (hoặc dùng mẫu Hóa đơn mua để nhập thẳng hóa đơn kèm tự gắn PO).</t>
         </is>
@@ -7508,419 +8014,447 @@
     </row>
     <row r="9" ht="12" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">GIẢI THÍCH TỪNG CỘT</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Cột</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Tên cột</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Bắt buộc</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Kiểu dữ liệu</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Quy tắc / mô tả</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ví dụ</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Số đơn / PO khách</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Không</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Số đơn DH-… hoặc số PO khách duy nhất; TRỐNG hoặc "chung" = chi phí chung; chia nhiều đơn: DH-1:60%;DH-2:40% (theo %), DH-1:700.000;DH-2:300.000 (theo số tiền) hoặc chỉ liệt kê các đơn để chia đều.</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">DH-2026-000001</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">B</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nhà cung cấp</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nhà cung cấp (tên viết tắt hoặc tên pháp lý).</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Cảng Cát Lái</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">C</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">PO gửi NCC</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Không</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Số PO bạn gửi nhà cung cấp.</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">PO-NCC-01</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">D</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ngày</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ngày dd/MM/yyyy</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">dd/MM/yyyy; trong kỳ đang mở.</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">05/10/2026</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">E</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Loại phí</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Tên hoặc mã loại phí.</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Cước vận chuyển</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">F</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Diễn giải</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nội dung chi phí.</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Cước đường bộ</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">G</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SL container</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SL (số lượng)</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Không</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Số nguyên</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Số nguyên, tùy chọn.</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chữ</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Số lượng (tối đa 3 số lẻ, tùy chọn).</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">H</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chữ</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá (tối đa 4 số lẻ, tùy chọn; cần có SL). Có SL + đơn giá thì để trống Số tiền trước thuế: hệ thống tự tính = SL × đơn giá; nếu nhập cả hai phải khớp.</t>
+        </is>
+      </c>
+      <c r="F19" s="20"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Số tiền trước thuế</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Số tiền</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Chưa gồm thuế GTGT.</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">4800000</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">J</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Thuế</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Không</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">KCT / số % / trống = chưa xác nhận.</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">KCT</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chi hộ (1/0)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thu hộ (1/0)</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Không</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 = chi hộ.</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 = thu hộ (mình thu hộ, phải trả lại).</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiền tệ</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Không</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Để trống = tiền tệ của đơn (bắt buộc với chi phí chung).</t>
         </is>
       </c>
-      <c r="F22" s="21"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mã dịch vụ</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Không</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Bắt buộc nếu PO có nhiều mã dịch vụ.</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">FWD</t>
         </is>
@@ -7946,7 +8480,7 @@
     <tabColor rgb="FF2F855A"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -7956,15 +8490,16 @@
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">VÍ DỤ MINH HỌA — sao chép sang sheet "Nhập liệu" rồi sửa lại cho đúng dữ liệu của bạn (đừng giữ nguyên dòng mẫu)</t>
         </is>
@@ -8003,146 +8538,153 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SL container</t>
+          <t xml:space="preserve">SL (số lượng)</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Đơn giá</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Số tiền trước thuế *</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Thuế</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chi hộ (1/0)</t>
-        </is>
-      </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thu hộ (1/0)</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tiền tệ</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mã dịch vụ</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">DH-2026-000001</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Cảng Cát Lái</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">PO-NCC-01</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">05/10/2026</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Cước vận chuyển</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Cước đường bộ</t>
         </is>
       </c>
-      <c r="G3" s="25" t="inlineStr">
+      <c r="G3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H3" s="25" t="inlineStr">
+      <c r="H3" s="23"/>
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">4800000</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">KCT</t>
         </is>
       </c>
-      <c r="J3" s="24" t="inlineStr">
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24" t="inlineStr">
+      <c r="L3" s="23"/>
+      <c r="M3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">FWD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">chung</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Công ty Kho vận</t>
         </is>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="C4" s="23"/>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">06/10/2026</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Khác</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Phí kho chung tháng 10</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25" t="inlineStr">
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">2100000</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="J4" s="24" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">VND</t>
         </is>
       </c>
-      <c r="L4" s="24"/>
+      <c r="M4" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -8172,250 +8714,222 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Loại phí (tên)</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mã loại phí</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nhóm nghiệp vụ (mã)</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Tên nhóm</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiền tệ</t>
         </is>
       </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mã dịch vụ</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Tên dịch vụ</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Thuế</t>
         </is>
       </c>
-      <c r="I1" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chi hộ/thu hộ</t>
-        </is>
-      </c>
-      <c r="J1" s="18" t="inlineStr">
+      <c r="I1" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chi hộ (phải thu lại) / Thu hộ (phải trả lại)</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nhà cung cấp (đang hoạt động)</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="K1" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Đơn đang mở (số đơn · PO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Cước vận chuyển</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUCKING</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">G1</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nhóm 1</t>
-        </is>
-      </c>
-      <c r="E2" s="26" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhóm 1 (ví dụ)</t>
+        </is>
+      </c>
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">VND</t>
         </is>
       </c>
-      <c r="F2" s="26" t="inlineStr">
+      <c r="F2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">FWD</t>
         </is>
       </c>
-      <c r="G2" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forwarding</t>
-        </is>
-      </c>
-      <c r="H2" s="26" t="inlineStr">
+      <c r="G2" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forwarding (ví dụ)</t>
+        </is>
+      </c>
+      <c r="H2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">KCT</t>
         </is>
       </c>
-      <c r="I2" s="26" t="inlineStr">
+      <c r="I2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="J2" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(tên viết tắt đối tác của bạn)</t>
-        </is>
-      </c>
-      <c r="K2" s="26" t="inlineStr">
+      <c r="J2" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khách hàng A</t>
+        </is>
+      </c>
+      <c r="K2" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">DH-2026-000001</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Phí nâng/hạ container</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">CONT_LIFT</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G2</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nhóm 2</t>
-        </is>
-      </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">USD</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CFN</t>
-        </is>
-      </c>
-      <c r="G3" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chuyển phát nhanh</t>
-        </is>
-      </c>
-      <c r="H3" s="26" t="inlineStr">
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="I3" s="26" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
+      <c r="J3" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cảng Cát Lái</t>
+        </is>
+      </c>
+      <c r="K3" s="25"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Phí dịch vụ thủ tục hải quan</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">CUSTOMS_SERVICE</t>
         </is>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBT</t>
-        </is>
-      </c>
-      <c r="G4" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vận tải xuyên biên giới</t>
-        </is>
-      </c>
-      <c r="H4" s="26" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phí xin giấy phép</t>
-        </is>
-      </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PERMIT</t>
-        </is>
-      </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khác</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTHER</t>
+        </is>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Khác</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OTHER</t>
-        </is>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
